--- a/Raw_Data/lignin.xlsx
+++ b/Raw_Data/lignin.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dkb1g24\Documents\GitHub\Plant Phyllosphere CODH Prokaryotes (MRes Project)\Raw_Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deepankanagarajanbabu/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D76CF136-6BDE-482E-ACAC-75C07F3E79A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0876BE2B-D8E8-1C4A-9987-70FCDF3351EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4340" yWindow="760" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -27,14 +27,14 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
-    <t>This is unpublised data, the link to the file will be updated here, once the article is published.</t>
+    <t>Check "README.md" file to get the link.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -391,12 +391,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S1102"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.81640625" customWidth="1"/>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -418,7 +418,7 @@
       <c r="Q1" s="2"/>
       <c r="S1" s="1"/>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -439,7 +439,7 @@
       <c r="R2" s="3"/>
       <c r="S2" s="3"/>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -460,7 +460,7 @@
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -481,7 +481,7 @@
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
@@ -502,7 +502,7 @@
       <c r="R5" s="4"/>
       <c r="S5" s="4"/>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -523,7 +523,7 @@
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" s="4"/>
       <c r="B7" s="5"/>
       <c r="C7" s="4"/>
@@ -544,7 +544,7 @@
       <c r="R7" s="4"/>
       <c r="S7" s="4"/>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
       <c r="B8" s="5"/>
       <c r="C8" s="4"/>
@@ -565,7 +565,7 @@
       <c r="R8" s="4"/>
       <c r="S8" s="4"/>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
       <c r="B9" s="5"/>
       <c r="C9" s="4"/>
@@ -586,7 +586,7 @@
       <c r="R9" s="4"/>
       <c r="S9" s="4"/>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" s="4"/>
       <c r="B10" s="5"/>
       <c r="C10" s="4"/>
@@ -607,7 +607,7 @@
       <c r="R10" s="4"/>
       <c r="S10" s="4"/>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" s="4"/>
       <c r="B11" s="5"/>
       <c r="C11" s="4"/>
@@ -628,7 +628,7 @@
       <c r="R11" s="4"/>
       <c r="S11" s="4"/>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="4"/>
       <c r="B12" s="5"/>
       <c r="C12" s="4"/>
@@ -649,7 +649,7 @@
       <c r="R12" s="4"/>
       <c r="S12" s="4"/>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="4"/>
       <c r="B13" s="5"/>
       <c r="C13" s="4"/>
@@ -670,7 +670,7 @@
       <c r="R13" s="4"/>
       <c r="S13" s="4"/>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="4"/>
       <c r="B14" s="5"/>
       <c r="C14" s="4"/>
@@ -691,7 +691,7 @@
       <c r="R14" s="4"/>
       <c r="S14" s="4"/>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="4"/>
       <c r="B15" s="5"/>
       <c r="C15" s="4"/>
@@ -712,7 +712,7 @@
       <c r="R15" s="4"/>
       <c r="S15" s="4"/>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="4"/>
       <c r="B16" s="5"/>
       <c r="C16" s="4"/>
@@ -733,7 +733,7 @@
       <c r="R16" s="4"/>
       <c r="S16" s="4"/>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
       <c r="B17" s="5"/>
       <c r="C17" s="4"/>
@@ -754,7 +754,7 @@
       <c r="R17" s="4"/>
       <c r="S17" s="4"/>
     </row>
-    <row r="18" spans="1:19">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" s="4"/>
       <c r="B18" s="5"/>
       <c r="C18" s="4"/>
@@ -775,7 +775,7 @@
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
     </row>
-    <row r="19" spans="1:19">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" s="4"/>
       <c r="B19" s="5"/>
       <c r="C19" s="4"/>
@@ -796,7 +796,7 @@
       <c r="R19" s="4"/>
       <c r="S19" s="4"/>
     </row>
-    <row r="20" spans="1:19">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" s="4"/>
       <c r="B20" s="5"/>
       <c r="C20" s="4"/>
@@ -817,7 +817,7 @@
       <c r="R20" s="4"/>
       <c r="S20" s="4"/>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" s="4"/>
       <c r="B21" s="5"/>
       <c r="C21" s="4"/>
@@ -838,7 +838,7 @@
       <c r="R21" s="4"/>
       <c r="S21" s="4"/>
     </row>
-    <row r="22" spans="1:19">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" s="4"/>
       <c r="B22" s="5"/>
       <c r="C22" s="4"/>
@@ -859,7 +859,7 @@
       <c r="R22" s="4"/>
       <c r="S22" s="4"/>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" s="4"/>
       <c r="B23" s="5"/>
       <c r="C23" s="4"/>
@@ -880,7 +880,7 @@
       <c r="R23" s="4"/>
       <c r="S23" s="4"/>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" s="4"/>
       <c r="B24" s="5"/>
       <c r="C24" s="4"/>
@@ -901,7 +901,7 @@
       <c r="R24" s="4"/>
       <c r="S24" s="4"/>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" s="4"/>
       <c r="B25" s="5"/>
       <c r="C25" s="4"/>
@@ -922,7 +922,7 @@
       <c r="R25" s="4"/>
       <c r="S25" s="4"/>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" s="4"/>
       <c r="B26" s="5"/>
       <c r="C26" s="4"/>
@@ -943,7 +943,7 @@
       <c r="R26" s="4"/>
       <c r="S26" s="4"/>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" s="4"/>
       <c r="B27" s="5"/>
       <c r="C27" s="4"/>
@@ -964,7 +964,7 @@
       <c r="R27" s="4"/>
       <c r="S27" s="4"/>
     </row>
-    <row r="28" spans="1:19">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" s="4"/>
       <c r="B28" s="5"/>
       <c r="C28" s="4"/>
@@ -985,7 +985,7 @@
       <c r="R28" s="4"/>
       <c r="S28" s="4"/>
     </row>
-    <row r="29" spans="1:19">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" s="4"/>
       <c r="B29" s="5"/>
       <c r="C29" s="4"/>
@@ -1006,7 +1006,7 @@
       <c r="R29" s="4"/>
       <c r="S29" s="4"/>
     </row>
-    <row r="30" spans="1:19">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" s="4"/>
       <c r="B30" s="5"/>
       <c r="C30" s="4"/>
@@ -1027,7 +1027,7 @@
       <c r="R30" s="4"/>
       <c r="S30" s="4"/>
     </row>
-    <row r="31" spans="1:19">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31" s="4"/>
       <c r="B31" s="5"/>
       <c r="C31" s="4"/>
@@ -1048,7 +1048,7 @@
       <c r="R31" s="4"/>
       <c r="S31" s="4"/>
     </row>
-    <row r="32" spans="1:19">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32" s="4"/>
       <c r="B32" s="5"/>
       <c r="C32" s="4"/>
@@ -1069,7 +1069,7 @@
       <c r="R32" s="4"/>
       <c r="S32" s="4"/>
     </row>
-    <row r="33" spans="1:19">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" s="4"/>
       <c r="B33" s="5"/>
       <c r="C33" s="4"/>
@@ -1090,7 +1090,7 @@
       <c r="R33" s="4"/>
       <c r="S33" s="4"/>
     </row>
-    <row r="34" spans="1:19">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34" s="4"/>
       <c r="B34" s="5"/>
       <c r="C34" s="4"/>
@@ -1111,7 +1111,7 @@
       <c r="R34" s="4"/>
       <c r="S34" s="4"/>
     </row>
-    <row r="35" spans="1:19">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
       <c r="B35" s="5"/>
       <c r="C35" s="4"/>
@@ -1132,7 +1132,7 @@
       <c r="R35" s="4"/>
       <c r="S35" s="4"/>
     </row>
-    <row r="36" spans="1:19">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
       <c r="B36" s="5"/>
       <c r="C36" s="4"/>
@@ -1153,7 +1153,7 @@
       <c r="R36" s="4"/>
       <c r="S36" s="4"/>
     </row>
-    <row r="37" spans="1:19">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
       <c r="B37" s="5"/>
       <c r="C37" s="4"/>
@@ -1174,7 +1174,7 @@
       <c r="R37" s="4"/>
       <c r="S37" s="4"/>
     </row>
-    <row r="38" spans="1:19">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" s="4"/>
       <c r="B38" s="5"/>
       <c r="C38" s="4"/>
@@ -1195,7 +1195,7 @@
       <c r="R38" s="4"/>
       <c r="S38" s="4"/>
     </row>
-    <row r="39" spans="1:19">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39" s="4"/>
       <c r="B39" s="5"/>
       <c r="C39" s="4"/>
@@ -1216,7 +1216,7 @@
       <c r="R39" s="4"/>
       <c r="S39" s="4"/>
     </row>
-    <row r="40" spans="1:19">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40" s="4"/>
       <c r="B40" s="5"/>
       <c r="C40" s="4"/>
@@ -1237,7 +1237,7 @@
       <c r="R40" s="4"/>
       <c r="S40" s="4"/>
     </row>
-    <row r="41" spans="1:19">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A41" s="4"/>
       <c r="B41" s="5"/>
       <c r="C41" s="4"/>
@@ -1258,7 +1258,7 @@
       <c r="R41" s="4"/>
       <c r="S41" s="4"/>
     </row>
-    <row r="42" spans="1:19">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A42" s="4"/>
       <c r="B42" s="5"/>
       <c r="C42" s="4"/>
@@ -1279,7 +1279,7 @@
       <c r="R42" s="4"/>
       <c r="S42" s="4"/>
     </row>
-    <row r="43" spans="1:19">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A43" s="4"/>
       <c r="B43" s="5"/>
       <c r="C43" s="4"/>
@@ -1300,7 +1300,7 @@
       <c r="R43" s="4"/>
       <c r="S43" s="4"/>
     </row>
-    <row r="44" spans="1:19">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A44" s="4"/>
       <c r="B44" s="5"/>
       <c r="C44" s="4"/>
@@ -1321,7 +1321,7 @@
       <c r="R44" s="4"/>
       <c r="S44" s="4"/>
     </row>
-    <row r="45" spans="1:19">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" s="4"/>
       <c r="B45" s="5"/>
       <c r="C45" s="4"/>
@@ -1342,7 +1342,7 @@
       <c r="R45" s="4"/>
       <c r="S45" s="4"/>
     </row>
-    <row r="46" spans="1:19">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A46" s="4"/>
       <c r="B46" s="5"/>
       <c r="C46" s="4"/>
@@ -1363,7 +1363,7 @@
       <c r="R46" s="4"/>
       <c r="S46" s="4"/>
     </row>
-    <row r="47" spans="1:19">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47" s="4"/>
       <c r="B47" s="5"/>
       <c r="C47" s="4"/>
@@ -1384,7 +1384,7 @@
       <c r="R47" s="4"/>
       <c r="S47" s="4"/>
     </row>
-    <row r="48" spans="1:19">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A48" s="4"/>
       <c r="B48" s="5"/>
       <c r="C48" s="4"/>
@@ -1405,7 +1405,7 @@
       <c r="R48" s="4"/>
       <c r="S48" s="4"/>
     </row>
-    <row r="49" spans="1:19">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A49" s="4"/>
       <c r="B49" s="5"/>
       <c r="C49" s="4"/>
@@ -1426,7 +1426,7 @@
       <c r="R49" s="4"/>
       <c r="S49" s="4"/>
     </row>
-    <row r="50" spans="1:19">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A50" s="4"/>
       <c r="B50" s="5"/>
       <c r="C50" s="4"/>
@@ -1447,7 +1447,7 @@
       <c r="R50" s="4"/>
       <c r="S50" s="4"/>
     </row>
-    <row r="51" spans="1:19">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A51" s="4"/>
       <c r="B51" s="5"/>
       <c r="C51" s="4"/>
@@ -1468,7 +1468,7 @@
       <c r="R51" s="4"/>
       <c r="S51" s="4"/>
     </row>
-    <row r="52" spans="1:19">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A52" s="4"/>
       <c r="B52" s="5"/>
       <c r="C52" s="4"/>
@@ -1489,7 +1489,7 @@
       <c r="R52" s="4"/>
       <c r="S52" s="4"/>
     </row>
-    <row r="53" spans="1:19">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A53" s="4"/>
       <c r="B53" s="5"/>
       <c r="C53" s="4"/>
@@ -1510,7 +1510,7 @@
       <c r="R53" s="4"/>
       <c r="S53" s="4"/>
     </row>
-    <row r="54" spans="1:19">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A54" s="4"/>
       <c r="B54" s="5"/>
       <c r="C54" s="4"/>
@@ -1531,7 +1531,7 @@
       <c r="R54" s="4"/>
       <c r="S54" s="4"/>
     </row>
-    <row r="55" spans="1:19">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A55" s="4"/>
       <c r="B55" s="5"/>
       <c r="C55" s="4"/>
@@ -1552,7 +1552,7 @@
       <c r="R55" s="4"/>
       <c r="S55" s="4"/>
     </row>
-    <row r="56" spans="1:19">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A56" s="4"/>
       <c r="B56" s="5"/>
       <c r="C56" s="4"/>
@@ -1573,7 +1573,7 @@
       <c r="R56" s="4"/>
       <c r="S56" s="4"/>
     </row>
-    <row r="57" spans="1:19">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A57" s="4"/>
       <c r="B57" s="5"/>
       <c r="C57" s="4"/>
@@ -1594,7 +1594,7 @@
       <c r="R57" s="4"/>
       <c r="S57" s="4"/>
     </row>
-    <row r="58" spans="1:19">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A58" s="4"/>
       <c r="B58" s="5"/>
       <c r="C58" s="4"/>
@@ -1615,7 +1615,7 @@
       <c r="R58" s="4"/>
       <c r="S58" s="4"/>
     </row>
-    <row r="59" spans="1:19">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A59" s="4"/>
       <c r="B59" s="5"/>
       <c r="C59" s="4"/>
@@ -1636,7 +1636,7 @@
       <c r="R59" s="4"/>
       <c r="S59" s="4"/>
     </row>
-    <row r="60" spans="1:19">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A60" s="4"/>
       <c r="B60" s="5"/>
       <c r="C60" s="4"/>
@@ -1657,7 +1657,7 @@
       <c r="R60" s="4"/>
       <c r="S60" s="4"/>
     </row>
-    <row r="61" spans="1:19">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A61" s="4"/>
       <c r="B61" s="5"/>
       <c r="C61" s="4"/>
@@ -1678,7 +1678,7 @@
       <c r="R61" s="4"/>
       <c r="S61" s="4"/>
     </row>
-    <row r="62" spans="1:19">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A62" s="4"/>
       <c r="B62" s="5"/>
       <c r="C62" s="4"/>
@@ -1699,7 +1699,7 @@
       <c r="R62" s="4"/>
       <c r="S62" s="4"/>
     </row>
-    <row r="63" spans="1:19">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A63" s="4"/>
       <c r="B63" s="5"/>
       <c r="C63" s="4"/>
@@ -1720,7 +1720,7 @@
       <c r="R63" s="4"/>
       <c r="S63" s="4"/>
     </row>
-    <row r="64" spans="1:19">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A64" s="4"/>
       <c r="B64" s="5"/>
       <c r="C64" s="4"/>
@@ -1741,7 +1741,7 @@
       <c r="R64" s="4"/>
       <c r="S64" s="4"/>
     </row>
-    <row r="65" spans="1:19">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A65" s="4"/>
       <c r="B65" s="5"/>
       <c r="C65" s="4"/>
@@ -1762,7 +1762,7 @@
       <c r="R65" s="4"/>
       <c r="S65" s="4"/>
     </row>
-    <row r="66" spans="1:19">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A66" s="4"/>
       <c r="B66" s="5"/>
       <c r="C66" s="4"/>
@@ -1783,7 +1783,7 @@
       <c r="R66" s="4"/>
       <c r="S66" s="4"/>
     </row>
-    <row r="67" spans="1:19">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A67" s="4"/>
       <c r="B67" s="5"/>
       <c r="C67" s="4"/>
@@ -1804,7 +1804,7 @@
       <c r="R67" s="4"/>
       <c r="S67" s="4"/>
     </row>
-    <row r="68" spans="1:19">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A68" s="4"/>
       <c r="B68" s="5"/>
       <c r="C68" s="4"/>
@@ -1825,7 +1825,7 @@
       <c r="R68" s="4"/>
       <c r="S68" s="4"/>
     </row>
-    <row r="69" spans="1:19">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A69" s="4"/>
       <c r="B69" s="5"/>
       <c r="C69" s="4"/>
@@ -1846,7 +1846,7 @@
       <c r="R69" s="4"/>
       <c r="S69" s="4"/>
     </row>
-    <row r="70" spans="1:19">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A70" s="4"/>
       <c r="B70" s="5"/>
       <c r="C70" s="4"/>
@@ -1867,7 +1867,7 @@
       <c r="R70" s="4"/>
       <c r="S70" s="4"/>
     </row>
-    <row r="71" spans="1:19">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
       <c r="B71" s="5"/>
       <c r="C71" s="4"/>
@@ -1888,7 +1888,7 @@
       <c r="R71" s="4"/>
       <c r="S71" s="4"/>
     </row>
-    <row r="72" spans="1:19">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A72" s="4"/>
       <c r="B72" s="5"/>
       <c r="C72" s="4"/>
@@ -1909,7 +1909,7 @@
       <c r="R72" s="4"/>
       <c r="S72" s="4"/>
     </row>
-    <row r="73" spans="1:19">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A73" s="4"/>
       <c r="B73" s="5"/>
       <c r="C73" s="4"/>
@@ -1930,7 +1930,7 @@
       <c r="R73" s="4"/>
       <c r="S73" s="4"/>
     </row>
-    <row r="74" spans="1:19">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A74" s="4"/>
       <c r="B74" s="5"/>
       <c r="C74" s="4"/>
@@ -1951,7 +1951,7 @@
       <c r="R74" s="4"/>
       <c r="S74" s="4"/>
     </row>
-    <row r="75" spans="1:19">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A75" s="4"/>
       <c r="B75" s="5"/>
       <c r="C75" s="4"/>
@@ -1972,7 +1972,7 @@
       <c r="R75" s="4"/>
       <c r="S75" s="4"/>
     </row>
-    <row r="76" spans="1:19">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
       <c r="B76" s="5"/>
       <c r="C76" s="4"/>
@@ -1993,7 +1993,7 @@
       <c r="R76" s="4"/>
       <c r="S76" s="4"/>
     </row>
-    <row r="77" spans="1:19">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A77" s="4"/>
       <c r="B77" s="5"/>
       <c r="C77" s="4"/>
@@ -2014,7 +2014,7 @@
       <c r="R77" s="4"/>
       <c r="S77" s="4"/>
     </row>
-    <row r="78" spans="1:19">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A78" s="4"/>
       <c r="B78" s="5"/>
       <c r="C78" s="4"/>
@@ -2035,7 +2035,7 @@
       <c r="R78" s="4"/>
       <c r="S78" s="4"/>
     </row>
-    <row r="79" spans="1:19">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A79" s="4"/>
       <c r="B79" s="5"/>
       <c r="C79" s="4"/>
@@ -2056,7 +2056,7 @@
       <c r="R79" s="4"/>
       <c r="S79" s="4"/>
     </row>
-    <row r="80" spans="1:19">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
       <c r="B80" s="5"/>
       <c r="C80" s="4"/>
@@ -2077,7 +2077,7 @@
       <c r="R80" s="4"/>
       <c r="S80" s="4"/>
     </row>
-    <row r="81" spans="1:19">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A81" s="4"/>
       <c r="B81" s="5"/>
       <c r="C81" s="4"/>
@@ -2098,7 +2098,7 @@
       <c r="R81" s="4"/>
       <c r="S81" s="4"/>
     </row>
-    <row r="82" spans="1:19">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A82" s="4"/>
       <c r="B82" s="5"/>
       <c r="C82" s="4"/>
@@ -2119,7 +2119,7 @@
       <c r="R82" s="4"/>
       <c r="S82" s="4"/>
     </row>
-    <row r="83" spans="1:19">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A83" s="4"/>
       <c r="B83" s="5"/>
       <c r="C83" s="4"/>
@@ -2140,7 +2140,7 @@
       <c r="R83" s="4"/>
       <c r="S83" s="4"/>
     </row>
-    <row r="84" spans="1:19">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A84" s="4"/>
       <c r="B84" s="5"/>
       <c r="C84" s="4"/>
@@ -2161,7 +2161,7 @@
       <c r="R84" s="4"/>
       <c r="S84" s="4"/>
     </row>
-    <row r="85" spans="1:19">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A85" s="4"/>
       <c r="B85" s="5"/>
       <c r="C85" s="4"/>
@@ -2182,7 +2182,7 @@
       <c r="R85" s="4"/>
       <c r="S85" s="4"/>
     </row>
-    <row r="86" spans="1:19">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A86" s="4"/>
       <c r="B86" s="5"/>
       <c r="C86" s="4"/>
@@ -2203,7 +2203,7 @@
       <c r="R86" s="4"/>
       <c r="S86" s="4"/>
     </row>
-    <row r="87" spans="1:19">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A87" s="4"/>
       <c r="B87" s="5"/>
       <c r="C87" s="4"/>
@@ -2224,7 +2224,7 @@
       <c r="R87" s="4"/>
       <c r="S87" s="4"/>
     </row>
-    <row r="88" spans="1:19">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
       <c r="B88" s="5"/>
       <c r="C88" s="4"/>
@@ -2245,7 +2245,7 @@
       <c r="R88" s="4"/>
       <c r="S88" s="4"/>
     </row>
-    <row r="89" spans="1:19">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A89" s="4"/>
       <c r="B89" s="5"/>
       <c r="C89" s="4"/>
@@ -2266,7 +2266,7 @@
       <c r="R89" s="4"/>
       <c r="S89" s="4"/>
     </row>
-    <row r="90" spans="1:19">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A90" s="4"/>
       <c r="B90" s="5"/>
       <c r="C90" s="4"/>
@@ -2287,7 +2287,7 @@
       <c r="R90" s="4"/>
       <c r="S90" s="4"/>
     </row>
-    <row r="91" spans="1:19">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A91" s="4"/>
       <c r="B91" s="5"/>
       <c r="C91" s="4"/>
@@ -2308,7 +2308,7 @@
       <c r="R91" s="4"/>
       <c r="S91" s="4"/>
     </row>
-    <row r="92" spans="1:19">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A92" s="4"/>
       <c r="B92" s="5"/>
       <c r="C92" s="4"/>
@@ -2329,7 +2329,7 @@
       <c r="R92" s="4"/>
       <c r="S92" s="4"/>
     </row>
-    <row r="93" spans="1:19">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A93" s="4"/>
       <c r="B93" s="5"/>
       <c r="C93" s="4"/>
@@ -2350,7 +2350,7 @@
       <c r="R93" s="4"/>
       <c r="S93" s="4"/>
     </row>
-    <row r="94" spans="1:19">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A94" s="4"/>
       <c r="B94" s="5"/>
       <c r="C94" s="4"/>
@@ -2371,7 +2371,7 @@
       <c r="R94" s="4"/>
       <c r="S94" s="4"/>
     </row>
-    <row r="95" spans="1:19">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A95" s="4"/>
       <c r="B95" s="5"/>
       <c r="C95" s="4"/>
@@ -2392,7 +2392,7 @@
       <c r="R95" s="4"/>
       <c r="S95" s="4"/>
     </row>
-    <row r="96" spans="1:19">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A96" s="4"/>
       <c r="B96" s="5"/>
       <c r="C96" s="4"/>
@@ -2413,7 +2413,7 @@
       <c r="R96" s="4"/>
       <c r="S96" s="4"/>
     </row>
-    <row r="97" spans="1:19">
+    <row r="97" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A97" s="4"/>
       <c r="B97" s="5"/>
       <c r="C97" s="4"/>
@@ -2434,7 +2434,7 @@
       <c r="R97" s="4"/>
       <c r="S97" s="4"/>
     </row>
-    <row r="98" spans="1:19">
+    <row r="98" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A98" s="4"/>
       <c r="B98" s="5"/>
       <c r="C98" s="4"/>
@@ -2455,7 +2455,7 @@
       <c r="R98" s="4"/>
       <c r="S98" s="4"/>
     </row>
-    <row r="99" spans="1:19">
+    <row r="99" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A99" s="4"/>
       <c r="B99" s="5"/>
       <c r="C99" s="4"/>
@@ -2476,7 +2476,7 @@
       <c r="R99" s="4"/>
       <c r="S99" s="4"/>
     </row>
-    <row r="100" spans="1:19">
+    <row r="100" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A100" s="4"/>
       <c r="B100" s="5"/>
       <c r="C100" s="4"/>
@@ -2497,7 +2497,7 @@
       <c r="R100" s="4"/>
       <c r="S100" s="4"/>
     </row>
-    <row r="101" spans="1:19">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
       <c r="B101" s="5"/>
       <c r="C101" s="4"/>
@@ -2518,7 +2518,7 @@
       <c r="R101" s="4"/>
       <c r="S101" s="4"/>
     </row>
-    <row r="102" spans="1:19">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A102" s="4"/>
       <c r="B102" s="5"/>
       <c r="C102" s="4"/>
@@ -2539,7 +2539,7 @@
       <c r="R102" s="4"/>
       <c r="S102" s="4"/>
     </row>
-    <row r="103" spans="1:19">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A103" s="4"/>
       <c r="B103" s="5"/>
       <c r="C103" s="4"/>
@@ -2560,7 +2560,7 @@
       <c r="R103" s="4"/>
       <c r="S103" s="4"/>
     </row>
-    <row r="104" spans="1:19">
+    <row r="104" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A104" s="4"/>
       <c r="B104" s="5"/>
       <c r="C104" s="4"/>
@@ -2581,7 +2581,7 @@
       <c r="R104" s="4"/>
       <c r="S104" s="4"/>
     </row>
-    <row r="105" spans="1:19">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A105" s="4"/>
       <c r="B105" s="5"/>
       <c r="C105" s="4"/>
@@ -2602,7 +2602,7 @@
       <c r="R105" s="4"/>
       <c r="S105" s="4"/>
     </row>
-    <row r="106" spans="1:19">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A106" s="4"/>
       <c r="B106" s="5"/>
       <c r="C106" s="4"/>
@@ -2623,7 +2623,7 @@
       <c r="R106" s="4"/>
       <c r="S106" s="4"/>
     </row>
-    <row r="107" spans="1:19">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A107" s="4"/>
       <c r="B107" s="5"/>
       <c r="C107" s="4"/>
@@ -2644,7 +2644,7 @@
       <c r="R107" s="4"/>
       <c r="S107" s="4"/>
     </row>
-    <row r="108" spans="1:19">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A108" s="4"/>
       <c r="B108" s="5"/>
       <c r="C108" s="4"/>
@@ -2665,7 +2665,7 @@
       <c r="R108" s="4"/>
       <c r="S108" s="4"/>
     </row>
-    <row r="109" spans="1:19">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A109" s="4"/>
       <c r="B109" s="5"/>
       <c r="C109" s="4"/>
@@ -2686,7 +2686,7 @@
       <c r="R109" s="4"/>
       <c r="S109" s="4"/>
     </row>
-    <row r="110" spans="1:19">
+    <row r="110" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A110" s="4"/>
       <c r="B110" s="5"/>
       <c r="C110" s="4"/>
@@ -2707,7 +2707,7 @@
       <c r="R110" s="4"/>
       <c r="S110" s="4"/>
     </row>
-    <row r="111" spans="1:19">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A111" s="4"/>
       <c r="B111" s="5"/>
       <c r="C111" s="4"/>
@@ -2728,7 +2728,7 @@
       <c r="R111" s="4"/>
       <c r="S111" s="4"/>
     </row>
-    <row r="112" spans="1:19">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A112" s="4"/>
       <c r="B112" s="5"/>
       <c r="C112" s="4"/>
@@ -2749,7 +2749,7 @@
       <c r="R112" s="4"/>
       <c r="S112" s="4"/>
     </row>
-    <row r="113" spans="1:19">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A113" s="4"/>
       <c r="B113" s="5"/>
       <c r="C113" s="4"/>
@@ -2770,7 +2770,7 @@
       <c r="R113" s="4"/>
       <c r="S113" s="4"/>
     </row>
-    <row r="114" spans="1:19">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A114" s="4"/>
       <c r="B114" s="5"/>
       <c r="C114" s="4"/>
@@ -2791,7 +2791,7 @@
       <c r="R114" s="4"/>
       <c r="S114" s="4"/>
     </row>
-    <row r="115" spans="1:19">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A115" s="4"/>
       <c r="B115" s="5"/>
       <c r="C115" s="4"/>
@@ -2812,7 +2812,7 @@
       <c r="R115" s="4"/>
       <c r="S115" s="4"/>
     </row>
-    <row r="116" spans="1:19">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A116" s="4"/>
       <c r="B116" s="5"/>
       <c r="C116" s="4"/>
@@ -2833,7 +2833,7 @@
       <c r="R116" s="4"/>
       <c r="S116" s="4"/>
     </row>
-    <row r="117" spans="1:19">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A117" s="4"/>
       <c r="B117" s="5"/>
       <c r="C117" s="4"/>
@@ -2854,7 +2854,7 @@
       <c r="R117" s="4"/>
       <c r="S117" s="4"/>
     </row>
-    <row r="118" spans="1:19">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A118" s="4"/>
       <c r="B118" s="5"/>
       <c r="C118" s="4"/>
@@ -2875,7 +2875,7 @@
       <c r="R118" s="4"/>
       <c r="S118" s="4"/>
     </row>
-    <row r="119" spans="1:19">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A119" s="4"/>
       <c r="B119" s="5"/>
       <c r="C119" s="4"/>
@@ -2896,7 +2896,7 @@
       <c r="R119" s="4"/>
       <c r="S119" s="4"/>
     </row>
-    <row r="120" spans="1:19">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A120" s="4"/>
       <c r="B120" s="5"/>
       <c r="C120" s="4"/>
@@ -2917,7 +2917,7 @@
       <c r="R120" s="4"/>
       <c r="S120" s="4"/>
     </row>
-    <row r="121" spans="1:19">
+    <row r="121" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A121" s="4"/>
       <c r="B121" s="5"/>
       <c r="C121" s="4"/>
@@ -2938,7 +2938,7 @@
       <c r="R121" s="4"/>
       <c r="S121" s="4"/>
     </row>
-    <row r="122" spans="1:19">
+    <row r="122" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A122" s="4"/>
       <c r="B122" s="5"/>
       <c r="C122" s="4"/>
@@ -2959,7 +2959,7 @@
       <c r="R122" s="4"/>
       <c r="S122" s="4"/>
     </row>
-    <row r="123" spans="1:19">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A123" s="4"/>
       <c r="B123" s="5"/>
       <c r="C123" s="4"/>
@@ -2980,7 +2980,7 @@
       <c r="R123" s="4"/>
       <c r="S123" s="4"/>
     </row>
-    <row r="124" spans="1:19">
+    <row r="124" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A124" s="4"/>
       <c r="B124" s="5"/>
       <c r="C124" s="4"/>
@@ -3001,7 +3001,7 @@
       <c r="R124" s="4"/>
       <c r="S124" s="4"/>
     </row>
-    <row r="125" spans="1:19">
+    <row r="125" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A125" s="4"/>
       <c r="B125" s="5"/>
       <c r="C125" s="4"/>
@@ -3022,7 +3022,7 @@
       <c r="R125" s="4"/>
       <c r="S125" s="4"/>
     </row>
-    <row r="126" spans="1:19">
+    <row r="126" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A126" s="4"/>
       <c r="B126" s="5"/>
       <c r="C126" s="4"/>
@@ -3043,7 +3043,7 @@
       <c r="R126" s="4"/>
       <c r="S126" s="4"/>
     </row>
-    <row r="127" spans="1:19">
+    <row r="127" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A127" s="4"/>
       <c r="B127" s="5"/>
       <c r="C127" s="4"/>
@@ -3064,7 +3064,7 @@
       <c r="R127" s="4"/>
       <c r="S127" s="4"/>
     </row>
-    <row r="128" spans="1:19">
+    <row r="128" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A128" s="4"/>
       <c r="B128" s="5"/>
       <c r="C128" s="4"/>
@@ -3085,7 +3085,7 @@
       <c r="R128" s="4"/>
       <c r="S128" s="4"/>
     </row>
-    <row r="129" spans="1:19">
+    <row r="129" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A129" s="4"/>
       <c r="B129" s="5"/>
       <c r="C129" s="4"/>
@@ -3106,7 +3106,7 @@
       <c r="R129" s="4"/>
       <c r="S129" s="4"/>
     </row>
-    <row r="130" spans="1:19">
+    <row r="130" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A130" s="4"/>
       <c r="B130" s="5"/>
       <c r="C130" s="4"/>
@@ -3127,7 +3127,7 @@
       <c r="R130" s="4"/>
       <c r="S130" s="4"/>
     </row>
-    <row r="131" spans="1:19">
+    <row r="131" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A131" s="4"/>
       <c r="B131" s="5"/>
       <c r="C131" s="4"/>
@@ -3148,7 +3148,7 @@
       <c r="R131" s="4"/>
       <c r="S131" s="4"/>
     </row>
-    <row r="132" spans="1:19">
+    <row r="132" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A132" s="4"/>
       <c r="B132" s="5"/>
       <c r="C132" s="4"/>
@@ -3169,7 +3169,7 @@
       <c r="R132" s="4"/>
       <c r="S132" s="4"/>
     </row>
-    <row r="133" spans="1:19">
+    <row r="133" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A133" s="4"/>
       <c r="B133" s="5"/>
       <c r="C133" s="4"/>
@@ -3190,7 +3190,7 @@
       <c r="R133" s="4"/>
       <c r="S133" s="4"/>
     </row>
-    <row r="134" spans="1:19">
+    <row r="134" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A134" s="4"/>
       <c r="B134" s="5"/>
       <c r="C134" s="4"/>
@@ -3211,7 +3211,7 @@
       <c r="R134" s="4"/>
       <c r="S134" s="4"/>
     </row>
-    <row r="135" spans="1:19">
+    <row r="135" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A135" s="4"/>
       <c r="B135" s="5"/>
       <c r="C135" s="4"/>
@@ -3232,7 +3232,7 @@
       <c r="R135" s="4"/>
       <c r="S135" s="4"/>
     </row>
-    <row r="136" spans="1:19">
+    <row r="136" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A136" s="4"/>
       <c r="B136" s="5"/>
       <c r="C136" s="4"/>
@@ -3253,7 +3253,7 @@
       <c r="R136" s="4"/>
       <c r="S136" s="4"/>
     </row>
-    <row r="137" spans="1:19">
+    <row r="137" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A137" s="4"/>
       <c r="B137" s="5"/>
       <c r="C137" s="4"/>
@@ -3274,7 +3274,7 @@
       <c r="R137" s="4"/>
       <c r="S137" s="4"/>
     </row>
-    <row r="138" spans="1:19">
+    <row r="138" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A138" s="4"/>
       <c r="B138" s="5"/>
       <c r="C138" s="4"/>
@@ -3295,7 +3295,7 @@
       <c r="R138" s="4"/>
       <c r="S138" s="4"/>
     </row>
-    <row r="139" spans="1:19">
+    <row r="139" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A139" s="4"/>
       <c r="B139" s="5"/>
       <c r="C139" s="4"/>
@@ -3316,7 +3316,7 @@
       <c r="R139" s="4"/>
       <c r="S139" s="4"/>
     </row>
-    <row r="140" spans="1:19">
+    <row r="140" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A140" s="4"/>
       <c r="B140" s="5"/>
       <c r="C140" s="4"/>
@@ -3337,7 +3337,7 @@
       <c r="R140" s="4"/>
       <c r="S140" s="4"/>
     </row>
-    <row r="141" spans="1:19">
+    <row r="141" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A141" s="4"/>
       <c r="B141" s="5"/>
       <c r="C141" s="4"/>
@@ -3358,7 +3358,7 @@
       <c r="R141" s="4"/>
       <c r="S141" s="4"/>
     </row>
-    <row r="142" spans="1:19">
+    <row r="142" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A142" s="4"/>
       <c r="B142" s="5"/>
       <c r="C142" s="4"/>
@@ -3379,7 +3379,7 @@
       <c r="R142" s="4"/>
       <c r="S142" s="4"/>
     </row>
-    <row r="143" spans="1:19">
+    <row r="143" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A143" s="4"/>
       <c r="B143" s="5"/>
       <c r="C143" s="4"/>
@@ -3400,7 +3400,7 @@
       <c r="R143" s="4"/>
       <c r="S143" s="4"/>
     </row>
-    <row r="144" spans="1:19">
+    <row r="144" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A144" s="4"/>
       <c r="B144" s="5"/>
       <c r="C144" s="4"/>
@@ -3421,7 +3421,7 @@
       <c r="R144" s="4"/>
       <c r="S144" s="4"/>
     </row>
-    <row r="145" spans="1:19">
+    <row r="145" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A145" s="4"/>
       <c r="B145" s="5"/>
       <c r="C145" s="4"/>
@@ -3442,7 +3442,7 @@
       <c r="R145" s="4"/>
       <c r="S145" s="4"/>
     </row>
-    <row r="146" spans="1:19">
+    <row r="146" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A146" s="4"/>
       <c r="B146" s="5"/>
       <c r="C146" s="4"/>
@@ -3463,7 +3463,7 @@
       <c r="R146" s="4"/>
       <c r="S146" s="4"/>
     </row>
-    <row r="147" spans="1:19">
+    <row r="147" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A147" s="4"/>
       <c r="B147" s="5"/>
       <c r="C147" s="4"/>
@@ -3484,7 +3484,7 @@
       <c r="R147" s="4"/>
       <c r="S147" s="4"/>
     </row>
-    <row r="148" spans="1:19">
+    <row r="148" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A148" s="4"/>
       <c r="B148" s="5"/>
       <c r="C148" s="4"/>
@@ -3505,7 +3505,7 @@
       <c r="R148" s="4"/>
       <c r="S148" s="4"/>
     </row>
-    <row r="149" spans="1:19">
+    <row r="149" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A149" s="4"/>
       <c r="B149" s="5"/>
       <c r="C149" s="4"/>
@@ -3526,7 +3526,7 @@
       <c r="R149" s="4"/>
       <c r="S149" s="4"/>
     </row>
-    <row r="150" spans="1:19">
+    <row r="150" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A150" s="4"/>
       <c r="B150" s="5"/>
       <c r="C150" s="4"/>
@@ -3547,7 +3547,7 @@
       <c r="R150" s="4"/>
       <c r="S150" s="4"/>
     </row>
-    <row r="151" spans="1:19">
+    <row r="151" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A151" s="4"/>
       <c r="B151" s="5"/>
       <c r="C151" s="4"/>
@@ -3568,7 +3568,7 @@
       <c r="R151" s="4"/>
       <c r="S151" s="4"/>
     </row>
-    <row r="152" spans="1:19">
+    <row r="152" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A152" s="4"/>
       <c r="B152" s="5"/>
       <c r="C152" s="4"/>
@@ -3589,7 +3589,7 @@
       <c r="R152" s="4"/>
       <c r="S152" s="4"/>
     </row>
-    <row r="153" spans="1:19">
+    <row r="153" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A153" s="4"/>
       <c r="B153" s="5"/>
       <c r="C153" s="4"/>
@@ -3610,7 +3610,7 @@
       <c r="R153" s="4"/>
       <c r="S153" s="4"/>
     </row>
-    <row r="154" spans="1:19">
+    <row r="154" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A154" s="4"/>
       <c r="B154" s="5"/>
       <c r="C154" s="4"/>
@@ -3631,7 +3631,7 @@
       <c r="R154" s="4"/>
       <c r="S154" s="4"/>
     </row>
-    <row r="155" spans="1:19">
+    <row r="155" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A155" s="4"/>
       <c r="B155" s="5"/>
       <c r="C155" s="4"/>
@@ -3652,7 +3652,7 @@
       <c r="R155" s="4"/>
       <c r="S155" s="4"/>
     </row>
-    <row r="156" spans="1:19">
+    <row r="156" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A156" s="4"/>
       <c r="B156" s="5"/>
       <c r="C156" s="4"/>
@@ -3673,7 +3673,7 @@
       <c r="R156" s="4"/>
       <c r="S156" s="4"/>
     </row>
-    <row r="157" spans="1:19">
+    <row r="157" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A157" s="4"/>
       <c r="B157" s="5"/>
       <c r="C157" s="4"/>
@@ -3694,7 +3694,7 @@
       <c r="R157" s="4"/>
       <c r="S157" s="4"/>
     </row>
-    <row r="158" spans="1:19">
+    <row r="158" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A158" s="4"/>
       <c r="B158" s="5"/>
       <c r="C158" s="4"/>
@@ -3715,7 +3715,7 @@
       <c r="R158" s="4"/>
       <c r="S158" s="4"/>
     </row>
-    <row r="159" spans="1:19">
+    <row r="159" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A159" s="4"/>
       <c r="B159" s="5"/>
       <c r="C159" s="4"/>
@@ -3736,7 +3736,7 @@
       <c r="R159" s="4"/>
       <c r="S159" s="4"/>
     </row>
-    <row r="160" spans="1:19">
+    <row r="160" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A160" s="4"/>
       <c r="B160" s="5"/>
       <c r="C160" s="4"/>
@@ -3757,7 +3757,7 @@
       <c r="R160" s="4"/>
       <c r="S160" s="4"/>
     </row>
-    <row r="161" spans="1:19">
+    <row r="161" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A161" s="4"/>
       <c r="B161" s="5"/>
       <c r="C161" s="4"/>
@@ -3778,7 +3778,7 @@
       <c r="R161" s="4"/>
       <c r="S161" s="4"/>
     </row>
-    <row r="162" spans="1:19">
+    <row r="162" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A162" s="4"/>
       <c r="B162" s="5"/>
       <c r="C162" s="4"/>
@@ -3799,7 +3799,7 @@
       <c r="R162" s="4"/>
       <c r="S162" s="4"/>
     </row>
-    <row r="163" spans="1:19">
+    <row r="163" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A163" s="4"/>
       <c r="B163" s="5"/>
       <c r="C163" s="4"/>
@@ -3820,7 +3820,7 @@
       <c r="R163" s="4"/>
       <c r="S163" s="4"/>
     </row>
-    <row r="164" spans="1:19">
+    <row r="164" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A164" s="4"/>
       <c r="B164" s="5"/>
       <c r="C164" s="4"/>
@@ -3841,7 +3841,7 @@
       <c r="R164" s="4"/>
       <c r="S164" s="4"/>
     </row>
-    <row r="165" spans="1:19">
+    <row r="165" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A165" s="4"/>
       <c r="B165" s="5"/>
       <c r="C165" s="4"/>
@@ -3862,7 +3862,7 @@
       <c r="R165" s="4"/>
       <c r="S165" s="4"/>
     </row>
-    <row r="166" spans="1:19">
+    <row r="166" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A166" s="4"/>
       <c r="B166" s="5"/>
       <c r="C166" s="4"/>
@@ -3883,7 +3883,7 @@
       <c r="R166" s="4"/>
       <c r="S166" s="4"/>
     </row>
-    <row r="167" spans="1:19">
+    <row r="167" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A167" s="4"/>
       <c r="B167" s="5"/>
       <c r="C167" s="4"/>
@@ -3904,7 +3904,7 @@
       <c r="R167" s="4"/>
       <c r="S167" s="4"/>
     </row>
-    <row r="168" spans="1:19">
+    <row r="168" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A168" s="4"/>
       <c r="B168" s="5"/>
       <c r="C168" s="4"/>
@@ -3925,7 +3925,7 @@
       <c r="R168" s="4"/>
       <c r="S168" s="4"/>
     </row>
-    <row r="169" spans="1:19">
+    <row r="169" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A169" s="4"/>
       <c r="B169" s="5"/>
       <c r="C169" s="4"/>
@@ -3946,7 +3946,7 @@
       <c r="R169" s="4"/>
       <c r="S169" s="4"/>
     </row>
-    <row r="170" spans="1:19">
+    <row r="170" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A170" s="4"/>
       <c r="B170" s="5"/>
       <c r="C170" s="4"/>
@@ -3967,7 +3967,7 @@
       <c r="R170" s="4"/>
       <c r="S170" s="4"/>
     </row>
-    <row r="171" spans="1:19">
+    <row r="171" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A171" s="4"/>
       <c r="B171" s="5"/>
       <c r="C171" s="4"/>
@@ -3988,7 +3988,7 @@
       <c r="R171" s="4"/>
       <c r="S171" s="4"/>
     </row>
-    <row r="172" spans="1:19">
+    <row r="172" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A172" s="4"/>
       <c r="B172" s="5"/>
       <c r="C172" s="4"/>
@@ -4009,7 +4009,7 @@
       <c r="R172" s="4"/>
       <c r="S172" s="4"/>
     </row>
-    <row r="173" spans="1:19">
+    <row r="173" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A173" s="4"/>
       <c r="B173" s="5"/>
       <c r="C173" s="4"/>
@@ -4030,7 +4030,7 @@
       <c r="R173" s="4"/>
       <c r="S173" s="4"/>
     </row>
-    <row r="174" spans="1:19">
+    <row r="174" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A174" s="4"/>
       <c r="B174" s="5"/>
       <c r="C174" s="4"/>
@@ -4051,7 +4051,7 @@
       <c r="R174" s="4"/>
       <c r="S174" s="4"/>
     </row>
-    <row r="175" spans="1:19">
+    <row r="175" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A175" s="4"/>
       <c r="B175" s="5"/>
       <c r="C175" s="4"/>
@@ -4072,7 +4072,7 @@
       <c r="R175" s="4"/>
       <c r="S175" s="4"/>
     </row>
-    <row r="176" spans="1:19">
+    <row r="176" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A176" s="4"/>
       <c r="B176" s="5"/>
       <c r="C176" s="4"/>
@@ -4093,7 +4093,7 @@
       <c r="R176" s="4"/>
       <c r="S176" s="4"/>
     </row>
-    <row r="177" spans="1:19">
+    <row r="177" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A177" s="4"/>
       <c r="B177" s="5"/>
       <c r="C177" s="4"/>
@@ -4114,7 +4114,7 @@
       <c r="R177" s="4"/>
       <c r="S177" s="4"/>
     </row>
-    <row r="178" spans="1:19">
+    <row r="178" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A178" s="4"/>
       <c r="B178" s="5"/>
       <c r="C178" s="4"/>
@@ -4135,7 +4135,7 @@
       <c r="R178" s="4"/>
       <c r="S178" s="4"/>
     </row>
-    <row r="179" spans="1:19">
+    <row r="179" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A179" s="4"/>
       <c r="B179" s="5"/>
       <c r="C179" s="4"/>
@@ -4156,7 +4156,7 @@
       <c r="R179" s="4"/>
       <c r="S179" s="4"/>
     </row>
-    <row r="180" spans="1:19">
+    <row r="180" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A180" s="4"/>
       <c r="B180" s="5"/>
       <c r="C180" s="4"/>
@@ -4177,7 +4177,7 @@
       <c r="R180" s="4"/>
       <c r="S180" s="4"/>
     </row>
-    <row r="181" spans="1:19">
+    <row r="181" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A181" s="4"/>
       <c r="B181" s="5"/>
       <c r="C181" s="4"/>
@@ -4198,7 +4198,7 @@
       <c r="R181" s="4"/>
       <c r="S181" s="4"/>
     </row>
-    <row r="182" spans="1:19">
+    <row r="182" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A182" s="4"/>
       <c r="B182" s="5"/>
       <c r="C182" s="4"/>
@@ -4219,7 +4219,7 @@
       <c r="R182" s="4"/>
       <c r="S182" s="4"/>
     </row>
-    <row r="183" spans="1:19">
+    <row r="183" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A183" s="4"/>
       <c r="B183" s="5"/>
       <c r="C183" s="4"/>
@@ -4240,7 +4240,7 @@
       <c r="R183" s="4"/>
       <c r="S183" s="4"/>
     </row>
-    <row r="184" spans="1:19">
+    <row r="184" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A184" s="4"/>
       <c r="B184" s="5"/>
       <c r="C184" s="4"/>
@@ -4261,7 +4261,7 @@
       <c r="R184" s="4"/>
       <c r="S184" s="4"/>
     </row>
-    <row r="185" spans="1:19">
+    <row r="185" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A185" s="4"/>
       <c r="B185" s="5"/>
       <c r="C185" s="4"/>
@@ -4282,7 +4282,7 @@
       <c r="R185" s="4"/>
       <c r="S185" s="4"/>
     </row>
-    <row r="186" spans="1:19">
+    <row r="186" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A186" s="4"/>
       <c r="B186" s="5"/>
       <c r="C186" s="4"/>
@@ -4303,7 +4303,7 @@
       <c r="R186" s="4"/>
       <c r="S186" s="4"/>
     </row>
-    <row r="187" spans="1:19">
+    <row r="187" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A187" s="4"/>
       <c r="B187" s="5"/>
       <c r="C187" s="4"/>
@@ -4324,7 +4324,7 @@
       <c r="R187" s="4"/>
       <c r="S187" s="4"/>
     </row>
-    <row r="188" spans="1:19">
+    <row r="188" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A188" s="4"/>
       <c r="B188" s="5"/>
       <c r="C188" s="4"/>
@@ -4345,7 +4345,7 @@
       <c r="R188" s="4"/>
       <c r="S188" s="4"/>
     </row>
-    <row r="189" spans="1:19">
+    <row r="189" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A189" s="4"/>
       <c r="B189" s="5"/>
       <c r="C189" s="4"/>
@@ -4366,7 +4366,7 @@
       <c r="R189" s="4"/>
       <c r="S189" s="4"/>
     </row>
-    <row r="190" spans="1:19">
+    <row r="190" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A190" s="4"/>
       <c r="B190" s="5"/>
       <c r="C190" s="4"/>
@@ -4387,7 +4387,7 @@
       <c r="R190" s="4"/>
       <c r="S190" s="4"/>
     </row>
-    <row r="191" spans="1:19">
+    <row r="191" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A191" s="4"/>
       <c r="B191" s="5"/>
       <c r="C191" s="4"/>
@@ -4408,7 +4408,7 @@
       <c r="R191" s="4"/>
       <c r="S191" s="4"/>
     </row>
-    <row r="192" spans="1:19">
+    <row r="192" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A192" s="4"/>
       <c r="B192" s="5"/>
       <c r="C192" s="4"/>
@@ -4429,7 +4429,7 @@
       <c r="R192" s="4"/>
       <c r="S192" s="4"/>
     </row>
-    <row r="193" spans="1:19">
+    <row r="193" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A193" s="4"/>
       <c r="B193" s="5"/>
       <c r="C193" s="4"/>
@@ -4450,7 +4450,7 @@
       <c r="R193" s="4"/>
       <c r="S193" s="4"/>
     </row>
-    <row r="194" spans="1:19">
+    <row r="194" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A194" s="4"/>
       <c r="B194" s="5"/>
       <c r="C194" s="4"/>
@@ -4471,7 +4471,7 @@
       <c r="R194" s="4"/>
       <c r="S194" s="4"/>
     </row>
-    <row r="195" spans="1:19">
+    <row r="195" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A195" s="4"/>
       <c r="B195" s="5"/>
       <c r="C195" s="4"/>
@@ -4492,7 +4492,7 @@
       <c r="R195" s="4"/>
       <c r="S195" s="4"/>
     </row>
-    <row r="196" spans="1:19">
+    <row r="196" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A196" s="4"/>
       <c r="B196" s="5"/>
       <c r="C196" s="4"/>
@@ -4513,7 +4513,7 @@
       <c r="R196" s="4"/>
       <c r="S196" s="4"/>
     </row>
-    <row r="197" spans="1:19">
+    <row r="197" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A197" s="4"/>
       <c r="B197" s="5"/>
       <c r="C197" s="4"/>
@@ -4534,7 +4534,7 @@
       <c r="R197" s="4"/>
       <c r="S197" s="4"/>
     </row>
-    <row r="198" spans="1:19">
+    <row r="198" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A198" s="4"/>
       <c r="B198" s="5"/>
       <c r="C198" s="4"/>
@@ -4555,7 +4555,7 @@
       <c r="R198" s="4"/>
       <c r="S198" s="4"/>
     </row>
-    <row r="199" spans="1:19">
+    <row r="199" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A199" s="4"/>
       <c r="B199" s="5"/>
       <c r="C199" s="4"/>
@@ -4576,7 +4576,7 @@
       <c r="R199" s="4"/>
       <c r="S199" s="4"/>
     </row>
-    <row r="200" spans="1:19">
+    <row r="200" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A200" s="4"/>
       <c r="B200" s="5"/>
       <c r="C200" s="4"/>
@@ -4597,7 +4597,7 @@
       <c r="R200" s="4"/>
       <c r="S200" s="4"/>
     </row>
-    <row r="201" spans="1:19">
+    <row r="201" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A201" s="4"/>
       <c r="B201" s="5"/>
       <c r="C201" s="4"/>
@@ -4618,7 +4618,7 @@
       <c r="R201" s="4"/>
       <c r="S201" s="4"/>
     </row>
-    <row r="202" spans="1:19">
+    <row r="202" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A202" s="4"/>
       <c r="B202" s="5"/>
       <c r="C202" s="4"/>
@@ -4639,7 +4639,7 @@
       <c r="R202" s="4"/>
       <c r="S202" s="4"/>
     </row>
-    <row r="203" spans="1:19">
+    <row r="203" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A203" s="4"/>
       <c r="B203" s="5"/>
       <c r="C203" s="4"/>
@@ -4660,7 +4660,7 @@
       <c r="R203" s="4"/>
       <c r="S203" s="4"/>
     </row>
-    <row r="204" spans="1:19">
+    <row r="204" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A204" s="4"/>
       <c r="B204" s="5"/>
       <c r="C204" s="4"/>
@@ -4681,7 +4681,7 @@
       <c r="R204" s="4"/>
       <c r="S204" s="4"/>
     </row>
-    <row r="205" spans="1:19">
+    <row r="205" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A205" s="4"/>
       <c r="B205" s="5"/>
       <c r="C205" s="4"/>
@@ -4702,7 +4702,7 @@
       <c r="R205" s="4"/>
       <c r="S205" s="4"/>
     </row>
-    <row r="206" spans="1:19">
+    <row r="206" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A206" s="4"/>
       <c r="B206" s="5"/>
       <c r="C206" s="4"/>
@@ -4723,7 +4723,7 @@
       <c r="R206" s="4"/>
       <c r="S206" s="4"/>
     </row>
-    <row r="207" spans="1:19">
+    <row r="207" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A207" s="4"/>
       <c r="B207" s="5"/>
       <c r="C207" s="4"/>
@@ -4744,7 +4744,7 @@
       <c r="R207" s="4"/>
       <c r="S207" s="4"/>
     </row>
-    <row r="208" spans="1:19">
+    <row r="208" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A208" s="4"/>
       <c r="B208" s="5"/>
       <c r="C208" s="4"/>
@@ -4765,7 +4765,7 @@
       <c r="R208" s="4"/>
       <c r="S208" s="4"/>
     </row>
-    <row r="209" spans="1:19">
+    <row r="209" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A209" s="4"/>
       <c r="B209" s="5"/>
       <c r="C209" s="4"/>
@@ -4786,7 +4786,7 @@
       <c r="R209" s="4"/>
       <c r="S209" s="4"/>
     </row>
-    <row r="210" spans="1:19">
+    <row r="210" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A210" s="4"/>
       <c r="B210" s="5"/>
       <c r="C210" s="4"/>
@@ -4807,7 +4807,7 @@
       <c r="R210" s="4"/>
       <c r="S210" s="4"/>
     </row>
-    <row r="211" spans="1:19">
+    <row r="211" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A211" s="4"/>
       <c r="B211" s="5"/>
       <c r="C211" s="4"/>
@@ -4828,7 +4828,7 @@
       <c r="R211" s="4"/>
       <c r="S211" s="4"/>
     </row>
-    <row r="212" spans="1:19">
+    <row r="212" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A212" s="4"/>
       <c r="B212" s="5"/>
       <c r="C212" s="4"/>
@@ -4849,7 +4849,7 @@
       <c r="R212" s="4"/>
       <c r="S212" s="4"/>
     </row>
-    <row r="213" spans="1:19">
+    <row r="213" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A213" s="4"/>
       <c r="B213" s="5"/>
       <c r="C213" s="4"/>
@@ -4870,7 +4870,7 @@
       <c r="R213" s="4"/>
       <c r="S213" s="4"/>
     </row>
-    <row r="214" spans="1:19">
+    <row r="214" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A214" s="4"/>
       <c r="B214" s="5"/>
       <c r="C214" s="4"/>
@@ -4891,7 +4891,7 @@
       <c r="R214" s="4"/>
       <c r="S214" s="4"/>
     </row>
-    <row r="215" spans="1:19">
+    <row r="215" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A215" s="4"/>
       <c r="B215" s="5"/>
       <c r="C215" s="4"/>
@@ -4912,7 +4912,7 @@
       <c r="R215" s="4"/>
       <c r="S215" s="4"/>
     </row>
-    <row r="216" spans="1:19">
+    <row r="216" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A216" s="4"/>
       <c r="B216" s="5"/>
       <c r="C216" s="4"/>
@@ -4933,7 +4933,7 @@
       <c r="R216" s="4"/>
       <c r="S216" s="4"/>
     </row>
-    <row r="217" spans="1:19">
+    <row r="217" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A217" s="4"/>
       <c r="B217" s="5"/>
       <c r="C217" s="4"/>
@@ -4954,7 +4954,7 @@
       <c r="R217" s="4"/>
       <c r="S217" s="4"/>
     </row>
-    <row r="218" spans="1:19">
+    <row r="218" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A218" s="4"/>
       <c r="B218" s="5"/>
       <c r="C218" s="4"/>
@@ -4975,7 +4975,7 @@
       <c r="R218" s="4"/>
       <c r="S218" s="4"/>
     </row>
-    <row r="219" spans="1:19">
+    <row r="219" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A219" s="4"/>
       <c r="B219" s="5"/>
       <c r="C219" s="4"/>
@@ -4996,7 +4996,7 @@
       <c r="R219" s="4"/>
       <c r="S219" s="4"/>
     </row>
-    <row r="220" spans="1:19">
+    <row r="220" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A220" s="4"/>
       <c r="B220" s="5"/>
       <c r="C220" s="4"/>
@@ -5017,7 +5017,7 @@
       <c r="R220" s="4"/>
       <c r="S220" s="4"/>
     </row>
-    <row r="221" spans="1:19">
+    <row r="221" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A221" s="4"/>
       <c r="B221" s="5"/>
       <c r="C221" s="4"/>
@@ -5038,7 +5038,7 @@
       <c r="R221" s="4"/>
       <c r="S221" s="4"/>
     </row>
-    <row r="222" spans="1:19">
+    <row r="222" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A222" s="4"/>
       <c r="B222" s="5"/>
       <c r="C222" s="4"/>
@@ -5059,7 +5059,7 @@
       <c r="R222" s="4"/>
       <c r="S222" s="4"/>
     </row>
-    <row r="223" spans="1:19">
+    <row r="223" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A223" s="4"/>
       <c r="B223" s="5"/>
       <c r="C223" s="4"/>
@@ -5080,7 +5080,7 @@
       <c r="R223" s="4"/>
       <c r="S223" s="4"/>
     </row>
-    <row r="224" spans="1:19">
+    <row r="224" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A224" s="4"/>
       <c r="B224" s="5"/>
       <c r="C224" s="4"/>
@@ -5101,7 +5101,7 @@
       <c r="R224" s="4"/>
       <c r="S224" s="4"/>
     </row>
-    <row r="225" spans="1:19">
+    <row r="225" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A225" s="4"/>
       <c r="B225" s="5"/>
       <c r="C225" s="4"/>
@@ -5122,7 +5122,7 @@
       <c r="R225" s="4"/>
       <c r="S225" s="4"/>
     </row>
-    <row r="226" spans="1:19">
+    <row r="226" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A226" s="4"/>
       <c r="B226" s="5"/>
       <c r="C226" s="4"/>
@@ -5143,7 +5143,7 @@
       <c r="R226" s="4"/>
       <c r="S226" s="4"/>
     </row>
-    <row r="227" spans="1:19">
+    <row r="227" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A227" s="4"/>
       <c r="B227" s="5"/>
       <c r="C227" s="4"/>
@@ -5164,7 +5164,7 @@
       <c r="R227" s="4"/>
       <c r="S227" s="4"/>
     </row>
-    <row r="228" spans="1:19">
+    <row r="228" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A228" s="4"/>
       <c r="B228" s="5"/>
       <c r="C228" s="4"/>
@@ -5185,7 +5185,7 @@
       <c r="R228" s="4"/>
       <c r="S228" s="4"/>
     </row>
-    <row r="229" spans="1:19">
+    <row r="229" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A229" s="4"/>
       <c r="B229" s="5"/>
       <c r="C229" s="4"/>
@@ -5206,7 +5206,7 @@
       <c r="R229" s="4"/>
       <c r="S229" s="4"/>
     </row>
-    <row r="230" spans="1:19">
+    <row r="230" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A230" s="4"/>
       <c r="B230" s="5"/>
       <c r="C230" s="4"/>
@@ -5227,7 +5227,7 @@
       <c r="R230" s="4"/>
       <c r="S230" s="4"/>
     </row>
-    <row r="231" spans="1:19">
+    <row r="231" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A231" s="4"/>
       <c r="B231" s="5"/>
       <c r="C231" s="4"/>
@@ -5248,7 +5248,7 @@
       <c r="R231" s="4"/>
       <c r="S231" s="4"/>
     </row>
-    <row r="232" spans="1:19">
+    <row r="232" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A232" s="4"/>
       <c r="B232" s="5"/>
       <c r="C232" s="4"/>
@@ -5269,7 +5269,7 @@
       <c r="R232" s="4"/>
       <c r="S232" s="4"/>
     </row>
-    <row r="233" spans="1:19">
+    <row r="233" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A233" s="4"/>
       <c r="B233" s="5"/>
       <c r="C233" s="4"/>
@@ -5290,7 +5290,7 @@
       <c r="R233" s="4"/>
       <c r="S233" s="4"/>
     </row>
-    <row r="234" spans="1:19">
+    <row r="234" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A234" s="4"/>
       <c r="B234" s="5"/>
       <c r="C234" s="4"/>
@@ -5311,7 +5311,7 @@
       <c r="R234" s="4"/>
       <c r="S234" s="4"/>
     </row>
-    <row r="235" spans="1:19">
+    <row r="235" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A235" s="4"/>
       <c r="B235" s="5"/>
       <c r="C235" s="4"/>
@@ -5332,7 +5332,7 @@
       <c r="R235" s="4"/>
       <c r="S235" s="4"/>
     </row>
-    <row r="236" spans="1:19">
+    <row r="236" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A236" s="4"/>
       <c r="B236" s="5"/>
       <c r="C236" s="4"/>
@@ -5353,7 +5353,7 @@
       <c r="R236" s="4"/>
       <c r="S236" s="4"/>
     </row>
-    <row r="237" spans="1:19">
+    <row r="237" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A237" s="4"/>
       <c r="B237" s="5"/>
       <c r="C237" s="4"/>
@@ -5374,7 +5374,7 @@
       <c r="R237" s="4"/>
       <c r="S237" s="4"/>
     </row>
-    <row r="238" spans="1:19">
+    <row r="238" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A238" s="4"/>
       <c r="B238" s="5"/>
       <c r="C238" s="4"/>
@@ -5395,7 +5395,7 @@
       <c r="R238" s="4"/>
       <c r="S238" s="4"/>
     </row>
-    <row r="239" spans="1:19">
+    <row r="239" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A239" s="4"/>
       <c r="B239" s="5"/>
       <c r="C239" s="4"/>
@@ -5416,7 +5416,7 @@
       <c r="R239" s="4"/>
       <c r="S239" s="4"/>
     </row>
-    <row r="240" spans="1:19">
+    <row r="240" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A240" s="4"/>
       <c r="B240" s="5"/>
       <c r="C240" s="4"/>
@@ -5437,7 +5437,7 @@
       <c r="R240" s="4"/>
       <c r="S240" s="4"/>
     </row>
-    <row r="241" spans="1:19">
+    <row r="241" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A241" s="4"/>
       <c r="B241" s="5"/>
       <c r="C241" s="4"/>
@@ -5458,7 +5458,7 @@
       <c r="R241" s="4"/>
       <c r="S241" s="4"/>
     </row>
-    <row r="242" spans="1:19">
+    <row r="242" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A242" s="4"/>
       <c r="B242" s="5"/>
       <c r="C242" s="4"/>
@@ -5479,7 +5479,7 @@
       <c r="R242" s="4"/>
       <c r="S242" s="4"/>
     </row>
-    <row r="243" spans="1:19">
+    <row r="243" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A243" s="4"/>
       <c r="B243" s="5"/>
       <c r="C243" s="4"/>
@@ -5500,7 +5500,7 @@
       <c r="R243" s="4"/>
       <c r="S243" s="4"/>
     </row>
-    <row r="244" spans="1:19">
+    <row r="244" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A244" s="4"/>
       <c r="B244" s="5"/>
       <c r="C244" s="4"/>
@@ -5521,7 +5521,7 @@
       <c r="R244" s="4"/>
       <c r="S244" s="4"/>
     </row>
-    <row r="245" spans="1:19">
+    <row r="245" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A245" s="4"/>
       <c r="B245" s="5"/>
       <c r="C245" s="4"/>
@@ -5542,7 +5542,7 @@
       <c r="R245" s="4"/>
       <c r="S245" s="4"/>
     </row>
-    <row r="246" spans="1:19">
+    <row r="246" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A246" s="4"/>
       <c r="B246" s="5"/>
       <c r="C246" s="4"/>
@@ -5563,7 +5563,7 @@
       <c r="R246" s="4"/>
       <c r="S246" s="4"/>
     </row>
-    <row r="247" spans="1:19">
+    <row r="247" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A247" s="4"/>
       <c r="B247" s="5"/>
       <c r="C247" s="4"/>
@@ -5584,7 +5584,7 @@
       <c r="R247" s="4"/>
       <c r="S247" s="4"/>
     </row>
-    <row r="248" spans="1:19">
+    <row r="248" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A248" s="4"/>
       <c r="B248" s="5"/>
       <c r="C248" s="4"/>
@@ -5605,7 +5605,7 @@
       <c r="R248" s="4"/>
       <c r="S248" s="4"/>
     </row>
-    <row r="249" spans="1:19">
+    <row r="249" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A249" s="4"/>
       <c r="B249" s="5"/>
       <c r="C249" s="4"/>
@@ -5626,7 +5626,7 @@
       <c r="R249" s="4"/>
       <c r="S249" s="4"/>
     </row>
-    <row r="250" spans="1:19">
+    <row r="250" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A250" s="4"/>
       <c r="B250" s="5"/>
       <c r="C250" s="4"/>
@@ -5647,7 +5647,7 @@
       <c r="R250" s="4"/>
       <c r="S250" s="4"/>
     </row>
-    <row r="251" spans="1:19">
+    <row r="251" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A251" s="4"/>
       <c r="B251" s="5"/>
       <c r="C251" s="4"/>
@@ -5668,7 +5668,7 @@
       <c r="R251" s="4"/>
       <c r="S251" s="4"/>
     </row>
-    <row r="252" spans="1:19">
+    <row r="252" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A252" s="4"/>
       <c r="B252" s="5"/>
       <c r="C252" s="4"/>
@@ -5689,7 +5689,7 @@
       <c r="R252" s="4"/>
       <c r="S252" s="4"/>
     </row>
-    <row r="253" spans="1:19">
+    <row r="253" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A253" s="4"/>
       <c r="B253" s="5"/>
       <c r="C253" s="4"/>
@@ -5710,7 +5710,7 @@
       <c r="R253" s="4"/>
       <c r="S253" s="4"/>
     </row>
-    <row r="254" spans="1:19">
+    <row r="254" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A254" s="4"/>
       <c r="B254" s="5"/>
       <c r="C254" s="4"/>
@@ -5731,7 +5731,7 @@
       <c r="R254" s="4"/>
       <c r="S254" s="4"/>
     </row>
-    <row r="255" spans="1:19">
+    <row r="255" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A255" s="4"/>
       <c r="B255" s="5"/>
       <c r="C255" s="4"/>
@@ -5752,7 +5752,7 @@
       <c r="R255" s="4"/>
       <c r="S255" s="4"/>
     </row>
-    <row r="256" spans="1:19">
+    <row r="256" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A256" s="4"/>
       <c r="B256" s="5"/>
       <c r="C256" s="4"/>
@@ -5773,7 +5773,7 @@
       <c r="R256" s="4"/>
       <c r="S256" s="4"/>
     </row>
-    <row r="257" spans="1:19">
+    <row r="257" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A257" s="4"/>
       <c r="B257" s="5"/>
       <c r="C257" s="4"/>
@@ -5794,7 +5794,7 @@
       <c r="R257" s="4"/>
       <c r="S257" s="4"/>
     </row>
-    <row r="258" spans="1:19">
+    <row r="258" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A258" s="4"/>
       <c r="B258" s="5"/>
       <c r="C258" s="4"/>
@@ -5815,7 +5815,7 @@
       <c r="R258" s="4"/>
       <c r="S258" s="4"/>
     </row>
-    <row r="259" spans="1:19">
+    <row r="259" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A259" s="4"/>
       <c r="B259" s="5"/>
       <c r="C259" s="4"/>
@@ -5836,7 +5836,7 @@
       <c r="R259" s="4"/>
       <c r="S259" s="4"/>
     </row>
-    <row r="260" spans="1:19">
+    <row r="260" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A260" s="4"/>
       <c r="B260" s="5"/>
       <c r="C260" s="4"/>
@@ -5857,7 +5857,7 @@
       <c r="R260" s="4"/>
       <c r="S260" s="4"/>
     </row>
-    <row r="261" spans="1:19">
+    <row r="261" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A261" s="4"/>
       <c r="B261" s="5"/>
       <c r="C261" s="4"/>
@@ -5878,7 +5878,7 @@
       <c r="R261" s="4"/>
       <c r="S261" s="4"/>
     </row>
-    <row r="262" spans="1:19">
+    <row r="262" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A262" s="4"/>
       <c r="B262" s="5"/>
       <c r="C262" s="4"/>
@@ -5899,7 +5899,7 @@
       <c r="R262" s="4"/>
       <c r="S262" s="4"/>
     </row>
-    <row r="263" spans="1:19">
+    <row r="263" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A263" s="4"/>
       <c r="B263" s="5"/>
       <c r="C263" s="4"/>
@@ -5920,7 +5920,7 @@
       <c r="R263" s="4"/>
       <c r="S263" s="4"/>
     </row>
-    <row r="264" spans="1:19">
+    <row r="264" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A264" s="4"/>
       <c r="B264" s="5"/>
       <c r="C264" s="4"/>
@@ -5941,7 +5941,7 @@
       <c r="R264" s="4"/>
       <c r="S264" s="4"/>
     </row>
-    <row r="265" spans="1:19">
+    <row r="265" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A265" s="4"/>
       <c r="B265" s="5"/>
       <c r="C265" s="4"/>
@@ -5962,7 +5962,7 @@
       <c r="R265" s="4"/>
       <c r="S265" s="4"/>
     </row>
-    <row r="266" spans="1:19">
+    <row r="266" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A266" s="4"/>
       <c r="B266" s="5"/>
       <c r="C266" s="4"/>
@@ -5983,7 +5983,7 @@
       <c r="R266" s="4"/>
       <c r="S266" s="4"/>
     </row>
-    <row r="267" spans="1:19">
+    <row r="267" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A267" s="4"/>
       <c r="B267" s="5"/>
       <c r="C267" s="4"/>
@@ -6004,7 +6004,7 @@
       <c r="R267" s="4"/>
       <c r="S267" s="4"/>
     </row>
-    <row r="268" spans="1:19">
+    <row r="268" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A268" s="4"/>
       <c r="B268" s="5"/>
       <c r="C268" s="4"/>
@@ -6025,7 +6025,7 @@
       <c r="R268" s="4"/>
       <c r="S268" s="4"/>
     </row>
-    <row r="269" spans="1:19">
+    <row r="269" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A269" s="4"/>
       <c r="B269" s="5"/>
       <c r="C269" s="4"/>
@@ -6046,7 +6046,7 @@
       <c r="R269" s="4"/>
       <c r="S269" s="4"/>
     </row>
-    <row r="270" spans="1:19">
+    <row r="270" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A270" s="4"/>
       <c r="B270" s="5"/>
       <c r="C270" s="4"/>
@@ -6067,7 +6067,7 @@
       <c r="R270" s="4"/>
       <c r="S270" s="4"/>
     </row>
-    <row r="271" spans="1:19">
+    <row r="271" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A271" s="4"/>
       <c r="B271" s="5"/>
       <c r="C271" s="4"/>
@@ -6088,7 +6088,7 @@
       <c r="R271" s="4"/>
       <c r="S271" s="4"/>
     </row>
-    <row r="272" spans="1:19">
+    <row r="272" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A272" s="4"/>
       <c r="B272" s="5"/>
       <c r="C272" s="4"/>
@@ -6109,7 +6109,7 @@
       <c r="R272" s="4"/>
       <c r="S272" s="4"/>
     </row>
-    <row r="273" spans="1:19">
+    <row r="273" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A273" s="4"/>
       <c r="B273" s="5"/>
       <c r="C273" s="4"/>
@@ -6130,7 +6130,7 @@
       <c r="R273" s="4"/>
       <c r="S273" s="4"/>
     </row>
-    <row r="274" spans="1:19">
+    <row r="274" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A274" s="4"/>
       <c r="B274" s="5"/>
       <c r="C274" s="4"/>
@@ -6151,7 +6151,7 @@
       <c r="R274" s="4"/>
       <c r="S274" s="4"/>
     </row>
-    <row r="275" spans="1:19">
+    <row r="275" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A275" s="4"/>
       <c r="B275" s="5"/>
       <c r="C275" s="4"/>
@@ -6172,7 +6172,7 @@
       <c r="R275" s="4"/>
       <c r="S275" s="4"/>
     </row>
-    <row r="276" spans="1:19">
+    <row r="276" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A276" s="4"/>
       <c r="B276" s="5"/>
       <c r="C276" s="4"/>
@@ -6193,7 +6193,7 @@
       <c r="R276" s="4"/>
       <c r="S276" s="4"/>
     </row>
-    <row r="277" spans="1:19">
+    <row r="277" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A277" s="4"/>
       <c r="B277" s="5"/>
       <c r="C277" s="4"/>
@@ -6214,7 +6214,7 @@
       <c r="R277" s="4"/>
       <c r="S277" s="4"/>
     </row>
-    <row r="278" spans="1:19">
+    <row r="278" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A278" s="4"/>
       <c r="B278" s="5"/>
       <c r="C278" s="4"/>
@@ -6235,7 +6235,7 @@
       <c r="R278" s="4"/>
       <c r="S278" s="4"/>
     </row>
-    <row r="279" spans="1:19">
+    <row r="279" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A279" s="4"/>
       <c r="B279" s="5"/>
       <c r="C279" s="4"/>
@@ -6256,7 +6256,7 @@
       <c r="R279" s="4"/>
       <c r="S279" s="4"/>
     </row>
-    <row r="280" spans="1:19">
+    <row r="280" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A280" s="4"/>
       <c r="B280" s="5"/>
       <c r="C280" s="4"/>
@@ -6277,7 +6277,7 @@
       <c r="R280" s="4"/>
       <c r="S280" s="4"/>
     </row>
-    <row r="281" spans="1:19">
+    <row r="281" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A281" s="4"/>
       <c r="B281" s="5"/>
       <c r="C281" s="4"/>
@@ -6298,7 +6298,7 @@
       <c r="R281" s="4"/>
       <c r="S281" s="4"/>
     </row>
-    <row r="282" spans="1:19">
+    <row r="282" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A282" s="4"/>
       <c r="B282" s="5"/>
       <c r="C282" s="4"/>
@@ -6319,7 +6319,7 @@
       <c r="R282" s="4"/>
       <c r="S282" s="4"/>
     </row>
-    <row r="283" spans="1:19">
+    <row r="283" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A283" s="4"/>
       <c r="B283" s="5"/>
       <c r="C283" s="4"/>
@@ -6340,7 +6340,7 @@
       <c r="R283" s="4"/>
       <c r="S283" s="4"/>
     </row>
-    <row r="284" spans="1:19">
+    <row r="284" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A284" s="4"/>
       <c r="B284" s="5"/>
       <c r="C284" s="4"/>
@@ -6361,7 +6361,7 @@
       <c r="R284" s="4"/>
       <c r="S284" s="4"/>
     </row>
-    <row r="285" spans="1:19">
+    <row r="285" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A285" s="4"/>
       <c r="B285" s="5"/>
       <c r="C285" s="4"/>
@@ -6382,7 +6382,7 @@
       <c r="R285" s="4"/>
       <c r="S285" s="4"/>
     </row>
-    <row r="286" spans="1:19">
+    <row r="286" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A286" s="4"/>
       <c r="B286" s="5"/>
       <c r="C286" s="4"/>
@@ -6403,7 +6403,7 @@
       <c r="R286" s="4"/>
       <c r="S286" s="4"/>
     </row>
-    <row r="287" spans="1:19">
+    <row r="287" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A287" s="4"/>
       <c r="B287" s="5"/>
       <c r="C287" s="4"/>
@@ -6424,7 +6424,7 @@
       <c r="R287" s="4"/>
       <c r="S287" s="4"/>
     </row>
-    <row r="288" spans="1:19">
+    <row r="288" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A288" s="4"/>
       <c r="B288" s="5"/>
       <c r="C288" s="4"/>
@@ -6445,7 +6445,7 @@
       <c r="R288" s="4"/>
       <c r="S288" s="4"/>
     </row>
-    <row r="289" spans="1:19">
+    <row r="289" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A289" s="4"/>
       <c r="B289" s="5"/>
       <c r="C289" s="4"/>
@@ -6466,7 +6466,7 @@
       <c r="R289" s="4"/>
       <c r="S289" s="4"/>
     </row>
-    <row r="290" spans="1:19">
+    <row r="290" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A290" s="4"/>
       <c r="B290" s="5"/>
       <c r="C290" s="4"/>
@@ -6487,7 +6487,7 @@
       <c r="R290" s="4"/>
       <c r="S290" s="4"/>
     </row>
-    <row r="291" spans="1:19">
+    <row r="291" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A291" s="4"/>
       <c r="B291" s="5"/>
       <c r="C291" s="4"/>
@@ -6508,7 +6508,7 @@
       <c r="R291" s="4"/>
       <c r="S291" s="4"/>
     </row>
-    <row r="292" spans="1:19">
+    <row r="292" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A292" s="4"/>
       <c r="B292" s="5"/>
       <c r="C292" s="4"/>
@@ -6529,7 +6529,7 @@
       <c r="R292" s="4"/>
       <c r="S292" s="4"/>
     </row>
-    <row r="293" spans="1:19">
+    <row r="293" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A293" s="4"/>
       <c r="B293" s="5"/>
       <c r="C293" s="4"/>
@@ -6550,7 +6550,7 @@
       <c r="R293" s="4"/>
       <c r="S293" s="4"/>
     </row>
-    <row r="294" spans="1:19">
+    <row r="294" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A294" s="4"/>
       <c r="B294" s="5"/>
       <c r="C294" s="4"/>
@@ -6571,7 +6571,7 @@
       <c r="R294" s="4"/>
       <c r="S294" s="4"/>
     </row>
-    <row r="295" spans="1:19">
+    <row r="295" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A295" s="4"/>
       <c r="B295" s="5"/>
       <c r="C295" s="4"/>
@@ -6592,7 +6592,7 @@
       <c r="R295" s="4"/>
       <c r="S295" s="4"/>
     </row>
-    <row r="296" spans="1:19">
+    <row r="296" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A296" s="4"/>
       <c r="B296" s="5"/>
       <c r="C296" s="4"/>
@@ -6613,7 +6613,7 @@
       <c r="R296" s="4"/>
       <c r="S296" s="4"/>
     </row>
-    <row r="297" spans="1:19">
+    <row r="297" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A297" s="4"/>
       <c r="B297" s="5"/>
       <c r="C297" s="4"/>
@@ -6634,7 +6634,7 @@
       <c r="R297" s="4"/>
       <c r="S297" s="4"/>
     </row>
-    <row r="298" spans="1:19">
+    <row r="298" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A298" s="4"/>
       <c r="B298" s="5"/>
       <c r="C298" s="4"/>
@@ -6655,7 +6655,7 @@
       <c r="R298" s="4"/>
       <c r="S298" s="4"/>
     </row>
-    <row r="299" spans="1:19">
+    <row r="299" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A299" s="4"/>
       <c r="B299" s="5"/>
       <c r="C299" s="4"/>
@@ -6676,7 +6676,7 @@
       <c r="R299" s="4"/>
       <c r="S299" s="4"/>
     </row>
-    <row r="300" spans="1:19">
+    <row r="300" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A300" s="4"/>
       <c r="B300" s="5"/>
       <c r="C300" s="4"/>
@@ -6697,7 +6697,7 @@
       <c r="R300" s="4"/>
       <c r="S300" s="4"/>
     </row>
-    <row r="301" spans="1:19">
+    <row r="301" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A301" s="4"/>
       <c r="B301" s="5"/>
       <c r="C301" s="4"/>
@@ -6718,7 +6718,7 @@
       <c r="R301" s="4"/>
       <c r="S301" s="4"/>
     </row>
-    <row r="302" spans="1:19">
+    <row r="302" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A302" s="4"/>
       <c r="B302" s="5"/>
       <c r="C302" s="4"/>
@@ -6739,7 +6739,7 @@
       <c r="R302" s="4"/>
       <c r="S302" s="4"/>
     </row>
-    <row r="303" spans="1:19">
+    <row r="303" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A303" s="4"/>
       <c r="B303" s="5"/>
       <c r="C303" s="4"/>
@@ -6760,7 +6760,7 @@
       <c r="R303" s="4"/>
       <c r="S303" s="4"/>
     </row>
-    <row r="304" spans="1:19">
+    <row r="304" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A304" s="4"/>
       <c r="B304" s="5"/>
       <c r="C304" s="4"/>
@@ -6781,7 +6781,7 @@
       <c r="R304" s="4"/>
       <c r="S304" s="4"/>
     </row>
-    <row r="305" spans="1:19">
+    <row r="305" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A305" s="4"/>
       <c r="B305" s="5"/>
       <c r="C305" s="4"/>
@@ -6802,7 +6802,7 @@
       <c r="R305" s="4"/>
       <c r="S305" s="4"/>
     </row>
-    <row r="306" spans="1:19">
+    <row r="306" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A306" s="4"/>
       <c r="B306" s="5"/>
       <c r="C306" s="4"/>
@@ -6823,7 +6823,7 @@
       <c r="R306" s="4"/>
       <c r="S306" s="4"/>
     </row>
-    <row r="307" spans="1:19">
+    <row r="307" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A307" s="4"/>
       <c r="B307" s="5"/>
       <c r="C307" s="4"/>
@@ -6844,7 +6844,7 @@
       <c r="R307" s="4"/>
       <c r="S307" s="4"/>
     </row>
-    <row r="308" spans="1:19">
+    <row r="308" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A308" s="4"/>
       <c r="B308" s="5"/>
       <c r="C308" s="4"/>
@@ -6865,7 +6865,7 @@
       <c r="R308" s="4"/>
       <c r="S308" s="4"/>
     </row>
-    <row r="309" spans="1:19">
+    <row r="309" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A309" s="4"/>
       <c r="B309" s="5"/>
       <c r="C309" s="4"/>
@@ -6886,7 +6886,7 @@
       <c r="R309" s="4"/>
       <c r="S309" s="4"/>
     </row>
-    <row r="310" spans="1:19">
+    <row r="310" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A310" s="4"/>
       <c r="B310" s="5"/>
       <c r="C310" s="4"/>
@@ -6907,7 +6907,7 @@
       <c r="R310" s="4"/>
       <c r="S310" s="4"/>
     </row>
-    <row r="311" spans="1:19">
+    <row r="311" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A311" s="4"/>
       <c r="B311" s="5"/>
       <c r="C311" s="4"/>
@@ -6928,7 +6928,7 @@
       <c r="R311" s="4"/>
       <c r="S311" s="4"/>
     </row>
-    <row r="312" spans="1:19">
+    <row r="312" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A312" s="4"/>
       <c r="B312" s="5"/>
       <c r="C312" s="4"/>
@@ -6949,7 +6949,7 @@
       <c r="R312" s="4"/>
       <c r="S312" s="4"/>
     </row>
-    <row r="313" spans="1:19">
+    <row r="313" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A313" s="4"/>
       <c r="B313" s="5"/>
       <c r="C313" s="4"/>
@@ -6970,7 +6970,7 @@
       <c r="R313" s="4"/>
       <c r="S313" s="4"/>
     </row>
-    <row r="314" spans="1:19">
+    <row r="314" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A314" s="4"/>
       <c r="B314" s="5"/>
       <c r="C314" s="4"/>
@@ -6991,7 +6991,7 @@
       <c r="R314" s="4"/>
       <c r="S314" s="4"/>
     </row>
-    <row r="315" spans="1:19">
+    <row r="315" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A315" s="4"/>
       <c r="B315" s="5"/>
       <c r="C315" s="4"/>
@@ -7012,7 +7012,7 @@
       <c r="R315" s="4"/>
       <c r="S315" s="4"/>
     </row>
-    <row r="316" spans="1:19">
+    <row r="316" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A316" s="4"/>
       <c r="B316" s="5"/>
       <c r="C316" s="4"/>
@@ -7033,7 +7033,7 @@
       <c r="R316" s="4"/>
       <c r="S316" s="4"/>
     </row>
-    <row r="317" spans="1:19">
+    <row r="317" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A317" s="4"/>
       <c r="B317" s="5"/>
       <c r="C317" s="4"/>
@@ -7054,7 +7054,7 @@
       <c r="R317" s="4"/>
       <c r="S317" s="4"/>
     </row>
-    <row r="318" spans="1:19">
+    <row r="318" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A318" s="4"/>
       <c r="B318" s="5"/>
       <c r="C318" s="4"/>
@@ -7075,7 +7075,7 @@
       <c r="R318" s="4"/>
       <c r="S318" s="4"/>
     </row>
-    <row r="319" spans="1:19">
+    <row r="319" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A319" s="4"/>
       <c r="B319" s="5"/>
       <c r="C319" s="4"/>
@@ -7096,7 +7096,7 @@
       <c r="R319" s="4"/>
       <c r="S319" s="4"/>
     </row>
-    <row r="320" spans="1:19">
+    <row r="320" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A320" s="4"/>
       <c r="B320" s="5"/>
       <c r="C320" s="4"/>
@@ -7117,7 +7117,7 @@
       <c r="R320" s="4"/>
       <c r="S320" s="4"/>
     </row>
-    <row r="321" spans="1:19">
+    <row r="321" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A321" s="4"/>
       <c r="B321" s="5"/>
       <c r="C321" s="4"/>
@@ -7138,7 +7138,7 @@
       <c r="R321" s="4"/>
       <c r="S321" s="4"/>
     </row>
-    <row r="322" spans="1:19">
+    <row r="322" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A322" s="4"/>
       <c r="B322" s="5"/>
       <c r="C322" s="4"/>
@@ -7159,7 +7159,7 @@
       <c r="R322" s="4"/>
       <c r="S322" s="4"/>
     </row>
-    <row r="323" spans="1:19">
+    <row r="323" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A323" s="4"/>
       <c r="B323" s="5"/>
       <c r="C323" s="4"/>
@@ -7180,7 +7180,7 @@
       <c r="R323" s="4"/>
       <c r="S323" s="4"/>
     </row>
-    <row r="324" spans="1:19">
+    <row r="324" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A324" s="4"/>
       <c r="B324" s="5"/>
       <c r="C324" s="4"/>
@@ -7201,7 +7201,7 @@
       <c r="R324" s="4"/>
       <c r="S324" s="4"/>
     </row>
-    <row r="325" spans="1:19">
+    <row r="325" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A325" s="4"/>
       <c r="B325" s="5"/>
       <c r="C325" s="4"/>
@@ -7222,7 +7222,7 @@
       <c r="R325" s="4"/>
       <c r="S325" s="4"/>
     </row>
-    <row r="326" spans="1:19">
+    <row r="326" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A326" s="4"/>
       <c r="B326" s="5"/>
       <c r="C326" s="4"/>
@@ -7243,7 +7243,7 @@
       <c r="R326" s="4"/>
       <c r="S326" s="4"/>
     </row>
-    <row r="327" spans="1:19">
+    <row r="327" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A327" s="4"/>
       <c r="B327" s="5"/>
       <c r="C327" s="4"/>
@@ -7264,7 +7264,7 @@
       <c r="R327" s="4"/>
       <c r="S327" s="4"/>
     </row>
-    <row r="328" spans="1:19">
+    <row r="328" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A328" s="4"/>
       <c r="B328" s="5"/>
       <c r="C328" s="4"/>
@@ -7285,7 +7285,7 @@
       <c r="R328" s="4"/>
       <c r="S328" s="4"/>
     </row>
-    <row r="329" spans="1:19">
+    <row r="329" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A329" s="4"/>
       <c r="B329" s="5"/>
       <c r="C329" s="4"/>
@@ -7306,7 +7306,7 @@
       <c r="R329" s="4"/>
       <c r="S329" s="4"/>
     </row>
-    <row r="330" spans="1:19">
+    <row r="330" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A330" s="4"/>
       <c r="B330" s="5"/>
       <c r="C330" s="4"/>
@@ -7327,7 +7327,7 @@
       <c r="R330" s="4"/>
       <c r="S330" s="4"/>
     </row>
-    <row r="331" spans="1:19">
+    <row r="331" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A331" s="4"/>
       <c r="B331" s="5"/>
       <c r="C331" s="4"/>
@@ -7348,7 +7348,7 @@
       <c r="R331" s="4"/>
       <c r="S331" s="4"/>
     </row>
-    <row r="332" spans="1:19">
+    <row r="332" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A332" s="4"/>
       <c r="B332" s="5"/>
       <c r="C332" s="4"/>
@@ -7369,7 +7369,7 @@
       <c r="R332" s="4"/>
       <c r="S332" s="4"/>
     </row>
-    <row r="333" spans="1:19">
+    <row r="333" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A333" s="4"/>
       <c r="B333" s="5"/>
       <c r="C333" s="4"/>
@@ -7390,7 +7390,7 @@
       <c r="R333" s="4"/>
       <c r="S333" s="4"/>
     </row>
-    <row r="334" spans="1:19">
+    <row r="334" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A334" s="4"/>
       <c r="B334" s="5"/>
       <c r="C334" s="4"/>
@@ -7411,7 +7411,7 @@
       <c r="R334" s="4"/>
       <c r="S334" s="4"/>
     </row>
-    <row r="335" spans="1:19">
+    <row r="335" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A335" s="4"/>
       <c r="B335" s="5"/>
       <c r="C335" s="4"/>
@@ -7432,7 +7432,7 @@
       <c r="R335" s="4"/>
       <c r="S335" s="4"/>
     </row>
-    <row r="336" spans="1:19">
+    <row r="336" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A336" s="4"/>
       <c r="B336" s="5"/>
       <c r="C336" s="4"/>
@@ -7453,7 +7453,7 @@
       <c r="R336" s="4"/>
       <c r="S336" s="4"/>
     </row>
-    <row r="337" spans="1:19">
+    <row r="337" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A337" s="4"/>
       <c r="B337" s="5"/>
       <c r="C337" s="4"/>
@@ -7474,7 +7474,7 @@
       <c r="R337" s="4"/>
       <c r="S337" s="4"/>
     </row>
-    <row r="338" spans="1:19">
+    <row r="338" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A338" s="4"/>
       <c r="B338" s="5"/>
       <c r="C338" s="4"/>
@@ -7495,7 +7495,7 @@
       <c r="R338" s="4"/>
       <c r="S338" s="4"/>
     </row>
-    <row r="339" spans="1:19">
+    <row r="339" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A339" s="4"/>
       <c r="B339" s="5"/>
       <c r="C339" s="4"/>
@@ -7516,7 +7516,7 @@
       <c r="R339" s="4"/>
       <c r="S339" s="4"/>
     </row>
-    <row r="340" spans="1:19">
+    <row r="340" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A340" s="4"/>
       <c r="B340" s="5"/>
       <c r="C340" s="4"/>
@@ -7537,7 +7537,7 @@
       <c r="R340" s="4"/>
       <c r="S340" s="4"/>
     </row>
-    <row r="341" spans="1:19">
+    <row r="341" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A341" s="4"/>
       <c r="B341" s="5"/>
       <c r="C341" s="4"/>
@@ -7558,7 +7558,7 @@
       <c r="R341" s="4"/>
       <c r="S341" s="4"/>
     </row>
-    <row r="342" spans="1:19">
+    <row r="342" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A342" s="4"/>
       <c r="B342" s="5"/>
       <c r="C342" s="4"/>
@@ -7579,7 +7579,7 @@
       <c r="R342" s="4"/>
       <c r="S342" s="4"/>
     </row>
-    <row r="343" spans="1:19">
+    <row r="343" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A343" s="4"/>
       <c r="B343" s="5"/>
       <c r="C343" s="4"/>
@@ -7600,7 +7600,7 @@
       <c r="R343" s="4"/>
       <c r="S343" s="4"/>
     </row>
-    <row r="344" spans="1:19">
+    <row r="344" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A344" s="4"/>
       <c r="B344" s="5"/>
       <c r="C344" s="4"/>
@@ -7621,7 +7621,7 @@
       <c r="R344" s="4"/>
       <c r="S344" s="4"/>
     </row>
-    <row r="345" spans="1:19">
+    <row r="345" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A345" s="4"/>
       <c r="B345" s="5"/>
       <c r="C345" s="4"/>
@@ -7642,7 +7642,7 @@
       <c r="R345" s="4"/>
       <c r="S345" s="4"/>
     </row>
-    <row r="346" spans="1:19">
+    <row r="346" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A346" s="4"/>
       <c r="B346" s="5"/>
       <c r="C346" s="4"/>
@@ -7663,7 +7663,7 @@
       <c r="R346" s="4"/>
       <c r="S346" s="4"/>
     </row>
-    <row r="347" spans="1:19">
+    <row r="347" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A347" s="4"/>
       <c r="B347" s="5"/>
       <c r="C347" s="4"/>
@@ -7684,7 +7684,7 @@
       <c r="R347" s="4"/>
       <c r="S347" s="4"/>
     </row>
-    <row r="348" spans="1:19">
+    <row r="348" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A348" s="4"/>
       <c r="B348" s="5"/>
       <c r="C348" s="4"/>
@@ -7705,7 +7705,7 @@
       <c r="R348" s="4"/>
       <c r="S348" s="4"/>
     </row>
-    <row r="349" spans="1:19">
+    <row r="349" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A349" s="4"/>
       <c r="B349" s="5"/>
       <c r="C349" s="4"/>
@@ -7726,7 +7726,7 @@
       <c r="R349" s="4"/>
       <c r="S349" s="4"/>
     </row>
-    <row r="350" spans="1:19">
+    <row r="350" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A350" s="4"/>
       <c r="B350" s="5"/>
       <c r="C350" s="4"/>
@@ -7747,7 +7747,7 @@
       <c r="R350" s="4"/>
       <c r="S350" s="4"/>
     </row>
-    <row r="351" spans="1:19">
+    <row r="351" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A351" s="4"/>
       <c r="B351" s="5"/>
       <c r="C351" s="4"/>
@@ -7768,7 +7768,7 @@
       <c r="R351" s="4"/>
       <c r="S351" s="4"/>
     </row>
-    <row r="352" spans="1:19">
+    <row r="352" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A352" s="4"/>
       <c r="B352" s="5"/>
       <c r="C352" s="4"/>
@@ -7789,7 +7789,7 @@
       <c r="R352" s="4"/>
       <c r="S352" s="4"/>
     </row>
-    <row r="353" spans="1:19">
+    <row r="353" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A353" s="4"/>
       <c r="B353" s="5"/>
       <c r="C353" s="4"/>
@@ -7810,7 +7810,7 @@
       <c r="R353" s="4"/>
       <c r="S353" s="4"/>
     </row>
-    <row r="354" spans="1:19">
+    <row r="354" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A354" s="4"/>
       <c r="B354" s="5"/>
       <c r="C354" s="4"/>
@@ -7831,7 +7831,7 @@
       <c r="R354" s="4"/>
       <c r="S354" s="4"/>
     </row>
-    <row r="355" spans="1:19">
+    <row r="355" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A355" s="4"/>
       <c r="B355" s="5"/>
       <c r="C355" s="4"/>
@@ -7852,7 +7852,7 @@
       <c r="R355" s="4"/>
       <c r="S355" s="4"/>
     </row>
-    <row r="356" spans="1:19">
+    <row r="356" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A356" s="4"/>
       <c r="B356" s="5"/>
       <c r="C356" s="4"/>
@@ -7873,7 +7873,7 @@
       <c r="R356" s="4"/>
       <c r="S356" s="4"/>
     </row>
-    <row r="357" spans="1:19">
+    <row r="357" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A357" s="4"/>
       <c r="B357" s="5"/>
       <c r="C357" s="4"/>
@@ -7894,7 +7894,7 @@
       <c r="R357" s="4"/>
       <c r="S357" s="4"/>
     </row>
-    <row r="358" spans="1:19">
+    <row r="358" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A358" s="4"/>
       <c r="B358" s="5"/>
       <c r="C358" s="4"/>
@@ -7915,7 +7915,7 @@
       <c r="R358" s="4"/>
       <c r="S358" s="4"/>
     </row>
-    <row r="359" spans="1:19">
+    <row r="359" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A359" s="4"/>
       <c r="B359" s="5"/>
       <c r="C359" s="4"/>
@@ -7936,7 +7936,7 @@
       <c r="R359" s="4"/>
       <c r="S359" s="4"/>
     </row>
-    <row r="360" spans="1:19">
+    <row r="360" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A360" s="4"/>
       <c r="B360" s="5"/>
       <c r="C360" s="4"/>
@@ -7957,7 +7957,7 @@
       <c r="R360" s="4"/>
       <c r="S360" s="4"/>
     </row>
-    <row r="361" spans="1:19">
+    <row r="361" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A361" s="4"/>
       <c r="B361" s="5"/>
       <c r="C361" s="4"/>
@@ -7978,7 +7978,7 @@
       <c r="R361" s="4"/>
       <c r="S361" s="4"/>
     </row>
-    <row r="362" spans="1:19">
+    <row r="362" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A362" s="4"/>
       <c r="B362" s="5"/>
       <c r="C362" s="4"/>
@@ -7999,7 +7999,7 @@
       <c r="R362" s="4"/>
       <c r="S362" s="4"/>
     </row>
-    <row r="363" spans="1:19">
+    <row r="363" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A363" s="4"/>
       <c r="B363" s="5"/>
       <c r="C363" s="4"/>
@@ -8020,7 +8020,7 @@
       <c r="R363" s="4"/>
       <c r="S363" s="4"/>
     </row>
-    <row r="364" spans="1:19">
+    <row r="364" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A364" s="4"/>
       <c r="B364" s="5"/>
       <c r="C364" s="4"/>
@@ -8041,7 +8041,7 @@
       <c r="R364" s="4"/>
       <c r="S364" s="4"/>
     </row>
-    <row r="365" spans="1:19">
+    <row r="365" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A365" s="4"/>
       <c r="B365" s="5"/>
       <c r="C365" s="4"/>
@@ -8062,7 +8062,7 @@
       <c r="R365" s="4"/>
       <c r="S365" s="4"/>
     </row>
-    <row r="366" spans="1:19">
+    <row r="366" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A366" s="4"/>
       <c r="B366" s="5"/>
       <c r="C366" s="4"/>
@@ -8083,7 +8083,7 @@
       <c r="R366" s="4"/>
       <c r="S366" s="4"/>
     </row>
-    <row r="367" spans="1:19">
+    <row r="367" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A367" s="4"/>
       <c r="B367" s="5"/>
       <c r="C367" s="4"/>
@@ -8104,7 +8104,7 @@
       <c r="R367" s="4"/>
       <c r="S367" s="4"/>
     </row>
-    <row r="368" spans="1:19">
+    <row r="368" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A368" s="4"/>
       <c r="B368" s="5"/>
       <c r="C368" s="4"/>
@@ -8125,7 +8125,7 @@
       <c r="R368" s="4"/>
       <c r="S368" s="4"/>
     </row>
-    <row r="369" spans="1:19">
+    <row r="369" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A369" s="4"/>
       <c r="B369" s="5"/>
       <c r="C369" s="4"/>
@@ -8146,7 +8146,7 @@
       <c r="R369" s="4"/>
       <c r="S369" s="4"/>
     </row>
-    <row r="370" spans="1:19">
+    <row r="370" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A370" s="4"/>
       <c r="B370" s="5"/>
       <c r="C370" s="4"/>
@@ -8167,7 +8167,7 @@
       <c r="R370" s="4"/>
       <c r="S370" s="4"/>
     </row>
-    <row r="371" spans="1:19">
+    <row r="371" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A371" s="4"/>
       <c r="B371" s="5"/>
       <c r="C371" s="4"/>
@@ -8188,7 +8188,7 @@
       <c r="R371" s="4"/>
       <c r="S371" s="4"/>
     </row>
-    <row r="372" spans="1:19">
+    <row r="372" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A372" s="4"/>
       <c r="B372" s="5"/>
       <c r="C372" s="4"/>
@@ -8209,7 +8209,7 @@
       <c r="R372" s="4"/>
       <c r="S372" s="4"/>
     </row>
-    <row r="373" spans="1:19">
+    <row r="373" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A373" s="4"/>
       <c r="B373" s="5"/>
       <c r="C373" s="4"/>
@@ -8230,7 +8230,7 @@
       <c r="R373" s="4"/>
       <c r="S373" s="4"/>
     </row>
-    <row r="374" spans="1:19">
+    <row r="374" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A374" s="4"/>
       <c r="B374" s="5"/>
       <c r="C374" s="4"/>
@@ -8251,7 +8251,7 @@
       <c r="R374" s="4"/>
       <c r="S374" s="4"/>
     </row>
-    <row r="375" spans="1:19">
+    <row r="375" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A375" s="4"/>
       <c r="B375" s="5"/>
       <c r="C375" s="4"/>
@@ -8272,7 +8272,7 @@
       <c r="R375" s="4"/>
       <c r="S375" s="4"/>
     </row>
-    <row r="376" spans="1:19">
+    <row r="376" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A376" s="4"/>
       <c r="B376" s="5"/>
       <c r="C376" s="4"/>
@@ -8293,7 +8293,7 @@
       <c r="R376" s="4"/>
       <c r="S376" s="4"/>
     </row>
-    <row r="377" spans="1:19">
+    <row r="377" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A377" s="4"/>
       <c r="B377" s="5"/>
       <c r="C377" s="4"/>
@@ -8314,7 +8314,7 @@
       <c r="R377" s="4"/>
       <c r="S377" s="4"/>
     </row>
-    <row r="378" spans="1:19">
+    <row r="378" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A378" s="4"/>
       <c r="B378" s="5"/>
       <c r="C378" s="4"/>
@@ -8335,7 +8335,7 @@
       <c r="R378" s="4"/>
       <c r="S378" s="4"/>
     </row>
-    <row r="379" spans="1:19">
+    <row r="379" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A379" s="4"/>
       <c r="B379" s="5"/>
       <c r="C379" s="4"/>
@@ -8356,7 +8356,7 @@
       <c r="R379" s="4"/>
       <c r="S379" s="4"/>
     </row>
-    <row r="380" spans="1:19">
+    <row r="380" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A380" s="4"/>
       <c r="B380" s="5"/>
       <c r="C380" s="4"/>
@@ -8377,7 +8377,7 @@
       <c r="R380" s="4"/>
       <c r="S380" s="4"/>
     </row>
-    <row r="381" spans="1:19">
+    <row r="381" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A381" s="4"/>
       <c r="B381" s="5"/>
       <c r="C381" s="4"/>
@@ -8398,7 +8398,7 @@
       <c r="R381" s="4"/>
       <c r="S381" s="4"/>
     </row>
-    <row r="382" spans="1:19">
+    <row r="382" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A382" s="4"/>
       <c r="B382" s="5"/>
       <c r="C382" s="4"/>
@@ -8419,7 +8419,7 @@
       <c r="R382" s="4"/>
       <c r="S382" s="4"/>
     </row>
-    <row r="383" spans="1:19">
+    <row r="383" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A383" s="4"/>
       <c r="B383" s="5"/>
       <c r="C383" s="4"/>
@@ -8440,7 +8440,7 @@
       <c r="R383" s="4"/>
       <c r="S383" s="4"/>
     </row>
-    <row r="384" spans="1:19">
+    <row r="384" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A384" s="4"/>
       <c r="B384" s="5"/>
       <c r="C384" s="4"/>
@@ -8461,7 +8461,7 @@
       <c r="R384" s="4"/>
       <c r="S384" s="4"/>
     </row>
-    <row r="385" spans="1:19">
+    <row r="385" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A385" s="4"/>
       <c r="B385" s="5"/>
       <c r="C385" s="4"/>
@@ -8482,7 +8482,7 @@
       <c r="R385" s="4"/>
       <c r="S385" s="4"/>
     </row>
-    <row r="386" spans="1:19">
+    <row r="386" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A386" s="4"/>
       <c r="B386" s="5"/>
       <c r="C386" s="4"/>
@@ -8503,7 +8503,7 @@
       <c r="R386" s="4"/>
       <c r="S386" s="4"/>
     </row>
-    <row r="387" spans="1:19">
+    <row r="387" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A387" s="4"/>
       <c r="B387" s="5"/>
       <c r="C387" s="4"/>
@@ -8524,7 +8524,7 @@
       <c r="R387" s="4"/>
       <c r="S387" s="4"/>
     </row>
-    <row r="388" spans="1:19">
+    <row r="388" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A388" s="4"/>
       <c r="B388" s="5"/>
       <c r="C388" s="4"/>
@@ -8545,7 +8545,7 @@
       <c r="R388" s="4"/>
       <c r="S388" s="4"/>
     </row>
-    <row r="389" spans="1:19">
+    <row r="389" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A389" s="4"/>
       <c r="B389" s="5"/>
       <c r="C389" s="4"/>
@@ -8566,7 +8566,7 @@
       <c r="R389" s="4"/>
       <c r="S389" s="4"/>
     </row>
-    <row r="390" spans="1:19">
+    <row r="390" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A390" s="4"/>
       <c r="B390" s="5"/>
       <c r="C390" s="4"/>
@@ -8587,7 +8587,7 @@
       <c r="R390" s="4"/>
       <c r="S390" s="4"/>
     </row>
-    <row r="391" spans="1:19">
+    <row r="391" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A391" s="4"/>
       <c r="B391" s="5"/>
       <c r="C391" s="4"/>
@@ -8608,7 +8608,7 @@
       <c r="R391" s="4"/>
       <c r="S391" s="4"/>
     </row>
-    <row r="392" spans="1:19">
+    <row r="392" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A392" s="4"/>
       <c r="B392" s="5"/>
       <c r="C392" s="4"/>
@@ -8629,7 +8629,7 @@
       <c r="R392" s="4"/>
       <c r="S392" s="4"/>
     </row>
-    <row r="393" spans="1:19">
+    <row r="393" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A393" s="4"/>
       <c r="B393" s="5"/>
       <c r="C393" s="4"/>
@@ -8650,7 +8650,7 @@
       <c r="R393" s="4"/>
       <c r="S393" s="4"/>
     </row>
-    <row r="394" spans="1:19">
+    <row r="394" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A394" s="4"/>
       <c r="B394" s="5"/>
       <c r="C394" s="4"/>
@@ -8671,7 +8671,7 @@
       <c r="R394" s="4"/>
       <c r="S394" s="4"/>
     </row>
-    <row r="395" spans="1:19">
+    <row r="395" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A395" s="4"/>
       <c r="B395" s="5"/>
       <c r="C395" s="4"/>
@@ -8692,7 +8692,7 @@
       <c r="R395" s="4"/>
       <c r="S395" s="4"/>
     </row>
-    <row r="396" spans="1:19">
+    <row r="396" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A396" s="4"/>
       <c r="B396" s="5"/>
       <c r="C396" s="4"/>
@@ -8713,7 +8713,7 @@
       <c r="R396" s="4"/>
       <c r="S396" s="4"/>
     </row>
-    <row r="397" spans="1:19">
+    <row r="397" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A397" s="4"/>
       <c r="B397" s="5"/>
       <c r="C397" s="4"/>
@@ -8734,7 +8734,7 @@
       <c r="R397" s="4"/>
       <c r="S397" s="4"/>
     </row>
-    <row r="398" spans="1:19">
+    <row r="398" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A398" s="4"/>
       <c r="B398" s="5"/>
       <c r="C398" s="4"/>
@@ -8755,7 +8755,7 @@
       <c r="R398" s="4"/>
       <c r="S398" s="4"/>
     </row>
-    <row r="399" spans="1:19">
+    <row r="399" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A399" s="4"/>
       <c r="B399" s="5"/>
       <c r="C399" s="4"/>
@@ -8776,7 +8776,7 @@
       <c r="R399" s="4"/>
       <c r="S399" s="4"/>
     </row>
-    <row r="400" spans="1:19">
+    <row r="400" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A400" s="4"/>
       <c r="B400" s="5"/>
       <c r="C400" s="4"/>
@@ -8797,7 +8797,7 @@
       <c r="R400" s="4"/>
       <c r="S400" s="4"/>
     </row>
-    <row r="401" spans="1:19">
+    <row r="401" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A401" s="4"/>
       <c r="B401" s="5"/>
       <c r="C401" s="4"/>
@@ -8818,7 +8818,7 @@
       <c r="R401" s="4"/>
       <c r="S401" s="4"/>
     </row>
-    <row r="402" spans="1:19">
+    <row r="402" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A402" s="4"/>
       <c r="B402" s="5"/>
       <c r="C402" s="4"/>
@@ -8839,7 +8839,7 @@
       <c r="R402" s="4"/>
       <c r="S402" s="4"/>
     </row>
-    <row r="403" spans="1:19">
+    <row r="403" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A403" s="4"/>
       <c r="B403" s="5"/>
       <c r="C403" s="4"/>
@@ -8860,7 +8860,7 @@
       <c r="R403" s="4"/>
       <c r="S403" s="4"/>
     </row>
-    <row r="404" spans="1:19">
+    <row r="404" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A404" s="4"/>
       <c r="B404" s="5"/>
       <c r="C404" s="4"/>
@@ -8881,7 +8881,7 @@
       <c r="R404" s="4"/>
       <c r="S404" s="4"/>
     </row>
-    <row r="405" spans="1:19">
+    <row r="405" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A405" s="4"/>
       <c r="B405" s="5"/>
       <c r="C405" s="4"/>
@@ -8902,7 +8902,7 @@
       <c r="R405" s="4"/>
       <c r="S405" s="4"/>
     </row>
-    <row r="406" spans="1:19">
+    <row r="406" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A406" s="4"/>
       <c r="B406" s="5"/>
       <c r="C406" s="4"/>
@@ -8923,7 +8923,7 @@
       <c r="R406" s="4"/>
       <c r="S406" s="4"/>
     </row>
-    <row r="407" spans="1:19">
+    <row r="407" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A407" s="4"/>
       <c r="B407" s="5"/>
       <c r="C407" s="4"/>
@@ -8944,7 +8944,7 @@
       <c r="R407" s="4"/>
       <c r="S407" s="4"/>
     </row>
-    <row r="408" spans="1:19">
+    <row r="408" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A408" s="4"/>
       <c r="B408" s="5"/>
       <c r="C408" s="4"/>
@@ -8965,7 +8965,7 @@
       <c r="R408" s="4"/>
       <c r="S408" s="4"/>
     </row>
-    <row r="409" spans="1:19">
+    <row r="409" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A409" s="4"/>
       <c r="B409" s="5"/>
       <c r="C409" s="4"/>
@@ -8986,7 +8986,7 @@
       <c r="R409" s="4"/>
       <c r="S409" s="4"/>
     </row>
-    <row r="410" spans="1:19">
+    <row r="410" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A410" s="4"/>
       <c r="B410" s="5"/>
       <c r="C410" s="4"/>
@@ -9007,7 +9007,7 @@
       <c r="R410" s="4"/>
       <c r="S410" s="4"/>
     </row>
-    <row r="411" spans="1:19">
+    <row r="411" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A411" s="4"/>
       <c r="B411" s="5"/>
       <c r="C411" s="4"/>
@@ -9028,7 +9028,7 @@
       <c r="R411" s="4"/>
       <c r="S411" s="4"/>
     </row>
-    <row r="412" spans="1:19">
+    <row r="412" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A412" s="4"/>
       <c r="B412" s="5"/>
       <c r="C412" s="4"/>
@@ -9049,7 +9049,7 @@
       <c r="R412" s="4"/>
       <c r="S412" s="4"/>
     </row>
-    <row r="413" spans="1:19">
+    <row r="413" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A413" s="4"/>
       <c r="B413" s="5"/>
       <c r="C413" s="4"/>
@@ -9070,7 +9070,7 @@
       <c r="R413" s="4"/>
       <c r="S413" s="4"/>
     </row>
-    <row r="414" spans="1:19">
+    <row r="414" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A414" s="4"/>
       <c r="B414" s="5"/>
       <c r="C414" s="4"/>
@@ -9091,7 +9091,7 @@
       <c r="R414" s="4"/>
       <c r="S414" s="4"/>
     </row>
-    <row r="415" spans="1:19">
+    <row r="415" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A415" s="4"/>
       <c r="B415" s="5"/>
       <c r="C415" s="4"/>
@@ -9112,7 +9112,7 @@
       <c r="R415" s="4"/>
       <c r="S415" s="4"/>
     </row>
-    <row r="416" spans="1:19">
+    <row r="416" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A416" s="4"/>
       <c r="B416" s="5"/>
       <c r="C416" s="4"/>
@@ -9133,7 +9133,7 @@
       <c r="R416" s="4"/>
       <c r="S416" s="4"/>
     </row>
-    <row r="417" spans="1:19">
+    <row r="417" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A417" s="4"/>
       <c r="B417" s="5"/>
       <c r="C417" s="4"/>
@@ -9154,7 +9154,7 @@
       <c r="R417" s="4"/>
       <c r="S417" s="4"/>
     </row>
-    <row r="418" spans="1:19">
+    <row r="418" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A418" s="4"/>
       <c r="B418" s="5"/>
       <c r="C418" s="4"/>
@@ -9175,7 +9175,7 @@
       <c r="R418" s="4"/>
       <c r="S418" s="4"/>
     </row>
-    <row r="419" spans="1:19">
+    <row r="419" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A419" s="4"/>
       <c r="B419" s="5"/>
       <c r="C419" s="4"/>
@@ -9196,7 +9196,7 @@
       <c r="R419" s="4"/>
       <c r="S419" s="4"/>
     </row>
-    <row r="420" spans="1:19">
+    <row r="420" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A420" s="4"/>
       <c r="B420" s="5"/>
       <c r="C420" s="4"/>
@@ -9217,7 +9217,7 @@
       <c r="R420" s="4"/>
       <c r="S420" s="4"/>
     </row>
-    <row r="421" spans="1:19">
+    <row r="421" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A421" s="4"/>
       <c r="B421" s="5"/>
       <c r="C421" s="4"/>
@@ -9238,7 +9238,7 @@
       <c r="R421" s="4"/>
       <c r="S421" s="4"/>
     </row>
-    <row r="422" spans="1:19">
+    <row r="422" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A422" s="4"/>
       <c r="B422" s="5"/>
       <c r="C422" s="4"/>
@@ -9259,7 +9259,7 @@
       <c r="R422" s="4"/>
       <c r="S422" s="4"/>
     </row>
-    <row r="423" spans="1:19">
+    <row r="423" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A423" s="4"/>
       <c r="B423" s="5"/>
       <c r="C423" s="4"/>
@@ -9280,7 +9280,7 @@
       <c r="R423" s="4"/>
       <c r="S423" s="4"/>
     </row>
-    <row r="424" spans="1:19">
+    <row r="424" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A424" s="4"/>
       <c r="B424" s="5"/>
       <c r="C424" s="4"/>
@@ -9301,7 +9301,7 @@
       <c r="R424" s="4"/>
       <c r="S424" s="4"/>
     </row>
-    <row r="425" spans="1:19">
+    <row r="425" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A425" s="4"/>
       <c r="B425" s="5"/>
       <c r="C425" s="4"/>
@@ -9322,7 +9322,7 @@
       <c r="R425" s="4"/>
       <c r="S425" s="4"/>
     </row>
-    <row r="426" spans="1:19">
+    <row r="426" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A426" s="4"/>
       <c r="B426" s="5"/>
       <c r="C426" s="4"/>
@@ -9343,7 +9343,7 @@
       <c r="R426" s="4"/>
       <c r="S426" s="4"/>
     </row>
-    <row r="427" spans="1:19">
+    <row r="427" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A427" s="4"/>
       <c r="B427" s="5"/>
       <c r="C427" s="4"/>
@@ -9364,7 +9364,7 @@
       <c r="R427" s="4"/>
       <c r="S427" s="4"/>
     </row>
-    <row r="428" spans="1:19">
+    <row r="428" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A428" s="4"/>
       <c r="B428" s="5"/>
       <c r="C428" s="4"/>
@@ -9385,7 +9385,7 @@
       <c r="R428" s="4"/>
       <c r="S428" s="4"/>
     </row>
-    <row r="429" spans="1:19">
+    <row r="429" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A429" s="4"/>
       <c r="B429" s="5"/>
       <c r="C429" s="4"/>
@@ -9406,7 +9406,7 @@
       <c r="R429" s="4"/>
       <c r="S429" s="4"/>
     </row>
-    <row r="430" spans="1:19">
+    <row r="430" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A430" s="4"/>
       <c r="B430" s="5"/>
       <c r="C430" s="4"/>
@@ -9427,7 +9427,7 @@
       <c r="R430" s="4"/>
       <c r="S430" s="4"/>
     </row>
-    <row r="431" spans="1:19">
+    <row r="431" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A431" s="4"/>
       <c r="B431" s="5"/>
       <c r="C431" s="4"/>
@@ -9448,7 +9448,7 @@
       <c r="R431" s="4"/>
       <c r="S431" s="4"/>
     </row>
-    <row r="432" spans="1:19">
+    <row r="432" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A432" s="4"/>
       <c r="B432" s="5"/>
       <c r="C432" s="4"/>
@@ -9469,7 +9469,7 @@
       <c r="R432" s="4"/>
       <c r="S432" s="4"/>
     </row>
-    <row r="433" spans="1:19">
+    <row r="433" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A433" s="4"/>
       <c r="B433" s="5"/>
       <c r="C433" s="4"/>
@@ -9490,7 +9490,7 @@
       <c r="R433" s="4"/>
       <c r="S433" s="4"/>
     </row>
-    <row r="434" spans="1:19">
+    <row r="434" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A434" s="4"/>
       <c r="B434" s="5"/>
       <c r="C434" s="4"/>
@@ -9511,7 +9511,7 @@
       <c r="R434" s="4"/>
       <c r="S434" s="4"/>
     </row>
-    <row r="435" spans="1:19">
+    <row r="435" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A435" s="4"/>
       <c r="B435" s="5"/>
       <c r="C435" s="4"/>
@@ -9532,7 +9532,7 @@
       <c r="R435" s="4"/>
       <c r="S435" s="4"/>
     </row>
-    <row r="436" spans="1:19">
+    <row r="436" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A436" s="4"/>
       <c r="B436" s="5"/>
       <c r="C436" s="4"/>
@@ -9553,7 +9553,7 @@
       <c r="R436" s="4"/>
       <c r="S436" s="4"/>
     </row>
-    <row r="437" spans="1:19">
+    <row r="437" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A437" s="4"/>
       <c r="B437" s="5"/>
       <c r="C437" s="4"/>
@@ -9574,7 +9574,7 @@
       <c r="R437" s="4"/>
       <c r="S437" s="4"/>
     </row>
-    <row r="438" spans="1:19">
+    <row r="438" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A438" s="4"/>
       <c r="B438" s="5"/>
       <c r="C438" s="4"/>
@@ -9595,7 +9595,7 @@
       <c r="R438" s="4"/>
       <c r="S438" s="4"/>
     </row>
-    <row r="439" spans="1:19">
+    <row r="439" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A439" s="4"/>
       <c r="B439" s="5"/>
       <c r="C439" s="4"/>
@@ -9616,7 +9616,7 @@
       <c r="R439" s="4"/>
       <c r="S439" s="4"/>
     </row>
-    <row r="440" spans="1:19">
+    <row r="440" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A440" s="4"/>
       <c r="B440" s="5"/>
       <c r="C440" s="4"/>
@@ -9637,7 +9637,7 @@
       <c r="R440" s="4"/>
       <c r="S440" s="4"/>
     </row>
-    <row r="441" spans="1:19">
+    <row r="441" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A441" s="4"/>
       <c r="B441" s="5"/>
       <c r="C441" s="4"/>
@@ -9658,7 +9658,7 @@
       <c r="R441" s="4"/>
       <c r="S441" s="4"/>
     </row>
-    <row r="442" spans="1:19">
+    <row r="442" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A442" s="4"/>
       <c r="B442" s="5"/>
       <c r="C442" s="4"/>
@@ -9679,7 +9679,7 @@
       <c r="R442" s="4"/>
       <c r="S442" s="4"/>
     </row>
-    <row r="443" spans="1:19">
+    <row r="443" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A443" s="4"/>
       <c r="B443" s="5"/>
       <c r="C443" s="4"/>
@@ -9700,7 +9700,7 @@
       <c r="R443" s="4"/>
       <c r="S443" s="4"/>
     </row>
-    <row r="444" spans="1:19">
+    <row r="444" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A444" s="4"/>
       <c r="B444" s="5"/>
       <c r="C444" s="4"/>
@@ -9721,7 +9721,7 @@
       <c r="R444" s="4"/>
       <c r="S444" s="4"/>
     </row>
-    <row r="445" spans="1:19">
+    <row r="445" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A445" s="4"/>
       <c r="B445" s="5"/>
       <c r="C445" s="4"/>
@@ -9742,7 +9742,7 @@
       <c r="R445" s="4"/>
       <c r="S445" s="4"/>
     </row>
-    <row r="446" spans="1:19">
+    <row r="446" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A446" s="4"/>
       <c r="B446" s="5"/>
       <c r="C446" s="4"/>
@@ -9763,7 +9763,7 @@
       <c r="R446" s="4"/>
       <c r="S446" s="4"/>
     </row>
-    <row r="447" spans="1:19">
+    <row r="447" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A447" s="4"/>
       <c r="B447" s="5"/>
       <c r="C447" s="4"/>
@@ -9784,7 +9784,7 @@
       <c r="R447" s="4"/>
       <c r="S447" s="4"/>
     </row>
-    <row r="448" spans="1:19">
+    <row r="448" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A448" s="4"/>
       <c r="B448" s="5"/>
       <c r="C448" s="4"/>
@@ -9805,7 +9805,7 @@
       <c r="R448" s="4"/>
       <c r="S448" s="4"/>
     </row>
-    <row r="449" spans="1:19">
+    <row r="449" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A449" s="4"/>
       <c r="B449" s="5"/>
       <c r="C449" s="4"/>
@@ -9826,7 +9826,7 @@
       <c r="R449" s="4"/>
       <c r="S449" s="4"/>
     </row>
-    <row r="450" spans="1:19">
+    <row r="450" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A450" s="4"/>
       <c r="B450" s="5"/>
       <c r="C450" s="4"/>
@@ -9847,7 +9847,7 @@
       <c r="R450" s="4"/>
       <c r="S450" s="4"/>
     </row>
-    <row r="451" spans="1:19">
+    <row r="451" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A451" s="4"/>
       <c r="B451" s="5"/>
       <c r="C451" s="4"/>
@@ -9868,7 +9868,7 @@
       <c r="R451" s="4"/>
       <c r="S451" s="4"/>
     </row>
-    <row r="452" spans="1:19">
+    <row r="452" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A452" s="4"/>
       <c r="B452" s="5"/>
       <c r="C452" s="4"/>
@@ -9889,7 +9889,7 @@
       <c r="R452" s="4"/>
       <c r="S452" s="4"/>
     </row>
-    <row r="453" spans="1:19">
+    <row r="453" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A453" s="4"/>
       <c r="B453" s="5"/>
       <c r="C453" s="4"/>
@@ -9910,7 +9910,7 @@
       <c r="R453" s="4"/>
       <c r="S453" s="4"/>
     </row>
-    <row r="454" spans="1:19">
+    <row r="454" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A454" s="4"/>
       <c r="B454" s="5"/>
       <c r="C454" s="4"/>
@@ -9931,7 +9931,7 @@
       <c r="R454" s="4"/>
       <c r="S454" s="4"/>
     </row>
-    <row r="455" spans="1:19">
+    <row r="455" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A455" s="4"/>
       <c r="B455" s="5"/>
       <c r="C455" s="4"/>
@@ -9952,7 +9952,7 @@
       <c r="R455" s="4"/>
       <c r="S455" s="4"/>
     </row>
-    <row r="456" spans="1:19">
+    <row r="456" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A456" s="4"/>
       <c r="B456" s="5"/>
       <c r="C456" s="4"/>
@@ -9973,7 +9973,7 @@
       <c r="R456" s="4"/>
       <c r="S456" s="4"/>
     </row>
-    <row r="457" spans="1:19">
+    <row r="457" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A457" s="4"/>
       <c r="B457" s="5"/>
       <c r="C457" s="4"/>
@@ -9994,7 +9994,7 @@
       <c r="R457" s="4"/>
       <c r="S457" s="4"/>
     </row>
-    <row r="458" spans="1:19">
+    <row r="458" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A458" s="4"/>
       <c r="B458" s="5"/>
       <c r="C458" s="4"/>
@@ -10015,7 +10015,7 @@
       <c r="R458" s="4"/>
       <c r="S458" s="4"/>
     </row>
-    <row r="459" spans="1:19">
+    <row r="459" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A459" s="4"/>
       <c r="B459" s="5"/>
       <c r="C459" s="4"/>
@@ -10036,7 +10036,7 @@
       <c r="R459" s="4"/>
       <c r="S459" s="4"/>
     </row>
-    <row r="460" spans="1:19">
+    <row r="460" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A460" s="4"/>
       <c r="B460" s="5"/>
       <c r="C460" s="4"/>
@@ -10057,7 +10057,7 @@
       <c r="R460" s="4"/>
       <c r="S460" s="4"/>
     </row>
-    <row r="461" spans="1:19">
+    <row r="461" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A461" s="4"/>
       <c r="B461" s="5"/>
       <c r="C461" s="4"/>
@@ -10078,7 +10078,7 @@
       <c r="R461" s="4"/>
       <c r="S461" s="4"/>
     </row>
-    <row r="462" spans="1:19">
+    <row r="462" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A462" s="4"/>
       <c r="B462" s="5"/>
       <c r="C462" s="4"/>
@@ -10099,7 +10099,7 @@
       <c r="R462" s="4"/>
       <c r="S462" s="4"/>
     </row>
-    <row r="463" spans="1:19">
+    <row r="463" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A463" s="4"/>
       <c r="B463" s="5"/>
       <c r="C463" s="4"/>
@@ -10120,7 +10120,7 @@
       <c r="R463" s="4"/>
       <c r="S463" s="4"/>
     </row>
-    <row r="464" spans="1:19">
+    <row r="464" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A464" s="4"/>
       <c r="B464" s="5"/>
       <c r="C464" s="4"/>
@@ -10141,7 +10141,7 @@
       <c r="R464" s="4"/>
       <c r="S464" s="4"/>
     </row>
-    <row r="465" spans="1:19">
+    <row r="465" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A465" s="4"/>
       <c r="B465" s="5"/>
       <c r="C465" s="4"/>
@@ -10162,7 +10162,7 @@
       <c r="R465" s="4"/>
       <c r="S465" s="4"/>
     </row>
-    <row r="466" spans="1:19">
+    <row r="466" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A466" s="4"/>
       <c r="B466" s="5"/>
       <c r="C466" s="4"/>
@@ -10183,7 +10183,7 @@
       <c r="R466" s="4"/>
       <c r="S466" s="4"/>
     </row>
-    <row r="467" spans="1:19">
+    <row r="467" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A467" s="4"/>
       <c r="B467" s="5"/>
       <c r="C467" s="4"/>
@@ -10204,7 +10204,7 @@
       <c r="R467" s="4"/>
       <c r="S467" s="4"/>
     </row>
-    <row r="468" spans="1:19">
+    <row r="468" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A468" s="4"/>
       <c r="B468" s="5"/>
       <c r="C468" s="4"/>
@@ -10225,7 +10225,7 @@
       <c r="R468" s="4"/>
       <c r="S468" s="4"/>
     </row>
-    <row r="469" spans="1:19">
+    <row r="469" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A469" s="4"/>
       <c r="B469" s="5"/>
       <c r="C469" s="4"/>
@@ -10246,7 +10246,7 @@
       <c r="R469" s="4"/>
       <c r="S469" s="4"/>
     </row>
-    <row r="470" spans="1:19">
+    <row r="470" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A470" s="4"/>
       <c r="B470" s="5"/>
       <c r="C470" s="4"/>
@@ -10267,7 +10267,7 @@
       <c r="R470" s="4"/>
       <c r="S470" s="4"/>
     </row>
-    <row r="471" spans="1:19">
+    <row r="471" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A471" s="4"/>
       <c r="B471" s="5"/>
       <c r="C471" s="4"/>
@@ -10288,7 +10288,7 @@
       <c r="R471" s="4"/>
       <c r="S471" s="4"/>
     </row>
-    <row r="472" spans="1:19">
+    <row r="472" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A472" s="4"/>
       <c r="B472" s="5"/>
       <c r="C472" s="4"/>
@@ -10309,7 +10309,7 @@
       <c r="R472" s="4"/>
       <c r="S472" s="4"/>
     </row>
-    <row r="473" spans="1:19">
+    <row r="473" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A473" s="4"/>
       <c r="B473" s="5"/>
       <c r="C473" s="4"/>
@@ -10330,7 +10330,7 @@
       <c r="R473" s="4"/>
       <c r="S473" s="4"/>
     </row>
-    <row r="474" spans="1:19">
+    <row r="474" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A474" s="4"/>
       <c r="B474" s="5"/>
       <c r="C474" s="4"/>
@@ -10351,7 +10351,7 @@
       <c r="R474" s="4"/>
       <c r="S474" s="4"/>
     </row>
-    <row r="475" spans="1:19">
+    <row r="475" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A475" s="4"/>
       <c r="B475" s="5"/>
       <c r="C475" s="4"/>
@@ -10372,7 +10372,7 @@
       <c r="R475" s="4"/>
       <c r="S475" s="4"/>
     </row>
-    <row r="476" spans="1:19">
+    <row r="476" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A476" s="4"/>
       <c r="B476" s="5"/>
       <c r="C476" s="4"/>
@@ -10393,7 +10393,7 @@
       <c r="R476" s="4"/>
       <c r="S476" s="4"/>
     </row>
-    <row r="477" spans="1:19">
+    <row r="477" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A477" s="4"/>
       <c r="B477" s="5"/>
       <c r="C477" s="4"/>
@@ -10414,7 +10414,7 @@
       <c r="R477" s="4"/>
       <c r="S477" s="4"/>
     </row>
-    <row r="478" spans="1:19">
+    <row r="478" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A478" s="4"/>
       <c r="B478" s="5"/>
       <c r="C478" s="4"/>
@@ -10435,7 +10435,7 @@
       <c r="R478" s="4"/>
       <c r="S478" s="4"/>
     </row>
-    <row r="479" spans="1:19">
+    <row r="479" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A479" s="4"/>
       <c r="B479" s="5"/>
       <c r="C479" s="4"/>
@@ -10456,7 +10456,7 @@
       <c r="R479" s="4"/>
       <c r="S479" s="4"/>
     </row>
-    <row r="480" spans="1:19">
+    <row r="480" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A480" s="4"/>
       <c r="B480" s="5"/>
       <c r="C480" s="4"/>
@@ -10477,7 +10477,7 @@
       <c r="R480" s="4"/>
       <c r="S480" s="4"/>
     </row>
-    <row r="481" spans="1:19">
+    <row r="481" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A481" s="4"/>
       <c r="B481" s="5"/>
       <c r="C481" s="4"/>
@@ -10498,7 +10498,7 @@
       <c r="R481" s="4"/>
       <c r="S481" s="4"/>
     </row>
-    <row r="482" spans="1:19">
+    <row r="482" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A482" s="4"/>
       <c r="B482" s="5"/>
       <c r="C482" s="4"/>
@@ -10519,7 +10519,7 @@
       <c r="R482" s="4"/>
       <c r="S482" s="4"/>
     </row>
-    <row r="483" spans="1:19">
+    <row r="483" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A483" s="4"/>
       <c r="B483" s="5"/>
       <c r="C483" s="4"/>
@@ -10540,7 +10540,7 @@
       <c r="R483" s="4"/>
       <c r="S483" s="4"/>
     </row>
-    <row r="484" spans="1:19">
+    <row r="484" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A484" s="4"/>
       <c r="B484" s="5"/>
       <c r="C484" s="4"/>
@@ -10561,7 +10561,7 @@
       <c r="R484" s="4"/>
       <c r="S484" s="4"/>
     </row>
-    <row r="485" spans="1:19">
+    <row r="485" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A485" s="4"/>
       <c r="B485" s="5"/>
       <c r="C485" s="4"/>
@@ -10582,7 +10582,7 @@
       <c r="R485" s="4"/>
       <c r="S485" s="4"/>
     </row>
-    <row r="486" spans="1:19">
+    <row r="486" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A486" s="4"/>
       <c r="B486" s="5"/>
       <c r="C486" s="4"/>
@@ -10603,7 +10603,7 @@
       <c r="R486" s="4"/>
       <c r="S486" s="4"/>
     </row>
-    <row r="487" spans="1:19">
+    <row r="487" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A487" s="4"/>
       <c r="B487" s="5"/>
       <c r="C487" s="4"/>
@@ -10624,7 +10624,7 @@
       <c r="R487" s="4"/>
       <c r="S487" s="4"/>
     </row>
-    <row r="488" spans="1:19">
+    <row r="488" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A488" s="4"/>
       <c r="B488" s="5"/>
       <c r="C488" s="4"/>
@@ -10645,7 +10645,7 @@
       <c r="R488" s="4"/>
       <c r="S488" s="4"/>
     </row>
-    <row r="489" spans="1:19">
+    <row r="489" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A489" s="4"/>
       <c r="B489" s="5"/>
       <c r="C489" s="4"/>
@@ -10666,7 +10666,7 @@
       <c r="R489" s="4"/>
       <c r="S489" s="4"/>
     </row>
-    <row r="490" spans="1:19">
+    <row r="490" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A490" s="4"/>
       <c r="B490" s="5"/>
       <c r="C490" s="4"/>
@@ -10687,7 +10687,7 @@
       <c r="R490" s="4"/>
       <c r="S490" s="4"/>
     </row>
-    <row r="491" spans="1:19">
+    <row r="491" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A491" s="4"/>
       <c r="B491" s="5"/>
       <c r="C491" s="4"/>
@@ -10708,7 +10708,7 @@
       <c r="R491" s="4"/>
       <c r="S491" s="4"/>
     </row>
-    <row r="492" spans="1:19">
+    <row r="492" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A492" s="4"/>
       <c r="B492" s="5"/>
       <c r="C492" s="4"/>
@@ -10729,7 +10729,7 @@
       <c r="R492" s="4"/>
       <c r="S492" s="4"/>
     </row>
-    <row r="493" spans="1:19">
+    <row r="493" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A493" s="4"/>
       <c r="B493" s="5"/>
       <c r="C493" s="4"/>
@@ -10750,7 +10750,7 @@
       <c r="R493" s="4"/>
       <c r="S493" s="4"/>
     </row>
-    <row r="494" spans="1:19">
+    <row r="494" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A494" s="4"/>
       <c r="B494" s="5"/>
       <c r="C494" s="4"/>
@@ -10771,7 +10771,7 @@
       <c r="R494" s="4"/>
       <c r="S494" s="4"/>
     </row>
-    <row r="495" spans="1:19">
+    <row r="495" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A495" s="4"/>
       <c r="B495" s="5"/>
       <c r="C495" s="4"/>
@@ -10792,7 +10792,7 @@
       <c r="R495" s="4"/>
       <c r="S495" s="4"/>
     </row>
-    <row r="496" spans="1:19">
+    <row r="496" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A496" s="4"/>
       <c r="B496" s="5"/>
       <c r="C496" s="4"/>
@@ -10813,7 +10813,7 @@
       <c r="R496" s="4"/>
       <c r="S496" s="4"/>
     </row>
-    <row r="497" spans="1:19">
+    <row r="497" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A497" s="4"/>
       <c r="B497" s="5"/>
       <c r="C497" s="4"/>
@@ -10834,7 +10834,7 @@
       <c r="R497" s="4"/>
       <c r="S497" s="4"/>
     </row>
-    <row r="498" spans="1:19">
+    <row r="498" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A498" s="4"/>
       <c r="B498" s="5"/>
       <c r="C498" s="4"/>
@@ -10855,7 +10855,7 @@
       <c r="R498" s="4"/>
       <c r="S498" s="4"/>
     </row>
-    <row r="499" spans="1:19">
+    <row r="499" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A499" s="4"/>
       <c r="B499" s="5"/>
       <c r="C499" s="4"/>
@@ -10876,7 +10876,7 @@
       <c r="R499" s="4"/>
       <c r="S499" s="4"/>
     </row>
-    <row r="500" spans="1:19">
+    <row r="500" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A500" s="4"/>
       <c r="B500" s="5"/>
       <c r="C500" s="4"/>
@@ -10897,7 +10897,7 @@
       <c r="R500" s="4"/>
       <c r="S500" s="4"/>
     </row>
-    <row r="501" spans="1:19">
+    <row r="501" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A501" s="4"/>
       <c r="B501" s="5"/>
       <c r="C501" s="4"/>
@@ -10918,7 +10918,7 @@
       <c r="R501" s="4"/>
       <c r="S501" s="4"/>
     </row>
-    <row r="502" spans="1:19">
+    <row r="502" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A502" s="4"/>
       <c r="B502" s="5"/>
       <c r="C502" s="4"/>
@@ -10939,7 +10939,7 @@
       <c r="R502" s="4"/>
       <c r="S502" s="4"/>
     </row>
-    <row r="503" spans="1:19">
+    <row r="503" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A503" s="4"/>
       <c r="B503" s="5"/>
       <c r="C503" s="4"/>
@@ -10960,7 +10960,7 @@
       <c r="R503" s="4"/>
       <c r="S503" s="4"/>
     </row>
-    <row r="504" spans="1:19">
+    <row r="504" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A504" s="4"/>
       <c r="B504" s="5"/>
       <c r="C504" s="4"/>
@@ -10981,7 +10981,7 @@
       <c r="R504" s="4"/>
       <c r="S504" s="4"/>
     </row>
-    <row r="505" spans="1:19">
+    <row r="505" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A505" s="4"/>
       <c r="B505" s="5"/>
       <c r="C505" s="4"/>
@@ -11002,7 +11002,7 @@
       <c r="R505" s="4"/>
       <c r="S505" s="4"/>
     </row>
-    <row r="506" spans="1:19">
+    <row r="506" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A506" s="4"/>
       <c r="B506" s="5"/>
       <c r="C506" s="4"/>
@@ -11023,7 +11023,7 @@
       <c r="R506" s="4"/>
       <c r="S506" s="4"/>
     </row>
-    <row r="507" spans="1:19">
+    <row r="507" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A507" s="4"/>
       <c r="B507" s="5"/>
       <c r="C507" s="4"/>
@@ -11044,7 +11044,7 @@
       <c r="R507" s="4"/>
       <c r="S507" s="4"/>
     </row>
-    <row r="508" spans="1:19">
+    <row r="508" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A508" s="4"/>
       <c r="B508" s="5"/>
       <c r="C508" s="4"/>
@@ -11065,7 +11065,7 @@
       <c r="R508" s="4"/>
       <c r="S508" s="4"/>
     </row>
-    <row r="509" spans="1:19">
+    <row r="509" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A509" s="4"/>
       <c r="B509" s="5"/>
       <c r="C509" s="4"/>
@@ -11086,7 +11086,7 @@
       <c r="R509" s="4"/>
       <c r="S509" s="4"/>
     </row>
-    <row r="510" spans="1:19">
+    <row r="510" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A510" s="4"/>
       <c r="B510" s="5"/>
       <c r="C510" s="4"/>
@@ -11107,7 +11107,7 @@
       <c r="R510" s="4"/>
       <c r="S510" s="4"/>
     </row>
-    <row r="511" spans="1:19">
+    <row r="511" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A511" s="4"/>
       <c r="B511" s="5"/>
       <c r="C511" s="4"/>
@@ -11128,7 +11128,7 @@
       <c r="R511" s="4"/>
       <c r="S511" s="4"/>
     </row>
-    <row r="512" spans="1:19">
+    <row r="512" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A512" s="4"/>
       <c r="B512" s="5"/>
       <c r="C512" s="4"/>
@@ -11149,7 +11149,7 @@
       <c r="R512" s="4"/>
       <c r="S512" s="4"/>
     </row>
-    <row r="513" spans="1:19">
+    <row r="513" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A513" s="4"/>
       <c r="B513" s="5"/>
       <c r="C513" s="4"/>
@@ -11170,7 +11170,7 @@
       <c r="R513" s="4"/>
       <c r="S513" s="4"/>
     </row>
-    <row r="514" spans="1:19">
+    <row r="514" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A514" s="4"/>
       <c r="B514" s="5"/>
       <c r="C514" s="4"/>
@@ -11191,7 +11191,7 @@
       <c r="R514" s="4"/>
       <c r="S514" s="4"/>
     </row>
-    <row r="515" spans="1:19">
+    <row r="515" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A515" s="4"/>
       <c r="B515" s="5"/>
       <c r="C515" s="4"/>
@@ -11212,7 +11212,7 @@
       <c r="R515" s="4"/>
       <c r="S515" s="4"/>
     </row>
-    <row r="516" spans="1:19">
+    <row r="516" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A516" s="4"/>
       <c r="B516" s="5"/>
       <c r="C516" s="4"/>
@@ -11233,7 +11233,7 @@
       <c r="R516" s="4"/>
       <c r="S516" s="4"/>
     </row>
-    <row r="517" spans="1:19">
+    <row r="517" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A517" s="4"/>
       <c r="B517" s="5"/>
       <c r="C517" s="4"/>
@@ -11254,7 +11254,7 @@
       <c r="R517" s="4"/>
       <c r="S517" s="4"/>
     </row>
-    <row r="518" spans="1:19">
+    <row r="518" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A518" s="4"/>
       <c r="B518" s="5"/>
       <c r="C518" s="4"/>
@@ -11275,7 +11275,7 @@
       <c r="R518" s="4"/>
       <c r="S518" s="4"/>
     </row>
-    <row r="519" spans="1:19">
+    <row r="519" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A519" s="4"/>
       <c r="B519" s="5"/>
       <c r="C519" s="4"/>
@@ -11296,7 +11296,7 @@
       <c r="R519" s="4"/>
       <c r="S519" s="4"/>
     </row>
-    <row r="520" spans="1:19">
+    <row r="520" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A520" s="4"/>
       <c r="B520" s="5"/>
       <c r="C520" s="4"/>
@@ -11317,7 +11317,7 @@
       <c r="R520" s="4"/>
       <c r="S520" s="4"/>
     </row>
-    <row r="521" spans="1:19">
+    <row r="521" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A521" s="4"/>
       <c r="B521" s="5"/>
       <c r="C521" s="4"/>
@@ -11338,7 +11338,7 @@
       <c r="R521" s="4"/>
       <c r="S521" s="4"/>
     </row>
-    <row r="522" spans="1:19">
+    <row r="522" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A522" s="4"/>
       <c r="B522" s="5"/>
       <c r="C522" s="4"/>
@@ -11359,7 +11359,7 @@
       <c r="R522" s="4"/>
       <c r="S522" s="4"/>
     </row>
-    <row r="523" spans="1:19">
+    <row r="523" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A523" s="4"/>
       <c r="B523" s="5"/>
       <c r="C523" s="4"/>
@@ -11380,7 +11380,7 @@
       <c r="R523" s="4"/>
       <c r="S523" s="4"/>
     </row>
-    <row r="524" spans="1:19">
+    <row r="524" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A524" s="4"/>
       <c r="B524" s="5"/>
       <c r="C524" s="4"/>
@@ -11401,7 +11401,7 @@
       <c r="R524" s="4"/>
       <c r="S524" s="4"/>
     </row>
-    <row r="525" spans="1:19">
+    <row r="525" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A525" s="4"/>
       <c r="B525" s="5"/>
       <c r="C525" s="4"/>
@@ -11422,7 +11422,7 @@
       <c r="R525" s="4"/>
       <c r="S525" s="4"/>
     </row>
-    <row r="526" spans="1:19">
+    <row r="526" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A526" s="4"/>
       <c r="B526" s="5"/>
       <c r="C526" s="4"/>
@@ -11443,7 +11443,7 @@
       <c r="R526" s="4"/>
       <c r="S526" s="4"/>
     </row>
-    <row r="527" spans="1:19">
+    <row r="527" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A527" s="4"/>
       <c r="B527" s="5"/>
       <c r="C527" s="4"/>
@@ -11464,7 +11464,7 @@
       <c r="R527" s="4"/>
       <c r="S527" s="4"/>
     </row>
-    <row r="528" spans="1:19">
+    <row r="528" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A528" s="4"/>
       <c r="B528" s="5"/>
       <c r="C528" s="4"/>
@@ -11485,7 +11485,7 @@
       <c r="R528" s="4"/>
       <c r="S528" s="4"/>
     </row>
-    <row r="529" spans="1:19">
+    <row r="529" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A529" s="4"/>
       <c r="B529" s="5"/>
       <c r="C529" s="4"/>
@@ -11506,7 +11506,7 @@
       <c r="R529" s="4"/>
       <c r="S529" s="4"/>
     </row>
-    <row r="530" spans="1:19">
+    <row r="530" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A530" s="4"/>
       <c r="B530" s="5"/>
       <c r="C530" s="4"/>
@@ -11527,7 +11527,7 @@
       <c r="R530" s="4"/>
       <c r="S530" s="4"/>
     </row>
-    <row r="531" spans="1:19">
+    <row r="531" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A531" s="4"/>
       <c r="B531" s="5"/>
       <c r="C531" s="4"/>
@@ -11548,7 +11548,7 @@
       <c r="R531" s="4"/>
       <c r="S531" s="4"/>
     </row>
-    <row r="532" spans="1:19">
+    <row r="532" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A532" s="4"/>
       <c r="B532" s="5"/>
       <c r="C532" s="4"/>
@@ -11569,7 +11569,7 @@
       <c r="R532" s="4"/>
       <c r="S532" s="4"/>
     </row>
-    <row r="533" spans="1:19">
+    <row r="533" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A533" s="4"/>
       <c r="B533" s="5"/>
       <c r="C533" s="4"/>
@@ -11590,7 +11590,7 @@
       <c r="R533" s="4"/>
       <c r="S533" s="4"/>
     </row>
-    <row r="534" spans="1:19">
+    <row r="534" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A534" s="4"/>
       <c r="B534" s="5"/>
       <c r="C534" s="4"/>
@@ -11611,7 +11611,7 @@
       <c r="R534" s="4"/>
       <c r="S534" s="4"/>
     </row>
-    <row r="535" spans="1:19">
+    <row r="535" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A535" s="4"/>
       <c r="B535" s="5"/>
       <c r="C535" s="4"/>
@@ -11632,7 +11632,7 @@
       <c r="R535" s="4"/>
       <c r="S535" s="4"/>
     </row>
-    <row r="536" spans="1:19">
+    <row r="536" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A536" s="4"/>
       <c r="B536" s="5"/>
       <c r="C536" s="4"/>
@@ -11653,7 +11653,7 @@
       <c r="R536" s="4"/>
       <c r="S536" s="4"/>
     </row>
-    <row r="537" spans="1:19">
+    <row r="537" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A537" s="4"/>
       <c r="B537" s="5"/>
       <c r="C537" s="4"/>
@@ -11674,7 +11674,7 @@
       <c r="R537" s="4"/>
       <c r="S537" s="4"/>
     </row>
-    <row r="538" spans="1:19">
+    <row r="538" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A538" s="4"/>
       <c r="B538" s="5"/>
       <c r="C538" s="4"/>
@@ -11695,7 +11695,7 @@
       <c r="R538" s="4"/>
       <c r="S538" s="4"/>
     </row>
-    <row r="539" spans="1:19">
+    <row r="539" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A539" s="4"/>
       <c r="B539" s="5"/>
       <c r="C539" s="4"/>
@@ -11716,7 +11716,7 @@
       <c r="R539" s="4"/>
       <c r="S539" s="4"/>
     </row>
-    <row r="540" spans="1:19">
+    <row r="540" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A540" s="4"/>
       <c r="B540" s="5"/>
       <c r="C540" s="4"/>
@@ -11737,7 +11737,7 @@
       <c r="R540" s="4"/>
       <c r="S540" s="4"/>
     </row>
-    <row r="541" spans="1:19">
+    <row r="541" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A541" s="4"/>
       <c r="B541" s="5"/>
       <c r="C541" s="4"/>
@@ -11758,7 +11758,7 @@
       <c r="R541" s="4"/>
       <c r="S541" s="4"/>
     </row>
-    <row r="542" spans="1:19">
+    <row r="542" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A542" s="4"/>
       <c r="B542" s="5"/>
       <c r="C542" s="4"/>
@@ -11779,7 +11779,7 @@
       <c r="R542" s="4"/>
       <c r="S542" s="4"/>
     </row>
-    <row r="543" spans="1:19">
+    <row r="543" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A543" s="4"/>
       <c r="B543" s="5"/>
       <c r="C543" s="4"/>
@@ -11800,7 +11800,7 @@
       <c r="R543" s="4"/>
       <c r="S543" s="4"/>
     </row>
-    <row r="544" spans="1:19">
+    <row r="544" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A544" s="4"/>
       <c r="B544" s="5"/>
       <c r="C544" s="4"/>
@@ -11821,7 +11821,7 @@
       <c r="R544" s="4"/>
       <c r="S544" s="4"/>
     </row>
-    <row r="545" spans="1:19">
+    <row r="545" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A545" s="4"/>
       <c r="B545" s="5"/>
       <c r="C545" s="4"/>
@@ -11842,7 +11842,7 @@
       <c r="R545" s="4"/>
       <c r="S545" s="4"/>
     </row>
-    <row r="546" spans="1:19">
+    <row r="546" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A546" s="4"/>
       <c r="B546" s="5"/>
       <c r="C546" s="4"/>
@@ -11863,7 +11863,7 @@
       <c r="R546" s="4"/>
       <c r="S546" s="4"/>
     </row>
-    <row r="547" spans="1:19">
+    <row r="547" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A547" s="4"/>
       <c r="B547" s="5"/>
       <c r="C547" s="4"/>
@@ -11884,7 +11884,7 @@
       <c r="R547" s="4"/>
       <c r="S547" s="4"/>
     </row>
-    <row r="548" spans="1:19">
+    <row r="548" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A548" s="4"/>
       <c r="B548" s="5"/>
       <c r="C548" s="4"/>
@@ -11905,7 +11905,7 @@
       <c r="R548" s="4"/>
       <c r="S548" s="4"/>
     </row>
-    <row r="549" spans="1:19">
+    <row r="549" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A549" s="4"/>
       <c r="B549" s="5"/>
       <c r="C549" s="4"/>
@@ -11926,7 +11926,7 @@
       <c r="R549" s="4"/>
       <c r="S549" s="4"/>
     </row>
-    <row r="550" spans="1:19">
+    <row r="550" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A550" s="4"/>
       <c r="B550" s="5"/>
       <c r="C550" s="4"/>
@@ -11947,7 +11947,7 @@
       <c r="R550" s="4"/>
       <c r="S550" s="4"/>
     </row>
-    <row r="551" spans="1:19">
+    <row r="551" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A551" s="4"/>
       <c r="B551" s="5"/>
       <c r="C551" s="4"/>
@@ -11968,7 +11968,7 @@
       <c r="R551" s="4"/>
       <c r="S551" s="4"/>
     </row>
-    <row r="552" spans="1:19">
+    <row r="552" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A552" s="4"/>
       <c r="B552" s="5"/>
       <c r="C552" s="4"/>
@@ -11989,7 +11989,7 @@
       <c r="R552" s="4"/>
       <c r="S552" s="4"/>
     </row>
-    <row r="553" spans="1:19">
+    <row r="553" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A553" s="4"/>
       <c r="B553" s="5"/>
       <c r="C553" s="4"/>
@@ -12010,7 +12010,7 @@
       <c r="R553" s="4"/>
       <c r="S553" s="4"/>
     </row>
-    <row r="554" spans="1:19">
+    <row r="554" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A554" s="4"/>
       <c r="B554" s="5"/>
       <c r="C554" s="4"/>
@@ -12031,7 +12031,7 @@
       <c r="R554" s="4"/>
       <c r="S554" s="4"/>
     </row>
-    <row r="555" spans="1:19">
+    <row r="555" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A555" s="4"/>
       <c r="B555" s="5"/>
       <c r="C555" s="4"/>
@@ -12052,7 +12052,7 @@
       <c r="R555" s="4"/>
       <c r="S555" s="4"/>
     </row>
-    <row r="556" spans="1:19">
+    <row r="556" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A556" s="4"/>
       <c r="B556" s="5"/>
       <c r="C556" s="4"/>
@@ -12073,7 +12073,7 @@
       <c r="R556" s="4"/>
       <c r="S556" s="4"/>
     </row>
-    <row r="557" spans="1:19">
+    <row r="557" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A557" s="4"/>
       <c r="B557" s="5"/>
       <c r="C557" s="4"/>
@@ -12094,7 +12094,7 @@
       <c r="R557" s="4"/>
       <c r="S557" s="4"/>
     </row>
-    <row r="558" spans="1:19">
+    <row r="558" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A558" s="4"/>
       <c r="B558" s="5"/>
       <c r="C558" s="4"/>
@@ -12115,7 +12115,7 @@
       <c r="R558" s="4"/>
       <c r="S558" s="4"/>
     </row>
-    <row r="559" spans="1:19">
+    <row r="559" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A559" s="4"/>
       <c r="B559" s="5"/>
       <c r="C559" s="4"/>
@@ -12136,7 +12136,7 @@
       <c r="R559" s="4"/>
       <c r="S559" s="4"/>
     </row>
-    <row r="560" spans="1:19">
+    <row r="560" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A560" s="4"/>
       <c r="B560" s="5"/>
       <c r="C560" s="4"/>
@@ -12157,7 +12157,7 @@
       <c r="R560" s="4"/>
       <c r="S560" s="4"/>
     </row>
-    <row r="561" spans="1:19">
+    <row r="561" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A561" s="4"/>
       <c r="B561" s="5"/>
       <c r="C561" s="4"/>
@@ -12178,7 +12178,7 @@
       <c r="R561" s="4"/>
       <c r="S561" s="4"/>
     </row>
-    <row r="562" spans="1:19">
+    <row r="562" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A562" s="4"/>
       <c r="B562" s="5"/>
       <c r="C562" s="4"/>
@@ -12199,7 +12199,7 @@
       <c r="R562" s="4"/>
       <c r="S562" s="4"/>
     </row>
-    <row r="563" spans="1:19">
+    <row r="563" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A563" s="4"/>
       <c r="B563" s="5"/>
       <c r="C563" s="4"/>
@@ -12220,7 +12220,7 @@
       <c r="R563" s="4"/>
       <c r="S563" s="4"/>
     </row>
-    <row r="564" spans="1:19">
+    <row r="564" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A564" s="4"/>
       <c r="B564" s="5"/>
       <c r="C564" s="4"/>
@@ -12241,7 +12241,7 @@
       <c r="R564" s="4"/>
       <c r="S564" s="4"/>
     </row>
-    <row r="565" spans="1:19">
+    <row r="565" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A565" s="4"/>
       <c r="B565" s="5"/>
       <c r="C565" s="4"/>
@@ -12262,7 +12262,7 @@
       <c r="R565" s="4"/>
       <c r="S565" s="4"/>
     </row>
-    <row r="566" spans="1:19">
+    <row r="566" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A566" s="4"/>
       <c r="B566" s="5"/>
       <c r="C566" s="4"/>
@@ -12283,7 +12283,7 @@
       <c r="R566" s="4"/>
       <c r="S566" s="4"/>
     </row>
-    <row r="567" spans="1:19">
+    <row r="567" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A567" s="4"/>
       <c r="B567" s="5"/>
       <c r="C567" s="4"/>
@@ -12304,7 +12304,7 @@
       <c r="R567" s="4"/>
       <c r="S567" s="4"/>
     </row>
-    <row r="568" spans="1:19">
+    <row r="568" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A568" s="4"/>
       <c r="B568" s="5"/>
       <c r="C568" s="4"/>
@@ -12325,7 +12325,7 @@
       <c r="R568" s="4"/>
       <c r="S568" s="4"/>
     </row>
-    <row r="569" spans="1:19">
+    <row r="569" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A569" s="4"/>
       <c r="B569" s="5"/>
       <c r="C569" s="4"/>
@@ -12346,7 +12346,7 @@
       <c r="R569" s="4"/>
       <c r="S569" s="4"/>
     </row>
-    <row r="570" spans="1:19">
+    <row r="570" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A570" s="4"/>
       <c r="B570" s="5"/>
       <c r="C570" s="4"/>
@@ -12367,7 +12367,7 @@
       <c r="R570" s="4"/>
       <c r="S570" s="4"/>
     </row>
-    <row r="571" spans="1:19">
+    <row r="571" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A571" s="4"/>
       <c r="B571" s="5"/>
       <c r="C571" s="4"/>
@@ -12388,7 +12388,7 @@
       <c r="R571" s="4"/>
       <c r="S571" s="4"/>
     </row>
-    <row r="572" spans="1:19">
+    <row r="572" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A572" s="4"/>
       <c r="B572" s="5"/>
       <c r="C572" s="4"/>
@@ -12409,7 +12409,7 @@
       <c r="R572" s="4"/>
       <c r="S572" s="4"/>
     </row>
-    <row r="573" spans="1:19">
+    <row r="573" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A573" s="4"/>
       <c r="B573" s="5"/>
       <c r="C573" s="4"/>
@@ -12430,7 +12430,7 @@
       <c r="R573" s="4"/>
       <c r="S573" s="4"/>
     </row>
-    <row r="574" spans="1:19">
+    <row r="574" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A574" s="4"/>
       <c r="B574" s="5"/>
       <c r="C574" s="4"/>
@@ -12451,7 +12451,7 @@
       <c r="R574" s="4"/>
       <c r="S574" s="4"/>
     </row>
-    <row r="575" spans="1:19">
+    <row r="575" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A575" s="4"/>
       <c r="B575" s="5"/>
       <c r="C575" s="4"/>
@@ -12472,7 +12472,7 @@
       <c r="R575" s="4"/>
       <c r="S575" s="4"/>
     </row>
-    <row r="576" spans="1:19">
+    <row r="576" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A576" s="4"/>
       <c r="B576" s="5"/>
       <c r="C576" s="4"/>
@@ -12493,7 +12493,7 @@
       <c r="R576" s="4"/>
       <c r="S576" s="4"/>
     </row>
-    <row r="577" spans="1:19">
+    <row r="577" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A577" s="4"/>
       <c r="B577" s="5"/>
       <c r="C577" s="4"/>
@@ -12514,7 +12514,7 @@
       <c r="R577" s="4"/>
       <c r="S577" s="4"/>
     </row>
-    <row r="578" spans="1:19">
+    <row r="578" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A578" s="4"/>
       <c r="B578" s="5"/>
       <c r="C578" s="4"/>
@@ -12535,7 +12535,7 @@
       <c r="R578" s="4"/>
       <c r="S578" s="4"/>
     </row>
-    <row r="579" spans="1:19">
+    <row r="579" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A579" s="4"/>
       <c r="B579" s="5"/>
       <c r="C579" s="4"/>
@@ -12556,7 +12556,7 @@
       <c r="R579" s="4"/>
       <c r="S579" s="4"/>
     </row>
-    <row r="580" spans="1:19">
+    <row r="580" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A580" s="4"/>
       <c r="B580" s="5"/>
       <c r="C580" s="4"/>
@@ -12577,7 +12577,7 @@
       <c r="R580" s="4"/>
       <c r="S580" s="4"/>
     </row>
-    <row r="581" spans="1:19">
+    <row r="581" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A581" s="4"/>
       <c r="B581" s="5"/>
       <c r="C581" s="4"/>
@@ -12598,7 +12598,7 @@
       <c r="R581" s="4"/>
       <c r="S581" s="4"/>
     </row>
-    <row r="582" spans="1:19">
+    <row r="582" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A582" s="4"/>
       <c r="B582" s="5"/>
       <c r="C582" s="4"/>
@@ -12619,7 +12619,7 @@
       <c r="R582" s="4"/>
       <c r="S582" s="4"/>
     </row>
-    <row r="583" spans="1:19">
+    <row r="583" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A583" s="4"/>
       <c r="B583" s="5"/>
       <c r="C583" s="4"/>
@@ -12640,7 +12640,7 @@
       <c r="R583" s="4"/>
       <c r="S583" s="4"/>
     </row>
-    <row r="584" spans="1:19">
+    <row r="584" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A584" s="4"/>
       <c r="B584" s="5"/>
       <c r="C584" s="4"/>
@@ -12661,7 +12661,7 @@
       <c r="R584" s="4"/>
       <c r="S584" s="4"/>
     </row>
-    <row r="585" spans="1:19">
+    <row r="585" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A585" s="4"/>
       <c r="B585" s="5"/>
       <c r="C585" s="4"/>
@@ -12682,7 +12682,7 @@
       <c r="R585" s="4"/>
       <c r="S585" s="4"/>
     </row>
-    <row r="586" spans="1:19">
+    <row r="586" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A586" s="4"/>
       <c r="B586" s="5"/>
       <c r="C586" s="4"/>
@@ -12703,7 +12703,7 @@
       <c r="R586" s="4"/>
       <c r="S586" s="4"/>
     </row>
-    <row r="587" spans="1:19">
+    <row r="587" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A587" s="4"/>
       <c r="B587" s="5"/>
       <c r="C587" s="4"/>
@@ -12724,7 +12724,7 @@
       <c r="R587" s="4"/>
       <c r="S587" s="4"/>
     </row>
-    <row r="588" spans="1:19">
+    <row r="588" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A588" s="4"/>
       <c r="B588" s="5"/>
       <c r="C588" s="4"/>
@@ -12745,7 +12745,7 @@
       <c r="R588" s="4"/>
       <c r="S588" s="4"/>
     </row>
-    <row r="589" spans="1:19">
+    <row r="589" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A589" s="4"/>
       <c r="B589" s="5"/>
       <c r="C589" s="4"/>
@@ -12766,7 +12766,7 @@
       <c r="R589" s="4"/>
       <c r="S589" s="4"/>
     </row>
-    <row r="590" spans="1:19">
+    <row r="590" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A590" s="4"/>
       <c r="B590" s="5"/>
       <c r="C590" s="4"/>
@@ -12787,7 +12787,7 @@
       <c r="R590" s="4"/>
       <c r="S590" s="4"/>
     </row>
-    <row r="591" spans="1:19">
+    <row r="591" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A591" s="4"/>
       <c r="B591" s="5"/>
       <c r="C591" s="4"/>
@@ -12808,7 +12808,7 @@
       <c r="R591" s="4"/>
       <c r="S591" s="4"/>
     </row>
-    <row r="592" spans="1:19">
+    <row r="592" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A592" s="4"/>
       <c r="B592" s="5"/>
       <c r="C592" s="4"/>
@@ -12829,7 +12829,7 @@
       <c r="R592" s="4"/>
       <c r="S592" s="4"/>
     </row>
-    <row r="593" spans="1:19">
+    <row r="593" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A593" s="4"/>
       <c r="B593" s="5"/>
       <c r="C593" s="4"/>
@@ -12850,7 +12850,7 @@
       <c r="R593" s="4"/>
       <c r="S593" s="4"/>
     </row>
-    <row r="594" spans="1:19">
+    <row r="594" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A594" s="4"/>
       <c r="B594" s="5"/>
       <c r="C594" s="4"/>
@@ -12871,7 +12871,7 @@
       <c r="R594" s="4"/>
       <c r="S594" s="4"/>
     </row>
-    <row r="595" spans="1:19">
+    <row r="595" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A595" s="4"/>
       <c r="B595" s="5"/>
       <c r="C595" s="4"/>
@@ -12892,7 +12892,7 @@
       <c r="R595" s="4"/>
       <c r="S595" s="4"/>
     </row>
-    <row r="596" spans="1:19">
+    <row r="596" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A596" s="4"/>
       <c r="B596" s="5"/>
       <c r="C596" s="4"/>
@@ -12913,7 +12913,7 @@
       <c r="R596" s="4"/>
       <c r="S596" s="4"/>
     </row>
-    <row r="597" spans="1:19">
+    <row r="597" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A597" s="4"/>
       <c r="B597" s="5"/>
       <c r="C597" s="4"/>
@@ -12934,7 +12934,7 @@
       <c r="R597" s="4"/>
       <c r="S597" s="4"/>
     </row>
-    <row r="598" spans="1:19">
+    <row r="598" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A598" s="4"/>
       <c r="B598" s="5"/>
       <c r="C598" s="4"/>
@@ -12955,7 +12955,7 @@
       <c r="R598" s="4"/>
       <c r="S598" s="4"/>
     </row>
-    <row r="599" spans="1:19">
+    <row r="599" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A599" s="4"/>
       <c r="B599" s="5"/>
       <c r="C599" s="4"/>
@@ -12976,7 +12976,7 @@
       <c r="R599" s="4"/>
       <c r="S599" s="4"/>
     </row>
-    <row r="600" spans="1:19">
+    <row r="600" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A600" s="4"/>
       <c r="B600" s="5"/>
       <c r="C600" s="4"/>
@@ -12997,7 +12997,7 @@
       <c r="R600" s="4"/>
       <c r="S600" s="4"/>
     </row>
-    <row r="601" spans="1:19">
+    <row r="601" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A601" s="4"/>
       <c r="B601" s="5"/>
       <c r="C601" s="4"/>
@@ -13018,7 +13018,7 @@
       <c r="R601" s="4"/>
       <c r="S601" s="4"/>
     </row>
-    <row r="602" spans="1:19">
+    <row r="602" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A602" s="4"/>
       <c r="B602" s="5"/>
       <c r="C602" s="4"/>
@@ -13039,7 +13039,7 @@
       <c r="R602" s="4"/>
       <c r="S602" s="4"/>
     </row>
-    <row r="603" spans="1:19">
+    <row r="603" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A603" s="4"/>
       <c r="B603" s="5"/>
       <c r="C603" s="4"/>
@@ -13060,7 +13060,7 @@
       <c r="R603" s="4"/>
       <c r="S603" s="4"/>
     </row>
-    <row r="604" spans="1:19">
+    <row r="604" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A604" s="4"/>
       <c r="B604" s="5"/>
       <c r="C604" s="4"/>
@@ -13081,7 +13081,7 @@
       <c r="R604" s="4"/>
       <c r="S604" s="4"/>
     </row>
-    <row r="605" spans="1:19">
+    <row r="605" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A605" s="4"/>
       <c r="B605" s="5"/>
       <c r="C605" s="4"/>
@@ -13102,7 +13102,7 @@
       <c r="R605" s="4"/>
       <c r="S605" s="4"/>
     </row>
-    <row r="606" spans="1:19">
+    <row r="606" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A606" s="4"/>
       <c r="B606" s="5"/>
       <c r="C606" s="4"/>
@@ -13123,7 +13123,7 @@
       <c r="R606" s="4"/>
       <c r="S606" s="4"/>
     </row>
-    <row r="607" spans="1:19">
+    <row r="607" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A607" s="4"/>
       <c r="B607" s="5"/>
       <c r="C607" s="4"/>
@@ -13144,7 +13144,7 @@
       <c r="R607" s="4"/>
       <c r="S607" s="4"/>
     </row>
-    <row r="608" spans="1:19">
+    <row r="608" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A608" s="4"/>
       <c r="B608" s="5"/>
       <c r="C608" s="4"/>
@@ -13165,7 +13165,7 @@
       <c r="R608" s="4"/>
       <c r="S608" s="4"/>
     </row>
-    <row r="609" spans="1:19">
+    <row r="609" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A609" s="4"/>
       <c r="B609" s="5"/>
       <c r="C609" s="4"/>
@@ -13186,7 +13186,7 @@
       <c r="R609" s="4"/>
       <c r="S609" s="4"/>
     </row>
-    <row r="610" spans="1:19">
+    <row r="610" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A610" s="4"/>
       <c r="B610" s="5"/>
       <c r="C610" s="4"/>
@@ -13207,7 +13207,7 @@
       <c r="R610" s="4"/>
       <c r="S610" s="4"/>
     </row>
-    <row r="611" spans="1:19">
+    <row r="611" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A611" s="4"/>
       <c r="B611" s="5"/>
       <c r="C611" s="4"/>
@@ -13228,7 +13228,7 @@
       <c r="R611" s="4"/>
       <c r="S611" s="4"/>
     </row>
-    <row r="612" spans="1:19">
+    <row r="612" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A612" s="4"/>
       <c r="B612" s="5"/>
       <c r="C612" s="4"/>
@@ -13249,7 +13249,7 @@
       <c r="R612" s="4"/>
       <c r="S612" s="4"/>
     </row>
-    <row r="613" spans="1:19">
+    <row r="613" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A613" s="4"/>
       <c r="B613" s="5"/>
       <c r="C613" s="4"/>
@@ -13270,7 +13270,7 @@
       <c r="R613" s="4"/>
       <c r="S613" s="4"/>
     </row>
-    <row r="614" spans="1:19">
+    <row r="614" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A614" s="4"/>
       <c r="B614" s="5"/>
       <c r="C614" s="4"/>
@@ -13291,7 +13291,7 @@
       <c r="R614" s="4"/>
       <c r="S614" s="4"/>
     </row>
-    <row r="615" spans="1:19">
+    <row r="615" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A615" s="4"/>
       <c r="B615" s="5"/>
       <c r="C615" s="4"/>
@@ -13312,7 +13312,7 @@
       <c r="R615" s="4"/>
       <c r="S615" s="4"/>
     </row>
-    <row r="616" spans="1:19">
+    <row r="616" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A616" s="4"/>
       <c r="B616" s="5"/>
       <c r="C616" s="4"/>
@@ -13333,7 +13333,7 @@
       <c r="R616" s="4"/>
       <c r="S616" s="4"/>
     </row>
-    <row r="617" spans="1:19">
+    <row r="617" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A617" s="4"/>
       <c r="B617" s="5"/>
       <c r="C617" s="4"/>
@@ -13354,7 +13354,7 @@
       <c r="R617" s="4"/>
       <c r="S617" s="4"/>
     </row>
-    <row r="618" spans="1:19">
+    <row r="618" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A618" s="4"/>
       <c r="B618" s="5"/>
       <c r="C618" s="4"/>
@@ -13375,7 +13375,7 @@
       <c r="R618" s="4"/>
       <c r="S618" s="4"/>
     </row>
-    <row r="619" spans="1:19">
+    <row r="619" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A619" s="4"/>
       <c r="B619" s="5"/>
       <c r="C619" s="4"/>
@@ -13396,7 +13396,7 @@
       <c r="R619" s="4"/>
       <c r="S619" s="4"/>
     </row>
-    <row r="620" spans="1:19">
+    <row r="620" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A620" s="4"/>
       <c r="B620" s="5"/>
       <c r="C620" s="4"/>
@@ -13417,7 +13417,7 @@
       <c r="R620" s="4"/>
       <c r="S620" s="4"/>
     </row>
-    <row r="621" spans="1:19">
+    <row r="621" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A621" s="4"/>
       <c r="B621" s="5"/>
       <c r="C621" s="4"/>
@@ -13438,7 +13438,7 @@
       <c r="R621" s="4"/>
       <c r="S621" s="4"/>
     </row>
-    <row r="622" spans="1:19">
+    <row r="622" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A622" s="4"/>
       <c r="B622" s="5"/>
       <c r="C622" s="4"/>
@@ -13459,7 +13459,7 @@
       <c r="R622" s="4"/>
       <c r="S622" s="4"/>
     </row>
-    <row r="623" spans="1:19">
+    <row r="623" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A623" s="4"/>
       <c r="B623" s="5"/>
       <c r="C623" s="4"/>
@@ -13480,7 +13480,7 @@
       <c r="R623" s="4"/>
       <c r="S623" s="4"/>
     </row>
-    <row r="624" spans="1:19">
+    <row r="624" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A624" s="4"/>
       <c r="B624" s="5"/>
       <c r="C624" s="4"/>
@@ -13501,7 +13501,7 @@
       <c r="R624" s="4"/>
       <c r="S624" s="4"/>
     </row>
-    <row r="625" spans="1:19">
+    <row r="625" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A625" s="4"/>
       <c r="B625" s="5"/>
       <c r="C625" s="4"/>
@@ -13522,7 +13522,7 @@
       <c r="R625" s="4"/>
       <c r="S625" s="4"/>
     </row>
-    <row r="626" spans="1:19">
+    <row r="626" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A626" s="4"/>
       <c r="B626" s="5"/>
       <c r="C626" s="4"/>
@@ -13543,7 +13543,7 @@
       <c r="R626" s="4"/>
       <c r="S626" s="4"/>
     </row>
-    <row r="627" spans="1:19">
+    <row r="627" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A627" s="4"/>
       <c r="B627" s="5"/>
       <c r="C627" s="4"/>
@@ -13564,7 +13564,7 @@
       <c r="R627" s="4"/>
       <c r="S627" s="4"/>
     </row>
-    <row r="628" spans="1:19">
+    <row r="628" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A628" s="4"/>
       <c r="B628" s="5"/>
       <c r="C628" s="4"/>
@@ -13585,7 +13585,7 @@
       <c r="R628" s="4"/>
       <c r="S628" s="4"/>
     </row>
-    <row r="629" spans="1:19">
+    <row r="629" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A629" s="4"/>
       <c r="B629" s="5"/>
       <c r="C629" s="4"/>
@@ -13606,7 +13606,7 @@
       <c r="R629" s="4"/>
       <c r="S629" s="4"/>
     </row>
-    <row r="630" spans="1:19">
+    <row r="630" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A630" s="4"/>
       <c r="B630" s="5"/>
       <c r="C630" s="4"/>
@@ -13627,7 +13627,7 @@
       <c r="R630" s="4"/>
       <c r="S630" s="4"/>
     </row>
-    <row r="631" spans="1:19">
+    <row r="631" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A631" s="4"/>
       <c r="B631" s="5"/>
       <c r="C631" s="4"/>
@@ -13648,7 +13648,7 @@
       <c r="R631" s="4"/>
       <c r="S631" s="4"/>
     </row>
-    <row r="632" spans="1:19">
+    <row r="632" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A632" s="4"/>
       <c r="B632" s="5"/>
       <c r="C632" s="4"/>
@@ -13669,7 +13669,7 @@
       <c r="R632" s="4"/>
       <c r="S632" s="4"/>
     </row>
-    <row r="633" spans="1:19">
+    <row r="633" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A633" s="4"/>
       <c r="B633" s="5"/>
       <c r="C633" s="4"/>
@@ -13690,7 +13690,7 @@
       <c r="R633" s="4"/>
       <c r="S633" s="4"/>
     </row>
-    <row r="634" spans="1:19">
+    <row r="634" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A634" s="4"/>
       <c r="B634" s="5"/>
       <c r="C634" s="4"/>
@@ -13711,7 +13711,7 @@
       <c r="R634" s="4"/>
       <c r="S634" s="4"/>
     </row>
-    <row r="635" spans="1:19">
+    <row r="635" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A635" s="4"/>
       <c r="B635" s="5"/>
       <c r="C635" s="4"/>
@@ -13732,7 +13732,7 @@
       <c r="R635" s="4"/>
       <c r="S635" s="4"/>
     </row>
-    <row r="636" spans="1:19">
+    <row r="636" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A636" s="4"/>
       <c r="B636" s="5"/>
       <c r="C636" s="4"/>
@@ -13753,7 +13753,7 @@
       <c r="R636" s="4"/>
       <c r="S636" s="4"/>
     </row>
-    <row r="637" spans="1:19">
+    <row r="637" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A637" s="4"/>
       <c r="B637" s="5"/>
       <c r="C637" s="4"/>
@@ -13774,7 +13774,7 @@
       <c r="R637" s="4"/>
       <c r="S637" s="4"/>
     </row>
-    <row r="638" spans="1:19">
+    <row r="638" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A638" s="4"/>
       <c r="B638" s="5"/>
       <c r="C638" s="4"/>
@@ -13795,7 +13795,7 @@
       <c r="R638" s="4"/>
       <c r="S638" s="4"/>
     </row>
-    <row r="639" spans="1:19">
+    <row r="639" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A639" s="4"/>
       <c r="B639" s="5"/>
       <c r="C639" s="4"/>
@@ -13816,7 +13816,7 @@
       <c r="R639" s="4"/>
       <c r="S639" s="4"/>
     </row>
-    <row r="640" spans="1:19">
+    <row r="640" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A640" s="4"/>
       <c r="B640" s="5"/>
       <c r="C640" s="4"/>
@@ -13837,7 +13837,7 @@
       <c r="R640" s="4"/>
       <c r="S640" s="4"/>
     </row>
-    <row r="641" spans="1:19">
+    <row r="641" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A641" s="4"/>
       <c r="B641" s="5"/>
       <c r="C641" s="4"/>
@@ -13858,7 +13858,7 @@
       <c r="R641" s="4"/>
       <c r="S641" s="4"/>
     </row>
-    <row r="642" spans="1:19">
+    <row r="642" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A642" s="4"/>
       <c r="B642" s="5"/>
       <c r="C642" s="4"/>
@@ -13879,7 +13879,7 @@
       <c r="R642" s="4"/>
       <c r="S642" s="4"/>
     </row>
-    <row r="643" spans="1:19">
+    <row r="643" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A643" s="4"/>
       <c r="B643" s="5"/>
       <c r="C643" s="4"/>
@@ -13900,7 +13900,7 @@
       <c r="R643" s="4"/>
       <c r="S643" s="4"/>
     </row>
-    <row r="644" spans="1:19">
+    <row r="644" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A644" s="4"/>
       <c r="B644" s="5"/>
       <c r="C644" s="4"/>
@@ -13921,7 +13921,7 @@
       <c r="R644" s="4"/>
       <c r="S644" s="4"/>
     </row>
-    <row r="645" spans="1:19">
+    <row r="645" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A645" s="4"/>
       <c r="B645" s="5"/>
       <c r="C645" s="4"/>
@@ -13942,7 +13942,7 @@
       <c r="R645" s="4"/>
       <c r="S645" s="4"/>
     </row>
-    <row r="646" spans="1:19">
+    <row r="646" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A646" s="4"/>
       <c r="B646" s="5"/>
       <c r="C646" s="4"/>
@@ -13963,7 +13963,7 @@
       <c r="R646" s="4"/>
       <c r="S646" s="4"/>
     </row>
-    <row r="647" spans="1:19">
+    <row r="647" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A647" s="4"/>
       <c r="B647" s="5"/>
       <c r="C647" s="4"/>
@@ -13984,7 +13984,7 @@
       <c r="R647" s="4"/>
       <c r="S647" s="4"/>
     </row>
-    <row r="648" spans="1:19">
+    <row r="648" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A648" s="4"/>
       <c r="B648" s="5"/>
       <c r="C648" s="4"/>
@@ -14005,7 +14005,7 @@
       <c r="R648" s="4"/>
       <c r="S648" s="4"/>
     </row>
-    <row r="649" spans="1:19">
+    <row r="649" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A649" s="4"/>
       <c r="B649" s="5"/>
       <c r="C649" s="4"/>
@@ -14026,7 +14026,7 @@
       <c r="R649" s="4"/>
       <c r="S649" s="4"/>
     </row>
-    <row r="650" spans="1:19">
+    <row r="650" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A650" s="4"/>
       <c r="B650" s="5"/>
       <c r="C650" s="4"/>
@@ -14047,7 +14047,7 @@
       <c r="R650" s="4"/>
       <c r="S650" s="4"/>
     </row>
-    <row r="651" spans="1:19">
+    <row r="651" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A651" s="4"/>
       <c r="B651" s="5"/>
       <c r="C651" s="4"/>
@@ -14068,7 +14068,7 @@
       <c r="R651" s="4"/>
       <c r="S651" s="4"/>
     </row>
-    <row r="652" spans="1:19">
+    <row r="652" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A652" s="4"/>
       <c r="B652" s="5"/>
       <c r="C652" s="4"/>
@@ -14089,7 +14089,7 @@
       <c r="R652" s="4"/>
       <c r="S652" s="4"/>
     </row>
-    <row r="653" spans="1:19">
+    <row r="653" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A653" s="4"/>
       <c r="B653" s="5"/>
       <c r="C653" s="4"/>
@@ -14110,7 +14110,7 @@
       <c r="R653" s="4"/>
       <c r="S653" s="4"/>
     </row>
-    <row r="654" spans="1:19">
+    <row r="654" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A654" s="4"/>
       <c r="B654" s="5"/>
       <c r="C654" s="4"/>
@@ -14131,7 +14131,7 @@
       <c r="R654" s="4"/>
       <c r="S654" s="4"/>
     </row>
-    <row r="655" spans="1:19">
+    <row r="655" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A655" s="4"/>
       <c r="B655" s="5"/>
       <c r="C655" s="4"/>
@@ -14152,7 +14152,7 @@
       <c r="R655" s="4"/>
       <c r="S655" s="4"/>
     </row>
-    <row r="656" spans="1:19">
+    <row r="656" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A656" s="4"/>
       <c r="B656" s="5"/>
       <c r="C656" s="4"/>
@@ -14173,7 +14173,7 @@
       <c r="R656" s="4"/>
       <c r="S656" s="4"/>
     </row>
-    <row r="657" spans="1:19">
+    <row r="657" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A657" s="4"/>
       <c r="B657" s="5"/>
       <c r="C657" s="4"/>
@@ -14194,7 +14194,7 @@
       <c r="R657" s="4"/>
       <c r="S657" s="4"/>
     </row>
-    <row r="658" spans="1:19">
+    <row r="658" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A658" s="4"/>
       <c r="B658" s="5"/>
       <c r="C658" s="4"/>
@@ -14215,7 +14215,7 @@
       <c r="R658" s="4"/>
       <c r="S658" s="4"/>
     </row>
-    <row r="659" spans="1:19">
+    <row r="659" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A659" s="4"/>
       <c r="B659" s="5"/>
       <c r="C659" s="4"/>
@@ -14236,7 +14236,7 @@
       <c r="R659" s="4"/>
       <c r="S659" s="4"/>
     </row>
-    <row r="660" spans="1:19">
+    <row r="660" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A660" s="4"/>
       <c r="B660" s="5"/>
       <c r="C660" s="4"/>
@@ -14257,7 +14257,7 @@
       <c r="R660" s="4"/>
       <c r="S660" s="4"/>
     </row>
-    <row r="661" spans="1:19">
+    <row r="661" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A661" s="4"/>
       <c r="B661" s="5"/>
       <c r="C661" s="4"/>
@@ -14278,7 +14278,7 @@
       <c r="R661" s="4"/>
       <c r="S661" s="4"/>
     </row>
-    <row r="662" spans="1:19">
+    <row r="662" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A662" s="4"/>
       <c r="B662" s="5"/>
       <c r="C662" s="4"/>
@@ -14299,7 +14299,7 @@
       <c r="R662" s="4"/>
       <c r="S662" s="4"/>
     </row>
-    <row r="663" spans="1:19">
+    <row r="663" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A663" s="4"/>
       <c r="B663" s="5"/>
       <c r="C663" s="4"/>
@@ -14320,7 +14320,7 @@
       <c r="R663" s="4"/>
       <c r="S663" s="4"/>
     </row>
-    <row r="664" spans="1:19">
+    <row r="664" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A664" s="4"/>
       <c r="B664" s="5"/>
       <c r="C664" s="4"/>
@@ -14341,7 +14341,7 @@
       <c r="R664" s="4"/>
       <c r="S664" s="4"/>
     </row>
-    <row r="665" spans="1:19">
+    <row r="665" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A665" s="4"/>
       <c r="B665" s="5"/>
       <c r="C665" s="4"/>
@@ -14362,7 +14362,7 @@
       <c r="R665" s="4"/>
       <c r="S665" s="4"/>
     </row>
-    <row r="666" spans="1:19">
+    <row r="666" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A666" s="4"/>
       <c r="B666" s="5"/>
       <c r="C666" s="4"/>
@@ -14383,7 +14383,7 @@
       <c r="R666" s="4"/>
       <c r="S666" s="4"/>
     </row>
-    <row r="667" spans="1:19">
+    <row r="667" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A667" s="4"/>
       <c r="B667" s="5"/>
       <c r="C667" s="4"/>
@@ -14404,7 +14404,7 @@
       <c r="R667" s="4"/>
       <c r="S667" s="4"/>
     </row>
-    <row r="668" spans="1:19">
+    <row r="668" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A668" s="4"/>
       <c r="B668" s="5"/>
       <c r="C668" s="4"/>
@@ -14425,7 +14425,7 @@
       <c r="R668" s="4"/>
       <c r="S668" s="4"/>
     </row>
-    <row r="669" spans="1:19">
+    <row r="669" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A669" s="4"/>
       <c r="B669" s="5"/>
       <c r="C669" s="4"/>
@@ -14446,7 +14446,7 @@
       <c r="R669" s="4"/>
       <c r="S669" s="4"/>
     </row>
-    <row r="670" spans="1:19">
+    <row r="670" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A670" s="4"/>
       <c r="B670" s="5"/>
       <c r="C670" s="4"/>
@@ -14467,7 +14467,7 @@
       <c r="R670" s="4"/>
       <c r="S670" s="4"/>
     </row>
-    <row r="671" spans="1:19">
+    <row r="671" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A671" s="4"/>
       <c r="B671" s="5"/>
       <c r="C671" s="4"/>
@@ -14488,7 +14488,7 @@
       <c r="R671" s="4"/>
       <c r="S671" s="4"/>
     </row>
-    <row r="672" spans="1:19">
+    <row r="672" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A672" s="4"/>
       <c r="B672" s="5"/>
       <c r="C672" s="4"/>
@@ -14509,7 +14509,7 @@
       <c r="R672" s="4"/>
       <c r="S672" s="4"/>
     </row>
-    <row r="673" spans="1:19">
+    <row r="673" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A673" s="4"/>
       <c r="B673" s="5"/>
       <c r="C673" s="4"/>
@@ -14530,7 +14530,7 @@
       <c r="R673" s="4"/>
       <c r="S673" s="4"/>
     </row>
-    <row r="674" spans="1:19">
+    <row r="674" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A674" s="4"/>
       <c r="B674" s="5"/>
       <c r="C674" s="4"/>
@@ -14551,7 +14551,7 @@
       <c r="R674" s="4"/>
       <c r="S674" s="4"/>
     </row>
-    <row r="675" spans="1:19">
+    <row r="675" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A675" s="4"/>
       <c r="B675" s="5"/>
       <c r="C675" s="4"/>
@@ -14572,7 +14572,7 @@
       <c r="R675" s="4"/>
       <c r="S675" s="4"/>
     </row>
-    <row r="676" spans="1:19">
+    <row r="676" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A676" s="4"/>
       <c r="B676" s="5"/>
       <c r="C676" s="4"/>
@@ -14593,7 +14593,7 @@
       <c r="R676" s="4"/>
       <c r="S676" s="4"/>
     </row>
-    <row r="677" spans="1:19">
+    <row r="677" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A677" s="4"/>
       <c r="B677" s="5"/>
       <c r="C677" s="4"/>
@@ -14614,7 +14614,7 @@
       <c r="R677" s="4"/>
       <c r="S677" s="4"/>
     </row>
-    <row r="678" spans="1:19">
+    <row r="678" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A678" s="4"/>
       <c r="B678" s="5"/>
       <c r="C678" s="4"/>
@@ -14635,7 +14635,7 @@
       <c r="R678" s="4"/>
       <c r="S678" s="4"/>
     </row>
-    <row r="679" spans="1:19">
+    <row r="679" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A679" s="4"/>
       <c r="B679" s="5"/>
       <c r="C679" s="4"/>
@@ -14656,7 +14656,7 @@
       <c r="R679" s="4"/>
       <c r="S679" s="4"/>
     </row>
-    <row r="680" spans="1:19">
+    <row r="680" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A680" s="4"/>
       <c r="B680" s="5"/>
       <c r="C680" s="4"/>
@@ -14677,7 +14677,7 @@
       <c r="R680" s="4"/>
       <c r="S680" s="4"/>
     </row>
-    <row r="681" spans="1:19">
+    <row r="681" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A681" s="4"/>
       <c r="B681" s="5"/>
       <c r="C681" s="4"/>
@@ -14698,7 +14698,7 @@
       <c r="R681" s="4"/>
       <c r="S681" s="4"/>
     </row>
-    <row r="682" spans="1:19">
+    <row r="682" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A682" s="4"/>
       <c r="B682" s="5"/>
       <c r="C682" s="4"/>
@@ -14719,7 +14719,7 @@
       <c r="R682" s="4"/>
       <c r="S682" s="4"/>
     </row>
-    <row r="683" spans="1:19">
+    <row r="683" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A683" s="4"/>
       <c r="B683" s="5"/>
       <c r="C683" s="4"/>
@@ -14740,7 +14740,7 @@
       <c r="R683" s="4"/>
       <c r="S683" s="4"/>
     </row>
-    <row r="684" spans="1:19">
+    <row r="684" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A684" s="4"/>
       <c r="B684" s="5"/>
       <c r="C684" s="4"/>
@@ -14761,7 +14761,7 @@
       <c r="R684" s="4"/>
       <c r="S684" s="4"/>
     </row>
-    <row r="685" spans="1:19">
+    <row r="685" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A685" s="4"/>
       <c r="B685" s="5"/>
       <c r="C685" s="4"/>
@@ -14782,7 +14782,7 @@
       <c r="R685" s="4"/>
       <c r="S685" s="4"/>
     </row>
-    <row r="686" spans="1:19">
+    <row r="686" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A686" s="4"/>
       <c r="B686" s="5"/>
       <c r="C686" s="4"/>
@@ -14803,7 +14803,7 @@
       <c r="R686" s="4"/>
       <c r="S686" s="4"/>
     </row>
-    <row r="687" spans="1:19">
+    <row r="687" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A687" s="4"/>
       <c r="B687" s="5"/>
       <c r="C687" s="4"/>
@@ -14824,7 +14824,7 @@
       <c r="R687" s="4"/>
       <c r="S687" s="4"/>
     </row>
-    <row r="688" spans="1:19">
+    <row r="688" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A688" s="4"/>
       <c r="B688" s="5"/>
       <c r="C688" s="4"/>
@@ -14845,7 +14845,7 @@
       <c r="R688" s="4"/>
       <c r="S688" s="4"/>
     </row>
-    <row r="689" spans="1:19">
+    <row r="689" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A689" s="4"/>
       <c r="B689" s="5"/>
       <c r="C689" s="4"/>
@@ -14866,7 +14866,7 @@
       <c r="R689" s="4"/>
       <c r="S689" s="4"/>
     </row>
-    <row r="690" spans="1:19">
+    <row r="690" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A690" s="4"/>
       <c r="B690" s="5"/>
       <c r="C690" s="4"/>
@@ -14887,7 +14887,7 @@
       <c r="R690" s="4"/>
       <c r="S690" s="4"/>
     </row>
-    <row r="691" spans="1:19">
+    <row r="691" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A691" s="4"/>
       <c r="B691" s="5"/>
       <c r="C691" s="4"/>
@@ -14908,7 +14908,7 @@
       <c r="R691" s="4"/>
       <c r="S691" s="4"/>
     </row>
-    <row r="692" spans="1:19">
+    <row r="692" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A692" s="4"/>
       <c r="B692" s="5"/>
       <c r="C692" s="4"/>
@@ -14929,7 +14929,7 @@
       <c r="R692" s="4"/>
       <c r="S692" s="4"/>
     </row>
-    <row r="693" spans="1:19">
+    <row r="693" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A693" s="4"/>
       <c r="B693" s="5"/>
       <c r="C693" s="4"/>
@@ -14950,7 +14950,7 @@
       <c r="R693" s="4"/>
       <c r="S693" s="4"/>
     </row>
-    <row r="694" spans="1:19">
+    <row r="694" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A694" s="4"/>
       <c r="B694" s="5"/>
       <c r="C694" s="4"/>
@@ -14971,7 +14971,7 @@
       <c r="R694" s="4"/>
       <c r="S694" s="4"/>
     </row>
-    <row r="695" spans="1:19">
+    <row r="695" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A695" s="4"/>
       <c r="B695" s="5"/>
       <c r="C695" s="4"/>
@@ -14992,7 +14992,7 @@
       <c r="R695" s="4"/>
       <c r="S695" s="4"/>
     </row>
-    <row r="696" spans="1:19">
+    <row r="696" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A696" s="4"/>
       <c r="B696" s="5"/>
       <c r="C696" s="4"/>
@@ -15013,7 +15013,7 @@
       <c r="R696" s="4"/>
       <c r="S696" s="4"/>
     </row>
-    <row r="697" spans="1:19">
+    <row r="697" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A697" s="4"/>
       <c r="B697" s="5"/>
       <c r="C697" s="4"/>
@@ -15034,7 +15034,7 @@
       <c r="R697" s="4"/>
       <c r="S697" s="4"/>
     </row>
-    <row r="698" spans="1:19">
+    <row r="698" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A698" s="4"/>
       <c r="B698" s="5"/>
       <c r="C698" s="4"/>
@@ -15055,7 +15055,7 @@
       <c r="R698" s="4"/>
       <c r="S698" s="4"/>
     </row>
-    <row r="699" spans="1:19">
+    <row r="699" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A699" s="4"/>
       <c r="B699" s="5"/>
       <c r="C699" s="4"/>
@@ -15076,7 +15076,7 @@
       <c r="R699" s="4"/>
       <c r="S699" s="4"/>
     </row>
-    <row r="700" spans="1:19">
+    <row r="700" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A700" s="4"/>
       <c r="B700" s="5"/>
       <c r="C700" s="4"/>
@@ -15097,7 +15097,7 @@
       <c r="R700" s="4"/>
       <c r="S700" s="4"/>
     </row>
-    <row r="701" spans="1:19">
+    <row r="701" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A701" s="4"/>
       <c r="B701" s="5"/>
       <c r="C701" s="4"/>
@@ -15118,7 +15118,7 @@
       <c r="R701" s="4"/>
       <c r="S701" s="4"/>
     </row>
-    <row r="702" spans="1:19">
+    <row r="702" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A702" s="4"/>
       <c r="B702" s="5"/>
       <c r="C702" s="4"/>
@@ -15139,7 +15139,7 @@
       <c r="R702" s="4"/>
       <c r="S702" s="4"/>
     </row>
-    <row r="703" spans="1:19">
+    <row r="703" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A703" s="4"/>
       <c r="B703" s="5"/>
       <c r="C703" s="4"/>
@@ -15160,7 +15160,7 @@
       <c r="R703" s="4"/>
       <c r="S703" s="4"/>
     </row>
-    <row r="704" spans="1:19">
+    <row r="704" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A704" s="4"/>
       <c r="B704" s="5"/>
       <c r="C704" s="4"/>
@@ -15181,7 +15181,7 @@
       <c r="R704" s="4"/>
       <c r="S704" s="4"/>
     </row>
-    <row r="705" spans="1:19">
+    <row r="705" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A705" s="4"/>
       <c r="B705" s="5"/>
       <c r="C705" s="4"/>
@@ -15202,7 +15202,7 @@
       <c r="R705" s="4"/>
       <c r="S705" s="4"/>
     </row>
-    <row r="706" spans="1:19">
+    <row r="706" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A706" s="4"/>
       <c r="B706" s="5"/>
       <c r="C706" s="4"/>
@@ -15223,7 +15223,7 @@
       <c r="R706" s="4"/>
       <c r="S706" s="4"/>
     </row>
-    <row r="707" spans="1:19">
+    <row r="707" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A707" s="4"/>
       <c r="B707" s="5"/>
       <c r="C707" s="4"/>
@@ -15244,7 +15244,7 @@
       <c r="R707" s="4"/>
       <c r="S707" s="4"/>
     </row>
-    <row r="708" spans="1:19">
+    <row r="708" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A708" s="4"/>
       <c r="B708" s="5"/>
       <c r="C708" s="4"/>
@@ -15265,7 +15265,7 @@
       <c r="R708" s="4"/>
       <c r="S708" s="4"/>
     </row>
-    <row r="709" spans="1:19">
+    <row r="709" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A709" s="4"/>
       <c r="B709" s="5"/>
       <c r="C709" s="4"/>
@@ -15286,7 +15286,7 @@
       <c r="R709" s="4"/>
       <c r="S709" s="4"/>
     </row>
-    <row r="710" spans="1:19">
+    <row r="710" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A710" s="4"/>
       <c r="B710" s="5"/>
       <c r="C710" s="4"/>
@@ -15307,7 +15307,7 @@
       <c r="R710" s="4"/>
       <c r="S710" s="4"/>
     </row>
-    <row r="711" spans="1:19">
+    <row r="711" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A711" s="4"/>
       <c r="B711" s="5"/>
       <c r="C711" s="4"/>
@@ -15328,7 +15328,7 @@
       <c r="R711" s="4"/>
       <c r="S711" s="4"/>
     </row>
-    <row r="712" spans="1:19">
+    <row r="712" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A712" s="4"/>
       <c r="B712" s="5"/>
       <c r="C712" s="4"/>
@@ -15349,7 +15349,7 @@
       <c r="R712" s="4"/>
       <c r="S712" s="4"/>
     </row>
-    <row r="713" spans="1:19">
+    <row r="713" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A713" s="4"/>
       <c r="B713" s="5"/>
       <c r="C713" s="4"/>
@@ -15370,7 +15370,7 @@
       <c r="R713" s="4"/>
       <c r="S713" s="4"/>
     </row>
-    <row r="714" spans="1:19">
+    <row r="714" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A714" s="4"/>
       <c r="B714" s="5"/>
       <c r="C714" s="4"/>
@@ -15391,7 +15391,7 @@
       <c r="R714" s="4"/>
       <c r="S714" s="4"/>
     </row>
-    <row r="715" spans="1:19">
+    <row r="715" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A715" s="4"/>
       <c r="B715" s="5"/>
       <c r="C715" s="4"/>
@@ -15412,7 +15412,7 @@
       <c r="R715" s="4"/>
       <c r="S715" s="4"/>
     </row>
-    <row r="716" spans="1:19">
+    <row r="716" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A716" s="4"/>
       <c r="B716" s="5"/>
       <c r="C716" s="4"/>
@@ -15433,7 +15433,7 @@
       <c r="R716" s="4"/>
       <c r="S716" s="4"/>
     </row>
-    <row r="717" spans="1:19">
+    <row r="717" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A717" s="4"/>
       <c r="B717" s="5"/>
       <c r="C717" s="4"/>
@@ -15454,7 +15454,7 @@
       <c r="R717" s="4"/>
       <c r="S717" s="4"/>
     </row>
-    <row r="718" spans="1:19">
+    <row r="718" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A718" s="4"/>
       <c r="B718" s="5"/>
       <c r="C718" s="4"/>
@@ -15475,7 +15475,7 @@
       <c r="R718" s="4"/>
       <c r="S718" s="4"/>
     </row>
-    <row r="719" spans="1:19">
+    <row r="719" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A719" s="4"/>
       <c r="B719" s="5"/>
       <c r="C719" s="4"/>
@@ -15496,7 +15496,7 @@
       <c r="R719" s="4"/>
       <c r="S719" s="4"/>
     </row>
-    <row r="720" spans="1:19">
+    <row r="720" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A720" s="4"/>
       <c r="B720" s="5"/>
       <c r="C720" s="4"/>
@@ -15517,7 +15517,7 @@
       <c r="R720" s="4"/>
       <c r="S720" s="4"/>
     </row>
-    <row r="721" spans="1:19">
+    <row r="721" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A721" s="4"/>
       <c r="B721" s="5"/>
       <c r="C721" s="4"/>
@@ -15538,7 +15538,7 @@
       <c r="R721" s="4"/>
       <c r="S721" s="4"/>
     </row>
-    <row r="722" spans="1:19">
+    <row r="722" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A722" s="4"/>
       <c r="B722" s="5"/>
       <c r="C722" s="4"/>
@@ -15559,7 +15559,7 @@
       <c r="R722" s="4"/>
       <c r="S722" s="4"/>
     </row>
-    <row r="723" spans="1:19">
+    <row r="723" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A723" s="4"/>
       <c r="B723" s="5"/>
       <c r="C723" s="4"/>
@@ -15580,7 +15580,7 @@
       <c r="R723" s="4"/>
       <c r="S723" s="4"/>
     </row>
-    <row r="724" spans="1:19">
+    <row r="724" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A724" s="4"/>
       <c r="B724" s="5"/>
       <c r="C724" s="4"/>
@@ -15601,7 +15601,7 @@
       <c r="R724" s="4"/>
       <c r="S724" s="4"/>
     </row>
-    <row r="725" spans="1:19">
+    <row r="725" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A725" s="4"/>
       <c r="B725" s="5"/>
       <c r="C725" s="4"/>
@@ -15622,7 +15622,7 @@
       <c r="R725" s="4"/>
       <c r="S725" s="4"/>
     </row>
-    <row r="726" spans="1:19">
+    <row r="726" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A726" s="4"/>
       <c r="B726" s="5"/>
       <c r="C726" s="4"/>
@@ -15643,7 +15643,7 @@
       <c r="R726" s="4"/>
       <c r="S726" s="4"/>
     </row>
-    <row r="727" spans="1:19">
+    <row r="727" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A727" s="4"/>
       <c r="B727" s="5"/>
       <c r="C727" s="4"/>
@@ -15664,7 +15664,7 @@
       <c r="R727" s="4"/>
       <c r="S727" s="4"/>
     </row>
-    <row r="728" spans="1:19">
+    <row r="728" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A728" s="4"/>
       <c r="B728" s="5"/>
       <c r="C728" s="4"/>
@@ -15685,7 +15685,7 @@
       <c r="R728" s="4"/>
       <c r="S728" s="4"/>
     </row>
-    <row r="729" spans="1:19">
+    <row r="729" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A729" s="4"/>
       <c r="B729" s="5"/>
       <c r="C729" s="4"/>
@@ -15706,7 +15706,7 @@
       <c r="R729" s="4"/>
       <c r="S729" s="4"/>
     </row>
-    <row r="730" spans="1:19">
+    <row r="730" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A730" s="4"/>
       <c r="B730" s="5"/>
       <c r="C730" s="4"/>
@@ -15727,7 +15727,7 @@
       <c r="R730" s="4"/>
       <c r="S730" s="4"/>
     </row>
-    <row r="731" spans="1:19">
+    <row r="731" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A731" s="4"/>
       <c r="B731" s="5"/>
       <c r="C731" s="4"/>
@@ -15748,7 +15748,7 @@
       <c r="R731" s="4"/>
       <c r="S731" s="4"/>
     </row>
-    <row r="732" spans="1:19">
+    <row r="732" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A732" s="4"/>
       <c r="B732" s="5"/>
       <c r="C732" s="4"/>
@@ -15769,7 +15769,7 @@
       <c r="R732" s="4"/>
       <c r="S732" s="4"/>
     </row>
-    <row r="733" spans="1:19">
+    <row r="733" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A733" s="4"/>
       <c r="B733" s="5"/>
       <c r="C733" s="4"/>
@@ -15790,7 +15790,7 @@
       <c r="R733" s="4"/>
       <c r="S733" s="4"/>
     </row>
-    <row r="734" spans="1:19">
+    <row r="734" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A734" s="4"/>
       <c r="B734" s="5"/>
       <c r="C734" s="4"/>
@@ -15811,7 +15811,7 @@
       <c r="R734" s="4"/>
       <c r="S734" s="4"/>
     </row>
-    <row r="735" spans="1:19">
+    <row r="735" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A735" s="4"/>
       <c r="B735" s="5"/>
       <c r="C735" s="4"/>
@@ -15832,7 +15832,7 @@
       <c r="R735" s="4"/>
       <c r="S735" s="4"/>
     </row>
-    <row r="736" spans="1:19">
+    <row r="736" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A736" s="4"/>
       <c r="B736" s="5"/>
       <c r="C736" s="4"/>
@@ -15853,7 +15853,7 @@
       <c r="R736" s="4"/>
       <c r="S736" s="4"/>
     </row>
-    <row r="737" spans="1:19">
+    <row r="737" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A737" s="4"/>
       <c r="B737" s="5"/>
       <c r="C737" s="4"/>
@@ -15874,7 +15874,7 @@
       <c r="R737" s="4"/>
       <c r="S737" s="4"/>
     </row>
-    <row r="738" spans="1:19">
+    <row r="738" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A738" s="4"/>
       <c r="B738" s="5"/>
       <c r="C738" s="4"/>
@@ -15895,7 +15895,7 @@
       <c r="R738" s="4"/>
       <c r="S738" s="4"/>
     </row>
-    <row r="739" spans="1:19">
+    <row r="739" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A739" s="4"/>
       <c r="B739" s="5"/>
       <c r="C739" s="4"/>
@@ -15916,7 +15916,7 @@
       <c r="R739" s="4"/>
       <c r="S739" s="4"/>
     </row>
-    <row r="740" spans="1:19">
+    <row r="740" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A740" s="4"/>
       <c r="B740" s="5"/>
       <c r="C740" s="4"/>
@@ -15937,7 +15937,7 @@
       <c r="R740" s="4"/>
       <c r="S740" s="4"/>
     </row>
-    <row r="741" spans="1:19">
+    <row r="741" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A741" s="4"/>
       <c r="B741" s="5"/>
       <c r="C741" s="4"/>
@@ -15958,7 +15958,7 @@
       <c r="R741" s="4"/>
       <c r="S741" s="4"/>
     </row>
-    <row r="742" spans="1:19">
+    <row r="742" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A742" s="4"/>
       <c r="B742" s="5"/>
       <c r="C742" s="4"/>
@@ -15979,7 +15979,7 @@
       <c r="R742" s="4"/>
       <c r="S742" s="4"/>
     </row>
-    <row r="743" spans="1:19">
+    <row r="743" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A743" s="4"/>
       <c r="B743" s="5"/>
       <c r="C743" s="4"/>
@@ -16000,7 +16000,7 @@
       <c r="R743" s="4"/>
       <c r="S743" s="4"/>
     </row>
-    <row r="744" spans="1:19">
+    <row r="744" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A744" s="4"/>
       <c r="B744" s="5"/>
       <c r="C744" s="4"/>
@@ -16021,7 +16021,7 @@
       <c r="R744" s="4"/>
       <c r="S744" s="4"/>
     </row>
-    <row r="745" spans="1:19">
+    <row r="745" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A745" s="4"/>
       <c r="B745" s="5"/>
       <c r="C745" s="4"/>
@@ -16042,7 +16042,7 @@
       <c r="R745" s="4"/>
       <c r="S745" s="4"/>
     </row>
-    <row r="746" spans="1:19">
+    <row r="746" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A746" s="4"/>
       <c r="B746" s="5"/>
       <c r="C746" s="4"/>
@@ -16063,7 +16063,7 @@
       <c r="R746" s="4"/>
       <c r="S746" s="4"/>
     </row>
-    <row r="747" spans="1:19">
+    <row r="747" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A747" s="4"/>
       <c r="B747" s="5"/>
       <c r="C747" s="4"/>
@@ -16084,7 +16084,7 @@
       <c r="R747" s="4"/>
       <c r="S747" s="4"/>
     </row>
-    <row r="748" spans="1:19">
+    <row r="748" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A748" s="4"/>
       <c r="B748" s="5"/>
       <c r="C748" s="4"/>
@@ -16105,7 +16105,7 @@
       <c r="R748" s="4"/>
       <c r="S748" s="4"/>
     </row>
-    <row r="749" spans="1:19">
+    <row r="749" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A749" s="4"/>
       <c r="B749" s="5"/>
       <c r="C749" s="4"/>
@@ -16126,7 +16126,7 @@
       <c r="R749" s="4"/>
       <c r="S749" s="4"/>
     </row>
-    <row r="750" spans="1:19">
+    <row r="750" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A750" s="4"/>
       <c r="B750" s="5"/>
       <c r="C750" s="4"/>
@@ -16147,7 +16147,7 @@
       <c r="R750" s="4"/>
       <c r="S750" s="4"/>
     </row>
-    <row r="751" spans="1:19">
+    <row r="751" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A751" s="4"/>
       <c r="B751" s="5"/>
       <c r="C751" s="4"/>
@@ -16168,7 +16168,7 @@
       <c r="R751" s="4"/>
       <c r="S751" s="4"/>
     </row>
-    <row r="752" spans="1:19">
+    <row r="752" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A752" s="4"/>
       <c r="B752" s="5"/>
       <c r="C752" s="4"/>
@@ -16189,7 +16189,7 @@
       <c r="R752" s="4"/>
       <c r="S752" s="4"/>
     </row>
-    <row r="753" spans="1:19">
+    <row r="753" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A753" s="4"/>
       <c r="B753" s="5"/>
       <c r="C753" s="4"/>
@@ -16210,7 +16210,7 @@
       <c r="R753" s="4"/>
       <c r="S753" s="4"/>
     </row>
-    <row r="754" spans="1:19">
+    <row r="754" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A754" s="4"/>
       <c r="B754" s="5"/>
       <c r="C754" s="4"/>
@@ -16231,7 +16231,7 @@
       <c r="R754" s="4"/>
       <c r="S754" s="4"/>
     </row>
-    <row r="755" spans="1:19">
+    <row r="755" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A755" s="4"/>
       <c r="B755" s="5"/>
       <c r="C755" s="4"/>
@@ -16252,7 +16252,7 @@
       <c r="R755" s="4"/>
       <c r="S755" s="4"/>
     </row>
-    <row r="756" spans="1:19">
+    <row r="756" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A756" s="4"/>
       <c r="B756" s="5"/>
       <c r="C756" s="4"/>
@@ -16273,7 +16273,7 @@
       <c r="R756" s="4"/>
       <c r="S756" s="4"/>
     </row>
-    <row r="757" spans="1:19">
+    <row r="757" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A757" s="4"/>
       <c r="B757" s="5"/>
       <c r="C757" s="4"/>
@@ -16294,7 +16294,7 @@
       <c r="R757" s="4"/>
       <c r="S757" s="4"/>
     </row>
-    <row r="758" spans="1:19">
+    <row r="758" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A758" s="4"/>
       <c r="B758" s="5"/>
       <c r="C758" s="4"/>
@@ -16315,7 +16315,7 @@
       <c r="R758" s="4"/>
       <c r="S758" s="4"/>
     </row>
-    <row r="759" spans="1:19">
+    <row r="759" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A759" s="4"/>
       <c r="B759" s="5"/>
       <c r="C759" s="4"/>
@@ -16336,7 +16336,7 @@
       <c r="R759" s="4"/>
       <c r="S759" s="4"/>
     </row>
-    <row r="760" spans="1:19">
+    <row r="760" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A760" s="4"/>
       <c r="B760" s="5"/>
       <c r="C760" s="4"/>
@@ -16357,7 +16357,7 @@
       <c r="R760" s="4"/>
       <c r="S760" s="4"/>
     </row>
-    <row r="761" spans="1:19">
+    <row r="761" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A761" s="4"/>
       <c r="B761" s="5"/>
       <c r="C761" s="4"/>
@@ -16378,7 +16378,7 @@
       <c r="R761" s="4"/>
       <c r="S761" s="4"/>
     </row>
-    <row r="762" spans="1:19">
+    <row r="762" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A762" s="4"/>
       <c r="B762" s="5"/>
       <c r="C762" s="4"/>
@@ -16399,7 +16399,7 @@
       <c r="R762" s="4"/>
       <c r="S762" s="4"/>
     </row>
-    <row r="763" spans="1:19">
+    <row r="763" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A763" s="4"/>
       <c r="B763" s="5"/>
       <c r="C763" s="4"/>
@@ -16420,7 +16420,7 @@
       <c r="R763" s="4"/>
       <c r="S763" s="4"/>
     </row>
-    <row r="764" spans="1:19">
+    <row r="764" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A764" s="4"/>
       <c r="B764" s="5"/>
       <c r="C764" s="4"/>
@@ -16441,7 +16441,7 @@
       <c r="R764" s="4"/>
       <c r="S764" s="4"/>
     </row>
-    <row r="765" spans="1:19">
+    <row r="765" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A765" s="4"/>
       <c r="B765" s="5"/>
       <c r="C765" s="4"/>
@@ -16462,7 +16462,7 @@
       <c r="R765" s="4"/>
       <c r="S765" s="4"/>
     </row>
-    <row r="766" spans="1:19">
+    <row r="766" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A766" s="4"/>
       <c r="B766" s="5"/>
       <c r="C766" s="4"/>
@@ -16483,7 +16483,7 @@
       <c r="R766" s="4"/>
       <c r="S766" s="4"/>
     </row>
-    <row r="767" spans="1:19">
+    <row r="767" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A767" s="4"/>
       <c r="B767" s="5"/>
       <c r="C767" s="4"/>
@@ -16504,7 +16504,7 @@
       <c r="R767" s="4"/>
       <c r="S767" s="4"/>
     </row>
-    <row r="768" spans="1:19">
+    <row r="768" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A768" s="4"/>
       <c r="B768" s="5"/>
       <c r="C768" s="4"/>
@@ -16525,7 +16525,7 @@
       <c r="R768" s="4"/>
       <c r="S768" s="4"/>
     </row>
-    <row r="769" spans="1:19">
+    <row r="769" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A769" s="4"/>
       <c r="B769" s="5"/>
       <c r="C769" s="4"/>
@@ -16546,7 +16546,7 @@
       <c r="R769" s="4"/>
       <c r="S769" s="4"/>
     </row>
-    <row r="770" spans="1:19">
+    <row r="770" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A770" s="4"/>
       <c r="B770" s="5"/>
       <c r="C770" s="4"/>
@@ -16567,7 +16567,7 @@
       <c r="R770" s="4"/>
       <c r="S770" s="4"/>
     </row>
-    <row r="771" spans="1:19">
+    <row r="771" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A771" s="4"/>
       <c r="B771" s="5"/>
       <c r="C771" s="4"/>
@@ -16588,7 +16588,7 @@
       <c r="R771" s="4"/>
       <c r="S771" s="4"/>
     </row>
-    <row r="772" spans="1:19">
+    <row r="772" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A772" s="4"/>
       <c r="B772" s="5"/>
       <c r="C772" s="4"/>
@@ -16609,7 +16609,7 @@
       <c r="R772" s="4"/>
       <c r="S772" s="4"/>
     </row>
-    <row r="773" spans="1:19">
+    <row r="773" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A773" s="4"/>
       <c r="B773" s="5"/>
       <c r="C773" s="4"/>
@@ -16630,7 +16630,7 @@
       <c r="R773" s="4"/>
       <c r="S773" s="4"/>
     </row>
-    <row r="774" spans="1:19">
+    <row r="774" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A774" s="4"/>
       <c r="B774" s="5"/>
       <c r="C774" s="4"/>
@@ -16651,7 +16651,7 @@
       <c r="R774" s="4"/>
       <c r="S774" s="4"/>
     </row>
-    <row r="775" spans="1:19">
+    <row r="775" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A775" s="4"/>
       <c r="B775" s="5"/>
       <c r="C775" s="4"/>
@@ -16672,7 +16672,7 @@
       <c r="R775" s="4"/>
       <c r="S775" s="4"/>
     </row>
-    <row r="776" spans="1:19">
+    <row r="776" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A776" s="4"/>
       <c r="B776" s="5"/>
       <c r="C776" s="4"/>
@@ -16693,7 +16693,7 @@
       <c r="R776" s="4"/>
       <c r="S776" s="4"/>
     </row>
-    <row r="777" spans="1:19">
+    <row r="777" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A777" s="4"/>
       <c r="B777" s="5"/>
       <c r="C777" s="4"/>
@@ -16714,7 +16714,7 @@
       <c r="R777" s="4"/>
       <c r="S777" s="4"/>
     </row>
-    <row r="778" spans="1:19">
+    <row r="778" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A778" s="4"/>
       <c r="B778" s="5"/>
       <c r="C778" s="4"/>
@@ -16735,7 +16735,7 @@
       <c r="R778" s="4"/>
       <c r="S778" s="4"/>
     </row>
-    <row r="779" spans="1:19">
+    <row r="779" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A779" s="4"/>
       <c r="B779" s="5"/>
       <c r="C779" s="4"/>
@@ -16756,7 +16756,7 @@
       <c r="R779" s="4"/>
       <c r="S779" s="4"/>
     </row>
-    <row r="780" spans="1:19">
+    <row r="780" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A780" s="4"/>
       <c r="B780" s="5"/>
       <c r="C780" s="4"/>
@@ -16777,7 +16777,7 @@
       <c r="R780" s="4"/>
       <c r="S780" s="4"/>
     </row>
-    <row r="781" spans="1:19">
+    <row r="781" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A781" s="4"/>
       <c r="B781" s="5"/>
       <c r="C781" s="4"/>
@@ -16798,7 +16798,7 @@
       <c r="R781" s="4"/>
       <c r="S781" s="4"/>
     </row>
-    <row r="782" spans="1:19">
+    <row r="782" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A782" s="4"/>
       <c r="B782" s="5"/>
       <c r="C782" s="4"/>
@@ -16819,7 +16819,7 @@
       <c r="R782" s="4"/>
       <c r="S782" s="4"/>
     </row>
-    <row r="783" spans="1:19">
+    <row r="783" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A783" s="4"/>
       <c r="B783" s="5"/>
       <c r="C783" s="4"/>
@@ -16840,7 +16840,7 @@
       <c r="R783" s="4"/>
       <c r="S783" s="4"/>
     </row>
-    <row r="784" spans="1:19">
+    <row r="784" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A784" s="4"/>
       <c r="B784" s="5"/>
       <c r="C784" s="4"/>
@@ -16861,7 +16861,7 @@
       <c r="R784" s="4"/>
       <c r="S784" s="4"/>
     </row>
-    <row r="785" spans="1:19">
+    <row r="785" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A785" s="4"/>
       <c r="B785" s="5"/>
       <c r="C785" s="4"/>
@@ -16882,7 +16882,7 @@
       <c r="R785" s="4"/>
       <c r="S785" s="4"/>
     </row>
-    <row r="786" spans="1:19">
+    <row r="786" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A786" s="4"/>
       <c r="B786" s="5"/>
       <c r="C786" s="4"/>
@@ -16903,7 +16903,7 @@
       <c r="R786" s="4"/>
       <c r="S786" s="4"/>
     </row>
-    <row r="787" spans="1:19">
+    <row r="787" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A787" s="4"/>
       <c r="B787" s="5"/>
       <c r="C787" s="4"/>
@@ -16924,7 +16924,7 @@
       <c r="R787" s="4"/>
       <c r="S787" s="4"/>
     </row>
-    <row r="788" spans="1:19">
+    <row r="788" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A788" s="4"/>
       <c r="B788" s="5"/>
       <c r="C788" s="4"/>
@@ -16945,7 +16945,7 @@
       <c r="R788" s="4"/>
       <c r="S788" s="4"/>
     </row>
-    <row r="789" spans="1:19">
+    <row r="789" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A789" s="4"/>
       <c r="B789" s="5"/>
       <c r="C789" s="4"/>
@@ -16966,7 +16966,7 @@
       <c r="R789" s="4"/>
       <c r="S789" s="4"/>
     </row>
-    <row r="790" spans="1:19">
+    <row r="790" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A790" s="4"/>
       <c r="B790" s="5"/>
       <c r="C790" s="4"/>
@@ -16987,7 +16987,7 @@
       <c r="R790" s="4"/>
       <c r="S790" s="4"/>
     </row>
-    <row r="791" spans="1:19">
+    <row r="791" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A791" s="4"/>
       <c r="B791" s="5"/>
       <c r="C791" s="4"/>
@@ -17008,7 +17008,7 @@
       <c r="R791" s="4"/>
       <c r="S791" s="4"/>
     </row>
-    <row r="792" spans="1:19">
+    <row r="792" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A792" s="4"/>
       <c r="B792" s="5"/>
       <c r="C792" s="4"/>
@@ -17029,7 +17029,7 @@
       <c r="R792" s="4"/>
       <c r="S792" s="4"/>
     </row>
-    <row r="793" spans="1:19">
+    <row r="793" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A793" s="4"/>
       <c r="B793" s="5"/>
       <c r="C793" s="4"/>
@@ -17050,7 +17050,7 @@
       <c r="R793" s="4"/>
       <c r="S793" s="4"/>
     </row>
-    <row r="794" spans="1:19">
+    <row r="794" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A794" s="4"/>
       <c r="B794" s="5"/>
       <c r="C794" s="4"/>
@@ -17071,7 +17071,7 @@
       <c r="R794" s="4"/>
       <c r="S794" s="4"/>
     </row>
-    <row r="795" spans="1:19">
+    <row r="795" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A795" s="4"/>
       <c r="B795" s="5"/>
       <c r="C795" s="4"/>
@@ -17092,7 +17092,7 @@
       <c r="R795" s="4"/>
       <c r="S795" s="4"/>
     </row>
-    <row r="796" spans="1:19">
+    <row r="796" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A796" s="4"/>
       <c r="B796" s="5"/>
       <c r="C796" s="4"/>
@@ -17113,7 +17113,7 @@
       <c r="R796" s="4"/>
       <c r="S796" s="4"/>
     </row>
-    <row r="797" spans="1:19">
+    <row r="797" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A797" s="4"/>
       <c r="B797" s="5"/>
       <c r="C797" s="4"/>
@@ -17134,7 +17134,7 @@
       <c r="R797" s="4"/>
       <c r="S797" s="4"/>
     </row>
-    <row r="798" spans="1:19">
+    <row r="798" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A798" s="4"/>
       <c r="B798" s="5"/>
       <c r="C798" s="4"/>
@@ -17155,7 +17155,7 @@
       <c r="R798" s="4"/>
       <c r="S798" s="4"/>
     </row>
-    <row r="799" spans="1:19">
+    <row r="799" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A799" s="4"/>
       <c r="B799" s="5"/>
       <c r="C799" s="4"/>
@@ -17176,7 +17176,7 @@
       <c r="R799" s="4"/>
       <c r="S799" s="4"/>
     </row>
-    <row r="800" spans="1:19">
+    <row r="800" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A800" s="4"/>
       <c r="B800" s="5"/>
       <c r="C800" s="4"/>
@@ -17197,7 +17197,7 @@
       <c r="R800" s="4"/>
       <c r="S800" s="4"/>
     </row>
-    <row r="801" spans="1:19">
+    <row r="801" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A801" s="4"/>
       <c r="B801" s="5"/>
       <c r="C801" s="4"/>
@@ -17218,7 +17218,7 @@
       <c r="R801" s="4"/>
       <c r="S801" s="4"/>
     </row>
-    <row r="802" spans="1:19">
+    <row r="802" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A802" s="4"/>
       <c r="B802" s="5"/>
       <c r="C802" s="4"/>
@@ -17239,7 +17239,7 @@
       <c r="R802" s="4"/>
       <c r="S802" s="4"/>
     </row>
-    <row r="803" spans="1:19">
+    <row r="803" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A803" s="4"/>
       <c r="B803" s="5"/>
       <c r="C803" s="4"/>
@@ -17260,7 +17260,7 @@
       <c r="R803" s="4"/>
       <c r="S803" s="4"/>
     </row>
-    <row r="804" spans="1:19">
+    <row r="804" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A804" s="4"/>
       <c r="B804" s="5"/>
       <c r="C804" s="4"/>
@@ -17281,7 +17281,7 @@
       <c r="R804" s="4"/>
       <c r="S804" s="4"/>
     </row>
-    <row r="805" spans="1:19">
+    <row r="805" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A805" s="4"/>
       <c r="B805" s="5"/>
       <c r="C805" s="4"/>
@@ -17302,7 +17302,7 @@
       <c r="R805" s="4"/>
       <c r="S805" s="4"/>
     </row>
-    <row r="806" spans="1:19">
+    <row r="806" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A806" s="4"/>
       <c r="B806" s="5"/>
       <c r="C806" s="4"/>
@@ -17323,7 +17323,7 @@
       <c r="R806" s="4"/>
       <c r="S806" s="4"/>
     </row>
-    <row r="807" spans="1:19">
+    <row r="807" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A807" s="4"/>
       <c r="B807" s="5"/>
       <c r="C807" s="4"/>
@@ -17344,7 +17344,7 @@
       <c r="R807" s="4"/>
       <c r="S807" s="4"/>
     </row>
-    <row r="808" spans="1:19">
+    <row r="808" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A808" s="4"/>
       <c r="B808" s="5"/>
       <c r="C808" s="4"/>
@@ -17365,7 +17365,7 @@
       <c r="R808" s="4"/>
       <c r="S808" s="4"/>
     </row>
-    <row r="809" spans="1:19">
+    <row r="809" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A809" s="4"/>
       <c r="B809" s="5"/>
       <c r="C809" s="4"/>
@@ -17386,7 +17386,7 @@
       <c r="R809" s="4"/>
       <c r="S809" s="4"/>
     </row>
-    <row r="810" spans="1:19">
+    <row r="810" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A810" s="4"/>
       <c r="B810" s="5"/>
       <c r="C810" s="4"/>
@@ -17407,7 +17407,7 @@
       <c r="R810" s="4"/>
       <c r="S810" s="4"/>
     </row>
-    <row r="811" spans="1:19">
+    <row r="811" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A811" s="4"/>
       <c r="B811" s="5"/>
       <c r="C811" s="4"/>
@@ -17428,7 +17428,7 @@
       <c r="R811" s="4"/>
       <c r="S811" s="4"/>
     </row>
-    <row r="812" spans="1:19">
+    <row r="812" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A812" s="4"/>
       <c r="B812" s="5"/>
       <c r="C812" s="4"/>
@@ -17449,7 +17449,7 @@
       <c r="R812" s="4"/>
       <c r="S812" s="4"/>
     </row>
-    <row r="813" spans="1:19">
+    <row r="813" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A813" s="4"/>
       <c r="B813" s="5"/>
       <c r="C813" s="4"/>
@@ -17470,7 +17470,7 @@
       <c r="R813" s="4"/>
       <c r="S813" s="4"/>
     </row>
-    <row r="814" spans="1:19">
+    <row r="814" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A814" s="4"/>
       <c r="B814" s="5"/>
       <c r="C814" s="4"/>
@@ -17491,7 +17491,7 @@
       <c r="R814" s="4"/>
       <c r="S814" s="4"/>
     </row>
-    <row r="815" spans="1:19">
+    <row r="815" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A815" s="4"/>
       <c r="B815" s="5"/>
       <c r="C815" s="4"/>
@@ -17512,7 +17512,7 @@
       <c r="R815" s="4"/>
       <c r="S815" s="4"/>
     </row>
-    <row r="816" spans="1:19">
+    <row r="816" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A816" s="4"/>
       <c r="B816" s="5"/>
       <c r="C816" s="4"/>
@@ -17533,7 +17533,7 @@
       <c r="R816" s="4"/>
       <c r="S816" s="4"/>
     </row>
-    <row r="817" spans="1:19">
+    <row r="817" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A817" s="4"/>
       <c r="B817" s="5"/>
       <c r="C817" s="4"/>
@@ -17554,7 +17554,7 @@
       <c r="R817" s="4"/>
       <c r="S817" s="4"/>
     </row>
-    <row r="818" spans="1:19">
+    <row r="818" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A818" s="4"/>
       <c r="B818" s="5"/>
       <c r="C818" s="4"/>
@@ -17575,7 +17575,7 @@
       <c r="R818" s="4"/>
       <c r="S818" s="4"/>
     </row>
-    <row r="819" spans="1:19">
+    <row r="819" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A819" s="4"/>
       <c r="B819" s="5"/>
       <c r="C819" s="4"/>
@@ -17596,7 +17596,7 @@
       <c r="R819" s="4"/>
       <c r="S819" s="4"/>
     </row>
-    <row r="820" spans="1:19">
+    <row r="820" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A820" s="4"/>
       <c r="B820" s="5"/>
       <c r="C820" s="4"/>
@@ -17617,7 +17617,7 @@
       <c r="R820" s="4"/>
       <c r="S820" s="4"/>
     </row>
-    <row r="821" spans="1:19">
+    <row r="821" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A821" s="4"/>
       <c r="B821" s="5"/>
       <c r="C821" s="4"/>
@@ -17638,7 +17638,7 @@
       <c r="R821" s="4"/>
       <c r="S821" s="4"/>
     </row>
-    <row r="822" spans="1:19">
+    <row r="822" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A822" s="4"/>
       <c r="B822" s="5"/>
       <c r="C822" s="4"/>
@@ -17659,7 +17659,7 @@
       <c r="R822" s="4"/>
       <c r="S822" s="4"/>
     </row>
-    <row r="823" spans="1:19">
+    <row r="823" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A823" s="4"/>
       <c r="B823" s="5"/>
       <c r="C823" s="4"/>
@@ -17680,7 +17680,7 @@
       <c r="R823" s="4"/>
       <c r="S823" s="4"/>
     </row>
-    <row r="824" spans="1:19">
+    <row r="824" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A824" s="4"/>
       <c r="B824" s="5"/>
       <c r="C824" s="4"/>
@@ -17701,7 +17701,7 @@
       <c r="R824" s="4"/>
       <c r="S824" s="4"/>
     </row>
-    <row r="825" spans="1:19">
+    <row r="825" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A825" s="4"/>
       <c r="B825" s="5"/>
       <c r="C825" s="4"/>
@@ -17722,7 +17722,7 @@
       <c r="R825" s="4"/>
       <c r="S825" s="4"/>
     </row>
-    <row r="826" spans="1:19">
+    <row r="826" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A826" s="4"/>
       <c r="B826" s="5"/>
       <c r="C826" s="4"/>
@@ -17743,7 +17743,7 @@
       <c r="R826" s="4"/>
       <c r="S826" s="4"/>
     </row>
-    <row r="827" spans="1:19">
+    <row r="827" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A827" s="4"/>
       <c r="B827" s="5"/>
       <c r="C827" s="4"/>
@@ -17764,7 +17764,7 @@
       <c r="R827" s="4"/>
       <c r="S827" s="4"/>
     </row>
-    <row r="828" spans="1:19">
+    <row r="828" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A828" s="4"/>
       <c r="B828" s="5"/>
       <c r="C828" s="4"/>
@@ -17785,7 +17785,7 @@
       <c r="R828" s="4"/>
       <c r="S828" s="4"/>
     </row>
-    <row r="829" spans="1:19">
+    <row r="829" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A829" s="4"/>
       <c r="B829" s="5"/>
       <c r="C829" s="4"/>
@@ -17806,7 +17806,7 @@
       <c r="R829" s="4"/>
       <c r="S829" s="4"/>
     </row>
-    <row r="830" spans="1:19">
+    <row r="830" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A830" s="4"/>
       <c r="B830" s="5"/>
       <c r="C830" s="4"/>
@@ -17827,7 +17827,7 @@
       <c r="R830" s="4"/>
       <c r="S830" s="4"/>
     </row>
-    <row r="831" spans="1:19">
+    <row r="831" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A831" s="4"/>
       <c r="B831" s="5"/>
       <c r="C831" s="4"/>
@@ -17848,7 +17848,7 @@
       <c r="R831" s="4"/>
       <c r="S831" s="4"/>
     </row>
-    <row r="832" spans="1:19">
+    <row r="832" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A832" s="4"/>
       <c r="B832" s="5"/>
       <c r="C832" s="4"/>
@@ -17869,7 +17869,7 @@
       <c r="R832" s="4"/>
       <c r="S832" s="4"/>
     </row>
-    <row r="833" spans="1:19">
+    <row r="833" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A833" s="4"/>
       <c r="B833" s="5"/>
       <c r="C833" s="4"/>
@@ -17890,7 +17890,7 @@
       <c r="R833" s="4"/>
       <c r="S833" s="4"/>
     </row>
-    <row r="834" spans="1:19">
+    <row r="834" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A834" s="4"/>
       <c r="B834" s="5"/>
       <c r="C834" s="4"/>
@@ -17911,7 +17911,7 @@
       <c r="R834" s="4"/>
       <c r="S834" s="4"/>
     </row>
-    <row r="835" spans="1:19">
+    <row r="835" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A835" s="4"/>
       <c r="B835" s="5"/>
       <c r="C835" s="4"/>
@@ -17932,7 +17932,7 @@
       <c r="R835" s="4"/>
       <c r="S835" s="4"/>
     </row>
-    <row r="836" spans="1:19">
+    <row r="836" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A836" s="4"/>
       <c r="B836" s="5"/>
       <c r="C836" s="4"/>
@@ -17953,7 +17953,7 @@
       <c r="R836" s="4"/>
       <c r="S836" s="4"/>
     </row>
-    <row r="837" spans="1:19">
+    <row r="837" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A837" s="4"/>
       <c r="B837" s="5"/>
       <c r="C837" s="4"/>
@@ -17974,7 +17974,7 @@
       <c r="R837" s="4"/>
       <c r="S837" s="4"/>
     </row>
-    <row r="838" spans="1:19">
+    <row r="838" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A838" s="4"/>
       <c r="B838" s="5"/>
       <c r="C838" s="4"/>
@@ -17995,7 +17995,7 @@
       <c r="R838" s="4"/>
       <c r="S838" s="4"/>
     </row>
-    <row r="839" spans="1:19">
+    <row r="839" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A839" s="4"/>
       <c r="B839" s="5"/>
       <c r="C839" s="4"/>
@@ -18016,7 +18016,7 @@
       <c r="R839" s="4"/>
       <c r="S839" s="4"/>
     </row>
-    <row r="840" spans="1:19">
+    <row r="840" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A840" s="4"/>
       <c r="B840" s="5"/>
       <c r="C840" s="4"/>
@@ -18037,7 +18037,7 @@
       <c r="R840" s="4"/>
       <c r="S840" s="4"/>
     </row>
-    <row r="841" spans="1:19">
+    <row r="841" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A841" s="4"/>
       <c r="B841" s="5"/>
       <c r="C841" s="4"/>
@@ -18058,7 +18058,7 @@
       <c r="R841" s="4"/>
       <c r="S841" s="4"/>
     </row>
-    <row r="842" spans="1:19">
+    <row r="842" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A842" s="4"/>
       <c r="B842" s="5"/>
       <c r="C842" s="4"/>
@@ -18079,7 +18079,7 @@
       <c r="R842" s="4"/>
       <c r="S842" s="4"/>
     </row>
-    <row r="843" spans="1:19">
+    <row r="843" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A843" s="4"/>
       <c r="B843" s="5"/>
       <c r="C843" s="4"/>
@@ -18100,7 +18100,7 @@
       <c r="R843" s="4"/>
       <c r="S843" s="4"/>
     </row>
-    <row r="844" spans="1:19">
+    <row r="844" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A844" s="4"/>
       <c r="B844" s="5"/>
       <c r="C844" s="4"/>
@@ -18121,7 +18121,7 @@
       <c r="R844" s="4"/>
       <c r="S844" s="4"/>
     </row>
-    <row r="845" spans="1:19">
+    <row r="845" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A845" s="4"/>
       <c r="B845" s="5"/>
       <c r="C845" s="4"/>
@@ -18142,7 +18142,7 @@
       <c r="R845" s="4"/>
       <c r="S845" s="4"/>
     </row>
-    <row r="846" spans="1:19">
+    <row r="846" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A846" s="4"/>
       <c r="B846" s="5"/>
       <c r="C846" s="4"/>
@@ -18163,7 +18163,7 @@
       <c r="R846" s="4"/>
       <c r="S846" s="4"/>
     </row>
-    <row r="847" spans="1:19">
+    <row r="847" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A847" s="4"/>
       <c r="B847" s="5"/>
       <c r="C847" s="4"/>
@@ -18184,7 +18184,7 @@
       <c r="R847" s="4"/>
       <c r="S847" s="4"/>
     </row>
-    <row r="848" spans="1:19">
+    <row r="848" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A848" s="4"/>
       <c r="B848" s="5"/>
       <c r="C848" s="4"/>
@@ -18205,7 +18205,7 @@
       <c r="R848" s="4"/>
       <c r="S848" s="4"/>
     </row>
-    <row r="849" spans="1:19">
+    <row r="849" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A849" s="4"/>
       <c r="B849" s="5"/>
       <c r="C849" s="4"/>
@@ -18226,7 +18226,7 @@
       <c r="R849" s="4"/>
       <c r="S849" s="4"/>
     </row>
-    <row r="850" spans="1:19">
+    <row r="850" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A850" s="4"/>
       <c r="B850" s="5"/>
       <c r="C850" s="4"/>
@@ -18247,7 +18247,7 @@
       <c r="R850" s="4"/>
       <c r="S850" s="4"/>
     </row>
-    <row r="851" spans="1:19">
+    <row r="851" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A851" s="4"/>
       <c r="B851" s="5"/>
       <c r="C851" s="4"/>
@@ -18268,7 +18268,7 @@
       <c r="R851" s="4"/>
       <c r="S851" s="4"/>
     </row>
-    <row r="852" spans="1:19">
+    <row r="852" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A852" s="4"/>
       <c r="B852" s="5"/>
       <c r="C852" s="4"/>
@@ -18289,7 +18289,7 @@
       <c r="R852" s="4"/>
       <c r="S852" s="4"/>
     </row>
-    <row r="853" spans="1:19">
+    <row r="853" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A853" s="4"/>
       <c r="B853" s="5"/>
       <c r="C853" s="4"/>
@@ -18310,7 +18310,7 @@
       <c r="R853" s="4"/>
       <c r="S853" s="4"/>
     </row>
-    <row r="854" spans="1:19">
+    <row r="854" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A854" s="4"/>
       <c r="B854" s="5"/>
       <c r="C854" s="4"/>
@@ -18331,7 +18331,7 @@
       <c r="R854" s="4"/>
       <c r="S854" s="4"/>
     </row>
-    <row r="855" spans="1:19">
+    <row r="855" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A855" s="4"/>
       <c r="B855" s="5"/>
       <c r="C855" s="4"/>
@@ -18352,7 +18352,7 @@
       <c r="R855" s="4"/>
       <c r="S855" s="4"/>
     </row>
-    <row r="856" spans="1:19">
+    <row r="856" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A856" s="4"/>
       <c r="B856" s="5"/>
       <c r="C856" s="4"/>
@@ -18373,7 +18373,7 @@
       <c r="R856" s="4"/>
       <c r="S856" s="4"/>
     </row>
-    <row r="857" spans="1:19">
+    <row r="857" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A857" s="4"/>
       <c r="B857" s="5"/>
       <c r="C857" s="4"/>
@@ -18394,7 +18394,7 @@
       <c r="R857" s="4"/>
       <c r="S857" s="4"/>
     </row>
-    <row r="858" spans="1:19">
+    <row r="858" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A858" s="4"/>
       <c r="B858" s="5"/>
       <c r="C858" s="4"/>
@@ -18415,7 +18415,7 @@
       <c r="R858" s="4"/>
       <c r="S858" s="4"/>
     </row>
-    <row r="859" spans="1:19">
+    <row r="859" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A859" s="4"/>
       <c r="B859" s="5"/>
       <c r="C859" s="4"/>
@@ -18436,7 +18436,7 @@
       <c r="R859" s="4"/>
       <c r="S859" s="4"/>
     </row>
-    <row r="860" spans="1:19">
+    <row r="860" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A860" s="4"/>
       <c r="B860" s="5"/>
       <c r="C860" s="4"/>
@@ -18457,7 +18457,7 @@
       <c r="R860" s="4"/>
       <c r="S860" s="4"/>
     </row>
-    <row r="861" spans="1:19">
+    <row r="861" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A861" s="4"/>
       <c r="B861" s="5"/>
       <c r="C861" s="4"/>
@@ -18478,7 +18478,7 @@
       <c r="R861" s="4"/>
       <c r="S861" s="4"/>
     </row>
-    <row r="862" spans="1:19">
+    <row r="862" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A862" s="4"/>
       <c r="B862" s="5"/>
       <c r="C862" s="4"/>
@@ -18499,7 +18499,7 @@
       <c r="R862" s="4"/>
       <c r="S862" s="4"/>
     </row>
-    <row r="863" spans="1:19">
+    <row r="863" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A863" s="4"/>
       <c r="B863" s="5"/>
       <c r="C863" s="4"/>
@@ -18520,7 +18520,7 @@
       <c r="R863" s="4"/>
       <c r="S863" s="4"/>
     </row>
-    <row r="864" spans="1:19">
+    <row r="864" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A864" s="4"/>
       <c r="B864" s="5"/>
       <c r="C864" s="4"/>
@@ -18541,7 +18541,7 @@
       <c r="R864" s="4"/>
       <c r="S864" s="4"/>
     </row>
-    <row r="865" spans="1:19">
+    <row r="865" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A865" s="4"/>
       <c r="B865" s="5"/>
       <c r="C865" s="4"/>
@@ -18562,7 +18562,7 @@
       <c r="R865" s="4"/>
       <c r="S865" s="4"/>
     </row>
-    <row r="866" spans="1:19">
+    <row r="866" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A866" s="4"/>
       <c r="B866" s="5"/>
       <c r="C866" s="4"/>
@@ -18583,7 +18583,7 @@
       <c r="R866" s="4"/>
       <c r="S866" s="4"/>
     </row>
-    <row r="867" spans="1:19">
+    <row r="867" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A867" s="4"/>
       <c r="B867" s="5"/>
       <c r="C867" s="4"/>
@@ -18604,7 +18604,7 @@
       <c r="R867" s="4"/>
       <c r="S867" s="4"/>
     </row>
-    <row r="868" spans="1:19">
+    <row r="868" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A868" s="4"/>
       <c r="B868" s="5"/>
       <c r="C868" s="4"/>
@@ -18625,7 +18625,7 @@
       <c r="R868" s="4"/>
       <c r="S868" s="4"/>
     </row>
-    <row r="869" spans="1:19">
+    <row r="869" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A869" s="4"/>
       <c r="B869" s="5"/>
       <c r="C869" s="4"/>
@@ -18646,7 +18646,7 @@
       <c r="R869" s="4"/>
       <c r="S869" s="4"/>
     </row>
-    <row r="870" spans="1:19">
+    <row r="870" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A870" s="4"/>
       <c r="B870" s="5"/>
       <c r="C870" s="4"/>
@@ -18667,7 +18667,7 @@
       <c r="R870" s="4"/>
       <c r="S870" s="4"/>
     </row>
-    <row r="871" spans="1:19">
+    <row r="871" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A871" s="4"/>
       <c r="B871" s="5"/>
       <c r="C871" s="4"/>
@@ -18688,7 +18688,7 @@
       <c r="R871" s="4"/>
       <c r="S871" s="4"/>
     </row>
-    <row r="872" spans="1:19">
+    <row r="872" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A872" s="4"/>
       <c r="B872" s="5"/>
       <c r="C872" s="4"/>
@@ -18709,7 +18709,7 @@
       <c r="R872" s="4"/>
       <c r="S872" s="4"/>
     </row>
-    <row r="873" spans="1:19">
+    <row r="873" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A873" s="4"/>
       <c r="B873" s="5"/>
       <c r="C873" s="4"/>
@@ -18730,7 +18730,7 @@
       <c r="R873" s="4"/>
       <c r="S873" s="4"/>
     </row>
-    <row r="874" spans="1:19">
+    <row r="874" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A874" s="4"/>
       <c r="B874" s="5"/>
       <c r="C874" s="4"/>
@@ -18751,7 +18751,7 @@
       <c r="R874" s="4"/>
       <c r="S874" s="4"/>
     </row>
-    <row r="875" spans="1:19">
+    <row r="875" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A875" s="4"/>
       <c r="B875" s="5"/>
       <c r="C875" s="4"/>
@@ -18772,7 +18772,7 @@
       <c r="R875" s="4"/>
       <c r="S875" s="4"/>
     </row>
-    <row r="876" spans="1:19">
+    <row r="876" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A876" s="4"/>
       <c r="B876" s="5"/>
       <c r="C876" s="4"/>
@@ -18793,7 +18793,7 @@
       <c r="R876" s="4"/>
       <c r="S876" s="4"/>
     </row>
-    <row r="877" spans="1:19">
+    <row r="877" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A877" s="4"/>
       <c r="B877" s="5"/>
       <c r="C877" s="4"/>
@@ -18814,7 +18814,7 @@
       <c r="R877" s="4"/>
       <c r="S877" s="4"/>
     </row>
-    <row r="878" spans="1:19">
+    <row r="878" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A878" s="4"/>
       <c r="B878" s="5"/>
       <c r="C878" s="4"/>
@@ -18835,7 +18835,7 @@
       <c r="R878" s="4"/>
       <c r="S878" s="4"/>
     </row>
-    <row r="879" spans="1:19">
+    <row r="879" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A879" s="4"/>
       <c r="B879" s="5"/>
       <c r="C879" s="4"/>
@@ -18856,7 +18856,7 @@
       <c r="R879" s="4"/>
       <c r="S879" s="4"/>
     </row>
-    <row r="880" spans="1:19">
+    <row r="880" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A880" s="4"/>
       <c r="B880" s="5"/>
       <c r="C880" s="4"/>
@@ -18877,7 +18877,7 @@
       <c r="R880" s="4"/>
       <c r="S880" s="4"/>
     </row>
-    <row r="881" spans="1:19">
+    <row r="881" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A881" s="4"/>
       <c r="B881" s="5"/>
       <c r="C881" s="4"/>
@@ -18898,7 +18898,7 @@
       <c r="R881" s="4"/>
       <c r="S881" s="4"/>
     </row>
-    <row r="882" spans="1:19">
+    <row r="882" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A882" s="4"/>
       <c r="B882" s="5"/>
       <c r="C882" s="4"/>
@@ -18919,7 +18919,7 @@
       <c r="R882" s="4"/>
       <c r="S882" s="4"/>
     </row>
-    <row r="883" spans="1:19">
+    <row r="883" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A883" s="4"/>
       <c r="B883" s="5"/>
       <c r="C883" s="4"/>
@@ -18940,7 +18940,7 @@
       <c r="R883" s="4"/>
       <c r="S883" s="4"/>
     </row>
-    <row r="884" spans="1:19">
+    <row r="884" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A884" s="4"/>
       <c r="B884" s="5"/>
       <c r="C884" s="4"/>
@@ -18961,7 +18961,7 @@
       <c r="R884" s="4"/>
       <c r="S884" s="4"/>
     </row>
-    <row r="885" spans="1:19">
+    <row r="885" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A885" s="4"/>
       <c r="B885" s="5"/>
       <c r="C885" s="4"/>
@@ -18982,7 +18982,7 @@
       <c r="R885" s="4"/>
       <c r="S885" s="4"/>
     </row>
-    <row r="886" spans="1:19">
+    <row r="886" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A886" s="4"/>
       <c r="B886" s="5"/>
       <c r="C886" s="4"/>
@@ -19003,7 +19003,7 @@
       <c r="R886" s="4"/>
       <c r="S886" s="4"/>
     </row>
-    <row r="887" spans="1:19">
+    <row r="887" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A887" s="4"/>
       <c r="B887" s="5"/>
       <c r="C887" s="4"/>
@@ -19024,7 +19024,7 @@
       <c r="R887" s="4"/>
       <c r="S887" s="4"/>
     </row>
-    <row r="888" spans="1:19">
+    <row r="888" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A888" s="4"/>
       <c r="B888" s="5"/>
       <c r="C888" s="4"/>
@@ -19045,7 +19045,7 @@
       <c r="R888" s="4"/>
       <c r="S888" s="4"/>
     </row>
-    <row r="889" spans="1:19">
+    <row r="889" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A889" s="4"/>
       <c r="B889" s="5"/>
       <c r="C889" s="4"/>
@@ -19066,7 +19066,7 @@
       <c r="R889" s="4"/>
       <c r="S889" s="4"/>
     </row>
-    <row r="890" spans="1:19">
+    <row r="890" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A890" s="4"/>
       <c r="B890" s="5"/>
       <c r="C890" s="4"/>
@@ -19087,7 +19087,7 @@
       <c r="R890" s="4"/>
       <c r="S890" s="4"/>
     </row>
-    <row r="891" spans="1:19">
+    <row r="891" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A891" s="4"/>
       <c r="B891" s="5"/>
       <c r="C891" s="4"/>
@@ -19108,7 +19108,7 @@
       <c r="R891" s="4"/>
       <c r="S891" s="4"/>
     </row>
-    <row r="892" spans="1:19">
+    <row r="892" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A892" s="4"/>
       <c r="B892" s="5"/>
       <c r="C892" s="4"/>
@@ -19129,7 +19129,7 @@
       <c r="R892" s="4"/>
       <c r="S892" s="4"/>
     </row>
-    <row r="893" spans="1:19">
+    <row r="893" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A893" s="4"/>
       <c r="B893" s="5"/>
       <c r="C893" s="4"/>
@@ -19150,7 +19150,7 @@
       <c r="R893" s="4"/>
       <c r="S893" s="4"/>
     </row>
-    <row r="894" spans="1:19">
+    <row r="894" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A894" s="4"/>
       <c r="B894" s="5"/>
       <c r="C894" s="4"/>
@@ -19171,7 +19171,7 @@
       <c r="R894" s="4"/>
       <c r="S894" s="4"/>
     </row>
-    <row r="895" spans="1:19">
+    <row r="895" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A895" s="4"/>
       <c r="B895" s="5"/>
       <c r="C895" s="4"/>
@@ -19192,7 +19192,7 @@
       <c r="R895" s="4"/>
       <c r="S895" s="4"/>
     </row>
-    <row r="896" spans="1:19">
+    <row r="896" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A896" s="4"/>
       <c r="B896" s="5"/>
       <c r="C896" s="4"/>
@@ -19213,7 +19213,7 @@
       <c r="R896" s="4"/>
       <c r="S896" s="4"/>
     </row>
-    <row r="897" spans="1:19">
+    <row r="897" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A897" s="4"/>
       <c r="B897" s="5"/>
       <c r="C897" s="4"/>
@@ -19234,7 +19234,7 @@
       <c r="R897" s="4"/>
       <c r="S897" s="4"/>
     </row>
-    <row r="898" spans="1:19">
+    <row r="898" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A898" s="4"/>
       <c r="B898" s="5"/>
       <c r="C898" s="4"/>
@@ -19255,7 +19255,7 @@
       <c r="R898" s="4"/>
       <c r="S898" s="4"/>
     </row>
-    <row r="899" spans="1:19">
+    <row r="899" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A899" s="4"/>
       <c r="B899" s="5"/>
       <c r="C899" s="4"/>
@@ -19276,7 +19276,7 @@
       <c r="R899" s="4"/>
       <c r="S899" s="4"/>
     </row>
-    <row r="900" spans="1:19">
+    <row r="900" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A900" s="4"/>
       <c r="B900" s="5"/>
       <c r="C900" s="4"/>
@@ -19297,7 +19297,7 @@
       <c r="R900" s="4"/>
       <c r="S900" s="4"/>
     </row>
-    <row r="901" spans="1:19">
+    <row r="901" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A901" s="4"/>
       <c r="B901" s="5"/>
       <c r="C901" s="4"/>
@@ -19318,7 +19318,7 @@
       <c r="R901" s="4"/>
       <c r="S901" s="4"/>
     </row>
-    <row r="902" spans="1:19">
+    <row r="902" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A902" s="4"/>
       <c r="B902" s="5"/>
       <c r="C902" s="4"/>
@@ -19339,7 +19339,7 @@
       <c r="R902" s="4"/>
       <c r="S902" s="4"/>
     </row>
-    <row r="903" spans="1:19">
+    <row r="903" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A903" s="4"/>
       <c r="B903" s="5"/>
       <c r="C903" s="4"/>
@@ -19360,7 +19360,7 @@
       <c r="R903" s="4"/>
       <c r="S903" s="4"/>
     </row>
-    <row r="904" spans="1:19">
+    <row r="904" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A904" s="4"/>
       <c r="B904" s="5"/>
       <c r="C904" s="4"/>
@@ -19381,7 +19381,7 @@
       <c r="R904" s="4"/>
       <c r="S904" s="4"/>
     </row>
-    <row r="905" spans="1:19">
+    <row r="905" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A905" s="4"/>
       <c r="B905" s="5"/>
       <c r="C905" s="4"/>
@@ -19402,7 +19402,7 @@
       <c r="R905" s="4"/>
       <c r="S905" s="4"/>
     </row>
-    <row r="906" spans="1:19">
+    <row r="906" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A906" s="4"/>
       <c r="B906" s="5"/>
       <c r="C906" s="4"/>
@@ -19423,7 +19423,7 @@
       <c r="R906" s="4"/>
       <c r="S906" s="4"/>
     </row>
-    <row r="907" spans="1:19">
+    <row r="907" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A907" s="4"/>
       <c r="B907" s="5"/>
       <c r="C907" s="4"/>
@@ -19444,7 +19444,7 @@
       <c r="R907" s="4"/>
       <c r="S907" s="4"/>
     </row>
-    <row r="908" spans="1:19">
+    <row r="908" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A908" s="4"/>
       <c r="B908" s="5"/>
       <c r="C908" s="4"/>
@@ -19465,7 +19465,7 @@
       <c r="R908" s="4"/>
       <c r="S908" s="4"/>
     </row>
-    <row r="909" spans="1:19">
+    <row r="909" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A909" s="4"/>
       <c r="B909" s="5"/>
       <c r="C909" s="4"/>
@@ -19486,7 +19486,7 @@
       <c r="R909" s="4"/>
       <c r="S909" s="4"/>
     </row>
-    <row r="910" spans="1:19">
+    <row r="910" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A910" s="4"/>
       <c r="B910" s="5"/>
       <c r="C910" s="4"/>
@@ -19507,7 +19507,7 @@
       <c r="R910" s="4"/>
       <c r="S910" s="4"/>
     </row>
-    <row r="911" spans="1:19">
+    <row r="911" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A911" s="4"/>
       <c r="B911" s="5"/>
       <c r="C911" s="4"/>
@@ -19528,7 +19528,7 @@
       <c r="R911" s="4"/>
       <c r="S911" s="4"/>
     </row>
-    <row r="912" spans="1:19">
+    <row r="912" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A912" s="4"/>
       <c r="B912" s="5"/>
       <c r="C912" s="4"/>
@@ -19549,7 +19549,7 @@
       <c r="R912" s="4"/>
       <c r="S912" s="4"/>
     </row>
-    <row r="913" spans="1:19">
+    <row r="913" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A913" s="4"/>
       <c r="B913" s="5"/>
       <c r="C913" s="4"/>
@@ -19570,7 +19570,7 @@
       <c r="R913" s="4"/>
       <c r="S913" s="4"/>
     </row>
-    <row r="914" spans="1:19">
+    <row r="914" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A914" s="4"/>
       <c r="B914" s="5"/>
       <c r="C914" s="4"/>
@@ -19591,7 +19591,7 @@
       <c r="R914" s="4"/>
       <c r="S914" s="4"/>
     </row>
-    <row r="915" spans="1:19">
+    <row r="915" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A915" s="4"/>
       <c r="B915" s="5"/>
       <c r="C915" s="4"/>
@@ -19612,7 +19612,7 @@
       <c r="R915" s="4"/>
       <c r="S915" s="4"/>
     </row>
-    <row r="916" spans="1:19">
+    <row r="916" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A916" s="4"/>
       <c r="B916" s="5"/>
       <c r="C916" s="4"/>
@@ -19633,7 +19633,7 @@
       <c r="R916" s="4"/>
       <c r="S916" s="4"/>
     </row>
-    <row r="917" spans="1:19">
+    <row r="917" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A917" s="4"/>
       <c r="B917" s="5"/>
       <c r="C917" s="4"/>
@@ -19654,7 +19654,7 @@
       <c r="R917" s="4"/>
       <c r="S917" s="4"/>
     </row>
-    <row r="918" spans="1:19">
+    <row r="918" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A918" s="4"/>
       <c r="B918" s="5"/>
       <c r="C918" s="4"/>
@@ -19675,7 +19675,7 @@
       <c r="R918" s="4"/>
       <c r="S918" s="4"/>
     </row>
-    <row r="919" spans="1:19">
+    <row r="919" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A919" s="4"/>
       <c r="B919" s="5"/>
       <c r="C919" s="4"/>
@@ -19696,7 +19696,7 @@
       <c r="R919" s="4"/>
       <c r="S919" s="4"/>
     </row>
-    <row r="920" spans="1:19">
+    <row r="920" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A920" s="4"/>
       <c r="B920" s="5"/>
       <c r="C920" s="4"/>
@@ -19717,7 +19717,7 @@
       <c r="R920" s="4"/>
       <c r="S920" s="4"/>
     </row>
-    <row r="921" spans="1:19">
+    <row r="921" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A921" s="4"/>
       <c r="B921" s="5"/>
       <c r="C921" s="4"/>
@@ -19738,7 +19738,7 @@
       <c r="R921" s="4"/>
       <c r="S921" s="4"/>
     </row>
-    <row r="922" spans="1:19">
+    <row r="922" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A922" s="4"/>
       <c r="B922" s="5"/>
       <c r="C922" s="4"/>
@@ -19759,7 +19759,7 @@
       <c r="R922" s="4"/>
       <c r="S922" s="4"/>
     </row>
-    <row r="923" spans="1:19">
+    <row r="923" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A923" s="4"/>
       <c r="B923" s="5"/>
       <c r="C923" s="4"/>
@@ -19780,7 +19780,7 @@
       <c r="R923" s="4"/>
       <c r="S923" s="4"/>
     </row>
-    <row r="924" spans="1:19">
+    <row r="924" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A924" s="4"/>
       <c r="B924" s="5"/>
       <c r="C924" s="4"/>
@@ -19801,7 +19801,7 @@
       <c r="R924" s="4"/>
       <c r="S924" s="4"/>
     </row>
-    <row r="925" spans="1:19">
+    <row r="925" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A925" s="4"/>
       <c r="B925" s="5"/>
       <c r="C925" s="4"/>
@@ -19822,7 +19822,7 @@
       <c r="R925" s="4"/>
       <c r="S925" s="4"/>
     </row>
-    <row r="926" spans="1:19">
+    <row r="926" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A926" s="4"/>
       <c r="B926" s="5"/>
       <c r="C926" s="4"/>
@@ -19843,7 +19843,7 @@
       <c r="R926" s="4"/>
       <c r="S926" s="4"/>
     </row>
-    <row r="927" spans="1:19">
+    <row r="927" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A927" s="4"/>
       <c r="B927" s="5"/>
       <c r="C927" s="4"/>
@@ -19864,7 +19864,7 @@
       <c r="R927" s="4"/>
       <c r="S927" s="4"/>
     </row>
-    <row r="928" spans="1:19">
+    <row r="928" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A928" s="4"/>
       <c r="B928" s="5"/>
       <c r="C928" s="4"/>
@@ -19885,7 +19885,7 @@
       <c r="R928" s="4"/>
       <c r="S928" s="4"/>
     </row>
-    <row r="929" spans="1:19">
+    <row r="929" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A929" s="4"/>
       <c r="B929" s="5"/>
       <c r="C929" s="4"/>
@@ -19906,7 +19906,7 @@
       <c r="R929" s="4"/>
       <c r="S929" s="4"/>
     </row>
-    <row r="930" spans="1:19">
+    <row r="930" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A930" s="4"/>
       <c r="B930" s="5"/>
       <c r="C930" s="4"/>
@@ -19927,7 +19927,7 @@
       <c r="R930" s="4"/>
       <c r="S930" s="4"/>
     </row>
-    <row r="931" spans="1:19">
+    <row r="931" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A931" s="4"/>
       <c r="B931" s="5"/>
       <c r="C931" s="4"/>
@@ -19948,7 +19948,7 @@
       <c r="R931" s="4"/>
       <c r="S931" s="4"/>
     </row>
-    <row r="932" spans="1:19">
+    <row r="932" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A932" s="4"/>
       <c r="B932" s="5"/>
       <c r="C932" s="4"/>
@@ -19969,7 +19969,7 @@
       <c r="R932" s="4"/>
       <c r="S932" s="4"/>
     </row>
-    <row r="933" spans="1:19">
+    <row r="933" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A933" s="4"/>
       <c r="B933" s="5"/>
       <c r="C933" s="4"/>
@@ -19990,7 +19990,7 @@
       <c r="R933" s="4"/>
       <c r="S933" s="4"/>
     </row>
-    <row r="934" spans="1:19">
+    <row r="934" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A934" s="4"/>
       <c r="B934" s="5"/>
       <c r="C934" s="4"/>
@@ -20011,7 +20011,7 @@
       <c r="R934" s="4"/>
       <c r="S934" s="4"/>
     </row>
-    <row r="935" spans="1:19">
+    <row r="935" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A935" s="4"/>
       <c r="B935" s="5"/>
       <c r="C935" s="4"/>
@@ -20032,7 +20032,7 @@
       <c r="R935" s="4"/>
       <c r="S935" s="4"/>
     </row>
-    <row r="936" spans="1:19">
+    <row r="936" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A936" s="4"/>
       <c r="B936" s="5"/>
       <c r="C936" s="4"/>
@@ -20053,7 +20053,7 @@
       <c r="R936" s="4"/>
       <c r="S936" s="4"/>
     </row>
-    <row r="937" spans="1:19">
+    <row r="937" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A937" s="4"/>
       <c r="B937" s="5"/>
       <c r="C937" s="4"/>
@@ -20074,7 +20074,7 @@
       <c r="R937" s="4"/>
       <c r="S937" s="4"/>
     </row>
-    <row r="938" spans="1:19">
+    <row r="938" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A938" s="4"/>
       <c r="B938" s="5"/>
       <c r="C938" s="4"/>
@@ -20095,7 +20095,7 @@
       <c r="R938" s="4"/>
       <c r="S938" s="4"/>
     </row>
-    <row r="939" spans="1:19">
+    <row r="939" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A939" s="4"/>
       <c r="B939" s="5"/>
       <c r="C939" s="4"/>
@@ -20116,7 +20116,7 @@
       <c r="R939" s="4"/>
       <c r="S939" s="4"/>
     </row>
-    <row r="940" spans="1:19">
+    <row r="940" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A940" s="4"/>
       <c r="B940" s="5"/>
       <c r="C940" s="4"/>
@@ -20137,7 +20137,7 @@
       <c r="R940" s="4"/>
       <c r="S940" s="4"/>
     </row>
-    <row r="941" spans="1:19">
+    <row r="941" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A941" s="4"/>
       <c r="B941" s="5"/>
       <c r="C941" s="4"/>
@@ -20158,7 +20158,7 @@
       <c r="R941" s="4"/>
       <c r="S941" s="4"/>
     </row>
-    <row r="942" spans="1:19">
+    <row r="942" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A942" s="4"/>
       <c r="B942" s="5"/>
       <c r="C942" s="4"/>
@@ -20179,7 +20179,7 @@
       <c r="R942" s="4"/>
       <c r="S942" s="4"/>
     </row>
-    <row r="943" spans="1:19">
+    <row r="943" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A943" s="4"/>
       <c r="B943" s="5"/>
       <c r="C943" s="4"/>
@@ -20200,7 +20200,7 @@
       <c r="R943" s="4"/>
       <c r="S943" s="4"/>
     </row>
-    <row r="944" spans="1:19">
+    <row r="944" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A944" s="4"/>
       <c r="B944" s="5"/>
       <c r="C944" s="4"/>
@@ -20221,7 +20221,7 @@
       <c r="R944" s="4"/>
       <c r="S944" s="4"/>
     </row>
-    <row r="945" spans="1:19">
+    <row r="945" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A945" s="4"/>
       <c r="B945" s="5"/>
       <c r="C945" s="4"/>
@@ -20242,7 +20242,7 @@
       <c r="R945" s="4"/>
       <c r="S945" s="4"/>
     </row>
-    <row r="946" spans="1:19">
+    <row r="946" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A946" s="4"/>
       <c r="B946" s="5"/>
       <c r="C946" s="4"/>
@@ -20263,7 +20263,7 @@
       <c r="R946" s="4"/>
       <c r="S946" s="4"/>
     </row>
-    <row r="947" spans="1:19">
+    <row r="947" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A947" s="4"/>
       <c r="B947" s="5"/>
       <c r="C947" s="4"/>
@@ -20284,7 +20284,7 @@
       <c r="R947" s="4"/>
       <c r="S947" s="4"/>
     </row>
-    <row r="948" spans="1:19">
+    <row r="948" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A948" s="4"/>
       <c r="B948" s="5"/>
       <c r="C948" s="4"/>
@@ -20305,7 +20305,7 @@
       <c r="R948" s="4"/>
       <c r="S948" s="4"/>
     </row>
-    <row r="949" spans="1:19">
+    <row r="949" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A949" s="4"/>
       <c r="B949" s="5"/>
       <c r="C949" s="4"/>
@@ -20326,7 +20326,7 @@
       <c r="R949" s="4"/>
       <c r="S949" s="4"/>
     </row>
-    <row r="950" spans="1:19">
+    <row r="950" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A950" s="4"/>
       <c r="B950" s="5"/>
       <c r="C950" s="4"/>
@@ -20347,7 +20347,7 @@
       <c r="R950" s="4"/>
       <c r="S950" s="4"/>
     </row>
-    <row r="951" spans="1:19">
+    <row r="951" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A951" s="4"/>
       <c r="B951" s="5"/>
       <c r="C951" s="4"/>
@@ -20368,7 +20368,7 @@
       <c r="R951" s="4"/>
       <c r="S951" s="4"/>
     </row>
-    <row r="952" spans="1:19">
+    <row r="952" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A952" s="4"/>
       <c r="B952" s="5"/>
       <c r="C952" s="4"/>
@@ -20389,7 +20389,7 @@
       <c r="R952" s="4"/>
       <c r="S952" s="4"/>
     </row>
-    <row r="953" spans="1:19">
+    <row r="953" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A953" s="4"/>
       <c r="B953" s="5"/>
       <c r="C953" s="4"/>
@@ -20410,7 +20410,7 @@
       <c r="R953" s="4"/>
       <c r="S953" s="4"/>
     </row>
-    <row r="954" spans="1:19">
+    <row r="954" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A954" s="4"/>
       <c r="B954" s="5"/>
       <c r="C954" s="4"/>
@@ -20431,7 +20431,7 @@
       <c r="R954" s="4"/>
       <c r="S954" s="4"/>
     </row>
-    <row r="955" spans="1:19">
+    <row r="955" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A955" s="4"/>
       <c r="B955" s="5"/>
       <c r="C955" s="4"/>
@@ -20452,7 +20452,7 @@
       <c r="R955" s="4"/>
       <c r="S955" s="4"/>
     </row>
-    <row r="956" spans="1:19">
+    <row r="956" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A956" s="4"/>
       <c r="B956" s="5"/>
       <c r="C956" s="4"/>
@@ -20473,7 +20473,7 @@
       <c r="R956" s="4"/>
       <c r="S956" s="4"/>
     </row>
-    <row r="957" spans="1:19">
+    <row r="957" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A957" s="4"/>
       <c r="B957" s="5"/>
       <c r="C957" s="4"/>
@@ -20494,7 +20494,7 @@
       <c r="R957" s="4"/>
       <c r="S957" s="4"/>
     </row>
-    <row r="958" spans="1:19">
+    <row r="958" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A958" s="4"/>
       <c r="B958" s="5"/>
       <c r="C958" s="4"/>
@@ -20515,7 +20515,7 @@
       <c r="R958" s="4"/>
       <c r="S958" s="4"/>
     </row>
-    <row r="959" spans="1:19">
+    <row r="959" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A959" s="4"/>
       <c r="B959" s="5"/>
       <c r="C959" s="4"/>
@@ -20536,7 +20536,7 @@
       <c r="R959" s="4"/>
       <c r="S959" s="4"/>
     </row>
-    <row r="960" spans="1:19">
+    <row r="960" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A960" s="4"/>
       <c r="B960" s="5"/>
       <c r="C960" s="4"/>
@@ -20557,7 +20557,7 @@
       <c r="R960" s="4"/>
       <c r="S960" s="4"/>
     </row>
-    <row r="961" spans="1:19">
+    <row r="961" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A961" s="4"/>
       <c r="B961" s="5"/>
       <c r="C961" s="4"/>
@@ -20578,7 +20578,7 @@
       <c r="R961" s="4"/>
       <c r="S961" s="4"/>
     </row>
-    <row r="962" spans="1:19">
+    <row r="962" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A962" s="4"/>
       <c r="B962" s="5"/>
       <c r="C962" s="4"/>
@@ -20599,7 +20599,7 @@
       <c r="R962" s="4"/>
       <c r="S962" s="4"/>
     </row>
-    <row r="963" spans="1:19">
+    <row r="963" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A963" s="4"/>
       <c r="B963" s="5"/>
       <c r="C963" s="4"/>
@@ -20620,7 +20620,7 @@
       <c r="R963" s="4"/>
       <c r="S963" s="4"/>
     </row>
-    <row r="964" spans="1:19">
+    <row r="964" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A964" s="4"/>
       <c r="B964" s="5"/>
       <c r="C964" s="4"/>
@@ -20641,7 +20641,7 @@
       <c r="R964" s="4"/>
       <c r="S964" s="4"/>
     </row>
-    <row r="965" spans="1:19">
+    <row r="965" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A965" s="4"/>
       <c r="B965" s="5"/>
       <c r="C965" s="4"/>
@@ -20662,7 +20662,7 @@
       <c r="R965" s="4"/>
       <c r="S965" s="4"/>
     </row>
-    <row r="966" spans="1:19">
+    <row r="966" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A966" s="4"/>
       <c r="B966" s="5"/>
       <c r="C966" s="4"/>
@@ -20683,7 +20683,7 @@
       <c r="R966" s="4"/>
       <c r="S966" s="4"/>
     </row>
-    <row r="967" spans="1:19">
+    <row r="967" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A967" s="4"/>
       <c r="B967" s="5"/>
       <c r="C967" s="4"/>
@@ -20704,7 +20704,7 @@
       <c r="R967" s="4"/>
       <c r="S967" s="4"/>
     </row>
-    <row r="968" spans="1:19">
+    <row r="968" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A968" s="4"/>
       <c r="B968" s="5"/>
       <c r="C968" s="4"/>
@@ -20725,7 +20725,7 @@
       <c r="R968" s="4"/>
       <c r="S968" s="4"/>
     </row>
-    <row r="969" spans="1:19">
+    <row r="969" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A969" s="4"/>
       <c r="B969" s="5"/>
       <c r="C969" s="4"/>
@@ -20746,7 +20746,7 @@
       <c r="R969" s="4"/>
       <c r="S969" s="4"/>
     </row>
-    <row r="970" spans="1:19">
+    <row r="970" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A970" s="4"/>
       <c r="B970" s="5"/>
       <c r="C970" s="4"/>
@@ -20767,7 +20767,7 @@
       <c r="R970" s="4"/>
       <c r="S970" s="4"/>
     </row>
-    <row r="971" spans="1:19">
+    <row r="971" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A971" s="4"/>
       <c r="B971" s="5"/>
       <c r="C971" s="4"/>
@@ -20788,7 +20788,7 @@
       <c r="R971" s="4"/>
       <c r="S971" s="4"/>
     </row>
-    <row r="972" spans="1:19">
+    <row r="972" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A972" s="4"/>
       <c r="B972" s="5"/>
       <c r="C972" s="4"/>
@@ -20809,7 +20809,7 @@
       <c r="R972" s="4"/>
       <c r="S972" s="4"/>
     </row>
-    <row r="973" spans="1:19">
+    <row r="973" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A973" s="4"/>
       <c r="B973" s="5"/>
       <c r="C973" s="4"/>
@@ -20830,7 +20830,7 @@
       <c r="R973" s="4"/>
       <c r="S973" s="4"/>
     </row>
-    <row r="974" spans="1:19">
+    <row r="974" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A974" s="4"/>
       <c r="B974" s="5"/>
       <c r="C974" s="4"/>
@@ -20851,7 +20851,7 @@
       <c r="R974" s="4"/>
       <c r="S974" s="4"/>
     </row>
-    <row r="975" spans="1:19">
+    <row r="975" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A975" s="4"/>
       <c r="B975" s="5"/>
       <c r="C975" s="4"/>
@@ -20872,7 +20872,7 @@
       <c r="R975" s="4"/>
       <c r="S975" s="4"/>
     </row>
-    <row r="976" spans="1:19">
+    <row r="976" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A976" s="4"/>
       <c r="B976" s="5"/>
       <c r="C976" s="4"/>
@@ -20893,7 +20893,7 @@
       <c r="R976" s="4"/>
       <c r="S976" s="4"/>
     </row>
-    <row r="977" spans="1:19">
+    <row r="977" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A977" s="4"/>
       <c r="B977" s="5"/>
       <c r="C977" s="4"/>
@@ -20914,7 +20914,7 @@
       <c r="R977" s="4"/>
       <c r="S977" s="4"/>
     </row>
-    <row r="978" spans="1:19">
+    <row r="978" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A978" s="4"/>
       <c r="B978" s="5"/>
       <c r="C978" s="4"/>
@@ -20935,7 +20935,7 @@
       <c r="R978" s="4"/>
       <c r="S978" s="4"/>
     </row>
-    <row r="979" spans="1:19">
+    <row r="979" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A979" s="4"/>
       <c r="B979" s="5"/>
       <c r="C979" s="4"/>
@@ -20956,7 +20956,7 @@
       <c r="R979" s="4"/>
       <c r="S979" s="4"/>
     </row>
-    <row r="980" spans="1:19">
+    <row r="980" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A980" s="4"/>
       <c r="B980" s="5"/>
       <c r="C980" s="4"/>
@@ -20977,7 +20977,7 @@
       <c r="R980" s="4"/>
       <c r="S980" s="4"/>
     </row>
-    <row r="981" spans="1:19">
+    <row r="981" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A981" s="4"/>
       <c r="B981" s="5"/>
       <c r="C981" s="4"/>
@@ -20998,7 +20998,7 @@
       <c r="R981" s="4"/>
       <c r="S981" s="4"/>
     </row>
-    <row r="982" spans="1:19">
+    <row r="982" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A982" s="4"/>
       <c r="B982" s="5"/>
       <c r="C982" s="4"/>
@@ -21019,7 +21019,7 @@
       <c r="R982" s="4"/>
       <c r="S982" s="4"/>
     </row>
-    <row r="983" spans="1:19">
+    <row r="983" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A983" s="4"/>
       <c r="B983" s="5"/>
       <c r="C983" s="4"/>
@@ -21040,7 +21040,7 @@
       <c r="R983" s="4"/>
       <c r="S983" s="4"/>
     </row>
-    <row r="984" spans="1:19">
+    <row r="984" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A984" s="4"/>
       <c r="B984" s="5"/>
       <c r="C984" s="4"/>
@@ -21061,7 +21061,7 @@
       <c r="R984" s="4"/>
       <c r="S984" s="4"/>
     </row>
-    <row r="985" spans="1:19">
+    <row r="985" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A985" s="4"/>
       <c r="B985" s="5"/>
       <c r="C985" s="4"/>
@@ -21082,7 +21082,7 @@
       <c r="R985" s="4"/>
       <c r="S985" s="4"/>
     </row>
-    <row r="986" spans="1:19">
+    <row r="986" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A986" s="4"/>
       <c r="B986" s="5"/>
       <c r="C986" s="4"/>
@@ -21103,7 +21103,7 @@
       <c r="R986" s="4"/>
       <c r="S986" s="4"/>
     </row>
-    <row r="987" spans="1:19">
+    <row r="987" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A987" s="4"/>
       <c r="B987" s="5"/>
       <c r="C987" s="4"/>
@@ -21124,7 +21124,7 @@
       <c r="R987" s="4"/>
       <c r="S987" s="4"/>
     </row>
-    <row r="988" spans="1:19">
+    <row r="988" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A988" s="4"/>
       <c r="B988" s="5"/>
       <c r="C988" s="4"/>
@@ -21145,7 +21145,7 @@
       <c r="R988" s="4"/>
       <c r="S988" s="4"/>
     </row>
-    <row r="989" spans="1:19">
+    <row r="989" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A989" s="4"/>
       <c r="B989" s="5"/>
       <c r="C989" s="4"/>
@@ -21166,7 +21166,7 @@
       <c r="R989" s="4"/>
       <c r="S989" s="4"/>
     </row>
-    <row r="990" spans="1:19">
+    <row r="990" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A990" s="4"/>
       <c r="B990" s="5"/>
       <c r="C990" s="4"/>
@@ -21187,7 +21187,7 @@
       <c r="R990" s="4"/>
       <c r="S990" s="4"/>
     </row>
-    <row r="991" spans="1:19">
+    <row r="991" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A991" s="4"/>
       <c r="B991" s="5"/>
       <c r="C991" s="4"/>
@@ -21208,7 +21208,7 @@
       <c r="R991" s="4"/>
       <c r="S991" s="4"/>
     </row>
-    <row r="992" spans="1:19">
+    <row r="992" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A992" s="4"/>
       <c r="B992" s="5"/>
       <c r="C992" s="4"/>
@@ -21229,7 +21229,7 @@
       <c r="R992" s="4"/>
       <c r="S992" s="4"/>
     </row>
-    <row r="993" spans="1:19">
+    <row r="993" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A993" s="4"/>
       <c r="B993" s="5"/>
       <c r="C993" s="4"/>
@@ -21250,7 +21250,7 @@
       <c r="R993" s="4"/>
       <c r="S993" s="4"/>
     </row>
-    <row r="994" spans="1:19">
+    <row r="994" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A994" s="4"/>
       <c r="B994" s="5"/>
       <c r="C994" s="4"/>
@@ -21271,7 +21271,7 @@
       <c r="R994" s="4"/>
       <c r="S994" s="4"/>
     </row>
-    <row r="995" spans="1:19">
+    <row r="995" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A995" s="4"/>
       <c r="B995" s="5"/>
       <c r="C995" s="4"/>
@@ -21292,7 +21292,7 @@
       <c r="R995" s="4"/>
       <c r="S995" s="4"/>
     </row>
-    <row r="996" spans="1:19">
+    <row r="996" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A996" s="4"/>
       <c r="B996" s="5"/>
       <c r="C996" s="4"/>
@@ -21313,7 +21313,7 @@
       <c r="R996" s="4"/>
       <c r="S996" s="4"/>
     </row>
-    <row r="997" spans="1:19">
+    <row r="997" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A997" s="4"/>
       <c r="B997" s="5"/>
       <c r="C997" s="4"/>
@@ -21334,7 +21334,7 @@
       <c r="R997" s="4"/>
       <c r="S997" s="4"/>
     </row>
-    <row r="998" spans="1:19">
+    <row r="998" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A998" s="4"/>
       <c r="B998" s="5"/>
       <c r="C998" s="4"/>
@@ -21355,7 +21355,7 @@
       <c r="R998" s="4"/>
       <c r="S998" s="4"/>
     </row>
-    <row r="999" spans="1:19">
+    <row r="999" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A999" s="4"/>
       <c r="B999" s="5"/>
       <c r="C999" s="4"/>
@@ -21376,7 +21376,7 @@
       <c r="R999" s="4"/>
       <c r="S999" s="4"/>
     </row>
-    <row r="1000" spans="1:19">
+    <row r="1000" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1000" s="4"/>
       <c r="B1000" s="5"/>
       <c r="C1000" s="4"/>
@@ -21397,7 +21397,7 @@
       <c r="R1000" s="4"/>
       <c r="S1000" s="4"/>
     </row>
-    <row r="1001" spans="1:19">
+    <row r="1001" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1001" s="4"/>
       <c r="B1001" s="5"/>
       <c r="C1001" s="4"/>
@@ -21418,7 +21418,7 @@
       <c r="R1001" s="4"/>
       <c r="S1001" s="4"/>
     </row>
-    <row r="1002" spans="1:19">
+    <row r="1002" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1002" s="4"/>
       <c r="B1002" s="5"/>
       <c r="C1002" s="4"/>
@@ -21439,7 +21439,7 @@
       <c r="R1002" s="4"/>
       <c r="S1002" s="4"/>
     </row>
-    <row r="1003" spans="1:19">
+    <row r="1003" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1003" s="4"/>
       <c r="B1003" s="5"/>
       <c r="C1003" s="4"/>
@@ -21460,7 +21460,7 @@
       <c r="R1003" s="4"/>
       <c r="S1003" s="4"/>
     </row>
-    <row r="1004" spans="1:19">
+    <row r="1004" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1004" s="4"/>
       <c r="B1004" s="5"/>
       <c r="C1004" s="4"/>
@@ -21481,7 +21481,7 @@
       <c r="R1004" s="4"/>
       <c r="S1004" s="4"/>
     </row>
-    <row r="1005" spans="1:19">
+    <row r="1005" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1005" s="4"/>
       <c r="B1005" s="5"/>
       <c r="C1005" s="4"/>
@@ -21502,7 +21502,7 @@
       <c r="R1005" s="4"/>
       <c r="S1005" s="4"/>
     </row>
-    <row r="1006" spans="1:19">
+    <row r="1006" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1006" s="4"/>
       <c r="B1006" s="5"/>
       <c r="C1006" s="4"/>
@@ -21523,7 +21523,7 @@
       <c r="R1006" s="4"/>
       <c r="S1006" s="4"/>
     </row>
-    <row r="1007" spans="1:19">
+    <row r="1007" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1007" s="4"/>
       <c r="B1007" s="5"/>
       <c r="C1007" s="4"/>
@@ -21544,7 +21544,7 @@
       <c r="R1007" s="4"/>
       <c r="S1007" s="4"/>
     </row>
-    <row r="1008" spans="1:19">
+    <row r="1008" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1008" s="4"/>
       <c r="B1008" s="5"/>
       <c r="C1008" s="4"/>
@@ -21565,7 +21565,7 @@
       <c r="R1008" s="4"/>
       <c r="S1008" s="4"/>
     </row>
-    <row r="1009" spans="1:19">
+    <row r="1009" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1009" s="4"/>
       <c r="B1009" s="5"/>
       <c r="C1009" s="4"/>
@@ -21586,7 +21586,7 @@
       <c r="R1009" s="4"/>
       <c r="S1009" s="4"/>
     </row>
-    <row r="1010" spans="1:19">
+    <row r="1010" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1010" s="4"/>
       <c r="B1010" s="5"/>
       <c r="C1010" s="4"/>
@@ -21607,7 +21607,7 @@
       <c r="R1010" s="4"/>
       <c r="S1010" s="4"/>
     </row>
-    <row r="1011" spans="1:19">
+    <row r="1011" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1011" s="4"/>
       <c r="B1011" s="5"/>
       <c r="C1011" s="4"/>
@@ -21628,7 +21628,7 @@
       <c r="R1011" s="4"/>
       <c r="S1011" s="4"/>
     </row>
-    <row r="1012" spans="1:19">
+    <row r="1012" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1012" s="4"/>
       <c r="B1012" s="5"/>
       <c r="C1012" s="4"/>
@@ -21649,7 +21649,7 @@
       <c r="R1012" s="4"/>
       <c r="S1012" s="4"/>
     </row>
-    <row r="1013" spans="1:19">
+    <row r="1013" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1013" s="4"/>
       <c r="B1013" s="5"/>
       <c r="C1013" s="4"/>
@@ -21670,7 +21670,7 @@
       <c r="R1013" s="4"/>
       <c r="S1013" s="4"/>
     </row>
-    <row r="1014" spans="1:19">
+    <row r="1014" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1014" s="4"/>
       <c r="B1014" s="5"/>
       <c r="C1014" s="4"/>
@@ -21691,7 +21691,7 @@
       <c r="R1014" s="4"/>
       <c r="S1014" s="4"/>
     </row>
-    <row r="1015" spans="1:19">
+    <row r="1015" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1015" s="4"/>
       <c r="B1015" s="5"/>
       <c r="C1015" s="4"/>
@@ -21712,7 +21712,7 @@
       <c r="R1015" s="4"/>
       <c r="S1015" s="4"/>
     </row>
-    <row r="1016" spans="1:19">
+    <row r="1016" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1016" s="4"/>
       <c r="B1016" s="5"/>
       <c r="C1016" s="4"/>
@@ -21733,7 +21733,7 @@
       <c r="R1016" s="4"/>
       <c r="S1016" s="4"/>
     </row>
-    <row r="1017" spans="1:19">
+    <row r="1017" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1017" s="4"/>
       <c r="B1017" s="5"/>
       <c r="C1017" s="4"/>
@@ -21754,7 +21754,7 @@
       <c r="R1017" s="4"/>
       <c r="S1017" s="4"/>
     </row>
-    <row r="1018" spans="1:19">
+    <row r="1018" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1018" s="4"/>
       <c r="B1018" s="5"/>
       <c r="C1018" s="4"/>
@@ -21775,7 +21775,7 @@
       <c r="R1018" s="4"/>
       <c r="S1018" s="4"/>
     </row>
-    <row r="1019" spans="1:19">
+    <row r="1019" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1019" s="4"/>
       <c r="B1019" s="5"/>
       <c r="C1019" s="4"/>
@@ -21796,7 +21796,7 @@
       <c r="R1019" s="4"/>
       <c r="S1019" s="4"/>
     </row>
-    <row r="1020" spans="1:19">
+    <row r="1020" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1020" s="4"/>
       <c r="B1020" s="5"/>
       <c r="C1020" s="4"/>
@@ -21817,7 +21817,7 @@
       <c r="R1020" s="4"/>
       <c r="S1020" s="4"/>
     </row>
-    <row r="1021" spans="1:19">
+    <row r="1021" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1021" s="4"/>
       <c r="B1021" s="5"/>
       <c r="C1021" s="4"/>
@@ -21838,7 +21838,7 @@
       <c r="R1021" s="4"/>
       <c r="S1021" s="4"/>
     </row>
-    <row r="1022" spans="1:19">
+    <row r="1022" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1022" s="4"/>
       <c r="B1022" s="5"/>
       <c r="C1022" s="4"/>
@@ -21859,7 +21859,7 @@
       <c r="R1022" s="4"/>
       <c r="S1022" s="4"/>
     </row>
-    <row r="1023" spans="1:19">
+    <row r="1023" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1023" s="4"/>
       <c r="B1023" s="5"/>
       <c r="C1023" s="4"/>
@@ -21880,7 +21880,7 @@
       <c r="R1023" s="4"/>
       <c r="S1023" s="4"/>
     </row>
-    <row r="1024" spans="1:19">
+    <row r="1024" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1024" s="4"/>
       <c r="B1024" s="5"/>
       <c r="C1024" s="4"/>
@@ -21901,7 +21901,7 @@
       <c r="R1024" s="4"/>
       <c r="S1024" s="4"/>
     </row>
-    <row r="1025" spans="1:19">
+    <row r="1025" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1025" s="4"/>
       <c r="B1025" s="5"/>
       <c r="C1025" s="4"/>
@@ -21922,7 +21922,7 @@
       <c r="R1025" s="4"/>
       <c r="S1025" s="4"/>
     </row>
-    <row r="1026" spans="1:19">
+    <row r="1026" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1026" s="4"/>
       <c r="B1026" s="5"/>
       <c r="C1026" s="4"/>
@@ -21943,7 +21943,7 @@
       <c r="R1026" s="4"/>
       <c r="S1026" s="4"/>
     </row>
-    <row r="1027" spans="1:19">
+    <row r="1027" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1027" s="4"/>
       <c r="B1027" s="5"/>
       <c r="C1027" s="4"/>
@@ -21964,7 +21964,7 @@
       <c r="R1027" s="4"/>
       <c r="S1027" s="4"/>
     </row>
-    <row r="1028" spans="1:19">
+    <row r="1028" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1028" s="4"/>
       <c r="B1028" s="5"/>
       <c r="C1028" s="4"/>
@@ -21985,7 +21985,7 @@
       <c r="R1028" s="4"/>
       <c r="S1028" s="4"/>
     </row>
-    <row r="1029" spans="1:19">
+    <row r="1029" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1029" s="4"/>
       <c r="B1029" s="5"/>
       <c r="C1029" s="4"/>
@@ -22006,7 +22006,7 @@
       <c r="R1029" s="4"/>
       <c r="S1029" s="4"/>
     </row>
-    <row r="1030" spans="1:19">
+    <row r="1030" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1030" s="4"/>
       <c r="B1030" s="5"/>
       <c r="C1030" s="4"/>
@@ -22027,7 +22027,7 @@
       <c r="R1030" s="4"/>
       <c r="S1030" s="4"/>
     </row>
-    <row r="1031" spans="1:19">
+    <row r="1031" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1031" s="4"/>
       <c r="B1031" s="5"/>
       <c r="C1031" s="4"/>
@@ -22048,7 +22048,7 @@
       <c r="R1031" s="4"/>
       <c r="S1031" s="4"/>
     </row>
-    <row r="1032" spans="1:19">
+    <row r="1032" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1032" s="4"/>
       <c r="B1032" s="5"/>
       <c r="C1032" s="4"/>
@@ -22069,7 +22069,7 @@
       <c r="R1032" s="4"/>
       <c r="S1032" s="4"/>
     </row>
-    <row r="1033" spans="1:19">
+    <row r="1033" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1033" s="4"/>
       <c r="B1033" s="5"/>
       <c r="C1033" s="4"/>
@@ -22090,7 +22090,7 @@
       <c r="R1033" s="4"/>
       <c r="S1033" s="4"/>
     </row>
-    <row r="1034" spans="1:19">
+    <row r="1034" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1034" s="4"/>
       <c r="B1034" s="5"/>
       <c r="C1034" s="4"/>
@@ -22111,7 +22111,7 @@
       <c r="R1034" s="4"/>
       <c r="S1034" s="4"/>
     </row>
-    <row r="1035" spans="1:19">
+    <row r="1035" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1035" s="4"/>
       <c r="B1035" s="5"/>
       <c r="C1035" s="4"/>
@@ -22132,7 +22132,7 @@
       <c r="R1035" s="4"/>
       <c r="S1035" s="4"/>
     </row>
-    <row r="1036" spans="1:19">
+    <row r="1036" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1036" s="4"/>
       <c r="B1036" s="5"/>
       <c r="C1036" s="4"/>
@@ -22153,7 +22153,7 @@
       <c r="R1036" s="4"/>
       <c r="S1036" s="4"/>
     </row>
-    <row r="1037" spans="1:19">
+    <row r="1037" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1037" s="4"/>
       <c r="B1037" s="5"/>
       <c r="C1037" s="4"/>
@@ -22174,7 +22174,7 @@
       <c r="R1037" s="4"/>
       <c r="S1037" s="4"/>
     </row>
-    <row r="1038" spans="1:19">
+    <row r="1038" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1038" s="4"/>
       <c r="B1038" s="5"/>
       <c r="C1038" s="4"/>
@@ -22195,7 +22195,7 @@
       <c r="R1038" s="4"/>
       <c r="S1038" s="4"/>
     </row>
-    <row r="1039" spans="1:19">
+    <row r="1039" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1039" s="4"/>
       <c r="B1039" s="5"/>
       <c r="C1039" s="4"/>
@@ -22216,7 +22216,7 @@
       <c r="R1039" s="4"/>
       <c r="S1039" s="4"/>
     </row>
-    <row r="1040" spans="1:19">
+    <row r="1040" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1040" s="4"/>
       <c r="B1040" s="5"/>
       <c r="C1040" s="4"/>
@@ -22237,7 +22237,7 @@
       <c r="R1040" s="4"/>
       <c r="S1040" s="4"/>
     </row>
-    <row r="1041" spans="1:19">
+    <row r="1041" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1041" s="4"/>
       <c r="B1041" s="5"/>
       <c r="C1041" s="4"/>
@@ -22258,7 +22258,7 @@
       <c r="R1041" s="4"/>
       <c r="S1041" s="4"/>
     </row>
-    <row r="1042" spans="1:19">
+    <row r="1042" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1042" s="4"/>
       <c r="B1042" s="5"/>
       <c r="C1042" s="4"/>
@@ -22279,7 +22279,7 @@
       <c r="R1042" s="4"/>
       <c r="S1042" s="4"/>
     </row>
-    <row r="1043" spans="1:19">
+    <row r="1043" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1043" s="4"/>
       <c r="B1043" s="5"/>
       <c r="C1043" s="4"/>
@@ -22300,7 +22300,7 @@
       <c r="R1043" s="4"/>
       <c r="S1043" s="4"/>
     </row>
-    <row r="1044" spans="1:19">
+    <row r="1044" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1044" s="4"/>
       <c r="B1044" s="5"/>
       <c r="C1044" s="4"/>
@@ -22321,7 +22321,7 @@
       <c r="R1044" s="4"/>
       <c r="S1044" s="4"/>
     </row>
-    <row r="1045" spans="1:19">
+    <row r="1045" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1045" s="4"/>
       <c r="B1045" s="5"/>
       <c r="C1045" s="4"/>
@@ -22342,7 +22342,7 @@
       <c r="R1045" s="4"/>
       <c r="S1045" s="4"/>
     </row>
-    <row r="1046" spans="1:19">
+    <row r="1046" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1046" s="4"/>
       <c r="B1046" s="5"/>
       <c r="C1046" s="4"/>
@@ -22363,7 +22363,7 @@
       <c r="R1046" s="4"/>
       <c r="S1046" s="4"/>
     </row>
-    <row r="1047" spans="1:19">
+    <row r="1047" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1047" s="4"/>
       <c r="B1047" s="5"/>
       <c r="C1047" s="4"/>
@@ -22384,7 +22384,7 @@
       <c r="R1047" s="4"/>
       <c r="S1047" s="4"/>
     </row>
-    <row r="1048" spans="1:19">
+    <row r="1048" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1048" s="4"/>
       <c r="B1048" s="5"/>
       <c r="C1048" s="4"/>
@@ -22405,7 +22405,7 @@
       <c r="R1048" s="4"/>
       <c r="S1048" s="4"/>
     </row>
-    <row r="1049" spans="1:19">
+    <row r="1049" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1049" s="4"/>
       <c r="B1049" s="5"/>
       <c r="C1049" s="4"/>
@@ -22426,7 +22426,7 @@
       <c r="R1049" s="4"/>
       <c r="S1049" s="4"/>
     </row>
-    <row r="1050" spans="1:19">
+    <row r="1050" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1050" s="4"/>
       <c r="B1050" s="5"/>
       <c r="C1050" s="4"/>
@@ -22447,7 +22447,7 @@
       <c r="R1050" s="4"/>
       <c r="S1050" s="4"/>
     </row>
-    <row r="1051" spans="1:19">
+    <row r="1051" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1051" s="4"/>
       <c r="B1051" s="5"/>
       <c r="C1051" s="4"/>
@@ -22468,7 +22468,7 @@
       <c r="R1051" s="4"/>
       <c r="S1051" s="4"/>
     </row>
-    <row r="1052" spans="1:19">
+    <row r="1052" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1052" s="4"/>
       <c r="B1052" s="5"/>
       <c r="C1052" s="4"/>
@@ -22489,7 +22489,7 @@
       <c r="R1052" s="4"/>
       <c r="S1052" s="4"/>
     </row>
-    <row r="1053" spans="1:19">
+    <row r="1053" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1053" s="4"/>
       <c r="B1053" s="5"/>
       <c r="C1053" s="4"/>
@@ -22510,7 +22510,7 @@
       <c r="R1053" s="4"/>
       <c r="S1053" s="4"/>
     </row>
-    <row r="1054" spans="1:19">
+    <row r="1054" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1054" s="4"/>
       <c r="B1054" s="5"/>
       <c r="C1054" s="4"/>
@@ -22531,7 +22531,7 @@
       <c r="R1054" s="4"/>
       <c r="S1054" s="4"/>
     </row>
-    <row r="1055" spans="1:19">
+    <row r="1055" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1055" s="4"/>
       <c r="B1055" s="5"/>
       <c r="C1055" s="4"/>
@@ -22552,7 +22552,7 @@
       <c r="R1055" s="4"/>
       <c r="S1055" s="4"/>
     </row>
-    <row r="1056" spans="1:19">
+    <row r="1056" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1056" s="4"/>
       <c r="B1056" s="5"/>
       <c r="C1056" s="4"/>
@@ -22573,7 +22573,7 @@
       <c r="R1056" s="4"/>
       <c r="S1056" s="4"/>
     </row>
-    <row r="1057" spans="1:19">
+    <row r="1057" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1057" s="4"/>
       <c r="B1057" s="5"/>
       <c r="C1057" s="4"/>
@@ -22594,7 +22594,7 @@
       <c r="R1057" s="4"/>
       <c r="S1057" s="4"/>
     </row>
-    <row r="1058" spans="1:19">
+    <row r="1058" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1058" s="4"/>
       <c r="B1058" s="5"/>
       <c r="C1058" s="4"/>
@@ -22615,7 +22615,7 @@
       <c r="R1058" s="4"/>
       <c r="S1058" s="4"/>
     </row>
-    <row r="1059" spans="1:19">
+    <row r="1059" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1059" s="4"/>
       <c r="B1059" s="5"/>
       <c r="C1059" s="4"/>
@@ -22636,7 +22636,7 @@
       <c r="R1059" s="4"/>
       <c r="S1059" s="4"/>
     </row>
-    <row r="1060" spans="1:19">
+    <row r="1060" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1060" s="4"/>
       <c r="B1060" s="5"/>
       <c r="C1060" s="4"/>
@@ -22657,7 +22657,7 @@
       <c r="R1060" s="4"/>
       <c r="S1060" s="4"/>
     </row>
-    <row r="1061" spans="1:19">
+    <row r="1061" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1061" s="4"/>
       <c r="B1061" s="5"/>
       <c r="C1061" s="4"/>
@@ -22678,7 +22678,7 @@
       <c r="R1061" s="4"/>
       <c r="S1061" s="4"/>
     </row>
-    <row r="1062" spans="1:19">
+    <row r="1062" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1062" s="4"/>
       <c r="B1062" s="5"/>
       <c r="C1062" s="4"/>
@@ -22699,7 +22699,7 @@
       <c r="R1062" s="4"/>
       <c r="S1062" s="4"/>
     </row>
-    <row r="1063" spans="1:19">
+    <row r="1063" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1063" s="4"/>
       <c r="B1063" s="5"/>
       <c r="C1063" s="4"/>
@@ -22720,7 +22720,7 @@
       <c r="R1063" s="4"/>
       <c r="S1063" s="4"/>
     </row>
-    <row r="1064" spans="1:19">
+    <row r="1064" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1064" s="4"/>
       <c r="B1064" s="5"/>
       <c r="C1064" s="4"/>
@@ -22741,7 +22741,7 @@
       <c r="R1064" s="4"/>
       <c r="S1064" s="4"/>
     </row>
-    <row r="1065" spans="1:19">
+    <row r="1065" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1065" s="4"/>
       <c r="B1065" s="5"/>
       <c r="C1065" s="4"/>
@@ -22762,7 +22762,7 @@
       <c r="R1065" s="4"/>
       <c r="S1065" s="4"/>
     </row>
-    <row r="1066" spans="1:19">
+    <row r="1066" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1066" s="4"/>
       <c r="B1066" s="5"/>
       <c r="C1066" s="4"/>
@@ -22783,7 +22783,7 @@
       <c r="R1066" s="4"/>
       <c r="S1066" s="4"/>
     </row>
-    <row r="1067" spans="1:19">
+    <row r="1067" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1067" s="4"/>
       <c r="B1067" s="5"/>
       <c r="C1067" s="4"/>
@@ -22804,7 +22804,7 @@
       <c r="R1067" s="4"/>
       <c r="S1067" s="4"/>
     </row>
-    <row r="1068" spans="1:19">
+    <row r="1068" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1068" s="4"/>
       <c r="B1068" s="5"/>
       <c r="C1068" s="4"/>
@@ -22825,7 +22825,7 @@
       <c r="R1068" s="4"/>
       <c r="S1068" s="4"/>
     </row>
-    <row r="1069" spans="1:19">
+    <row r="1069" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1069" s="4"/>
       <c r="B1069" s="5"/>
       <c r="C1069" s="4"/>
@@ -22846,7 +22846,7 @@
       <c r="R1069" s="4"/>
       <c r="S1069" s="4"/>
     </row>
-    <row r="1070" spans="1:19">
+    <row r="1070" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1070" s="4"/>
       <c r="B1070" s="5"/>
       <c r="C1070" s="4"/>
@@ -22867,7 +22867,7 @@
       <c r="R1070" s="4"/>
       <c r="S1070" s="4"/>
     </row>
-    <row r="1071" spans="1:19">
+    <row r="1071" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1071" s="4"/>
       <c r="B1071" s="5"/>
       <c r="C1071" s="4"/>
@@ -22888,7 +22888,7 @@
       <c r="R1071" s="4"/>
       <c r="S1071" s="4"/>
     </row>
-    <row r="1072" spans="1:19">
+    <row r="1072" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1072" s="4"/>
       <c r="B1072" s="5"/>
       <c r="C1072" s="4"/>
@@ -22909,7 +22909,7 @@
       <c r="R1072" s="4"/>
       <c r="S1072" s="4"/>
     </row>
-    <row r="1073" spans="1:19">
+    <row r="1073" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1073" s="4"/>
       <c r="B1073" s="5"/>
       <c r="C1073" s="4"/>
@@ -22930,7 +22930,7 @@
       <c r="R1073" s="4"/>
       <c r="S1073" s="4"/>
     </row>
-    <row r="1074" spans="1:19">
+    <row r="1074" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1074" s="4"/>
       <c r="B1074" s="5"/>
       <c r="C1074" s="4"/>
@@ -22951,7 +22951,7 @@
       <c r="R1074" s="4"/>
       <c r="S1074" s="4"/>
     </row>
-    <row r="1075" spans="1:19">
+    <row r="1075" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1075" s="4"/>
       <c r="B1075" s="5"/>
       <c r="C1075" s="4"/>
@@ -22972,7 +22972,7 @@
       <c r="R1075" s="4"/>
       <c r="S1075" s="4"/>
     </row>
-    <row r="1076" spans="1:19">
+    <row r="1076" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1076" s="4"/>
       <c r="B1076" s="5"/>
       <c r="C1076" s="4"/>
@@ -22993,7 +22993,7 @@
       <c r="R1076" s="4"/>
       <c r="S1076" s="4"/>
     </row>
-    <row r="1077" spans="1:19">
+    <row r="1077" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1077" s="4"/>
       <c r="B1077" s="5"/>
       <c r="C1077" s="4"/>
@@ -23014,7 +23014,7 @@
       <c r="R1077" s="4"/>
       <c r="S1077" s="4"/>
     </row>
-    <row r="1078" spans="1:19">
+    <row r="1078" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1078" s="4"/>
       <c r="B1078" s="5"/>
       <c r="C1078" s="4"/>
@@ -23035,7 +23035,7 @@
       <c r="R1078" s="4"/>
       <c r="S1078" s="4"/>
     </row>
-    <row r="1079" spans="1:19">
+    <row r="1079" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1079" s="4"/>
       <c r="B1079" s="5"/>
       <c r="C1079" s="4"/>
@@ -23056,7 +23056,7 @@
       <c r="R1079" s="4"/>
       <c r="S1079" s="4"/>
     </row>
-    <row r="1080" spans="1:19">
+    <row r="1080" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1080" s="4"/>
       <c r="B1080" s="5"/>
       <c r="C1080" s="4"/>
@@ -23077,7 +23077,7 @@
       <c r="R1080" s="4"/>
       <c r="S1080" s="4"/>
     </row>
-    <row r="1081" spans="1:19">
+    <row r="1081" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1081" s="4"/>
       <c r="B1081" s="5"/>
       <c r="C1081" s="4"/>
@@ -23098,7 +23098,7 @@
       <c r="R1081" s="4"/>
       <c r="S1081" s="4"/>
     </row>
-    <row r="1082" spans="1:19">
+    <row r="1082" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1082" s="4"/>
       <c r="B1082" s="5"/>
       <c r="C1082" s="4"/>
@@ -23119,7 +23119,7 @@
       <c r="R1082" s="4"/>
       <c r="S1082" s="4"/>
     </row>
-    <row r="1083" spans="1:19">
+    <row r="1083" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1083" s="4"/>
       <c r="B1083" s="5"/>
       <c r="C1083" s="4"/>
@@ -23140,7 +23140,7 @@
       <c r="R1083" s="4"/>
       <c r="S1083" s="4"/>
     </row>
-    <row r="1084" spans="1:19">
+    <row r="1084" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1084" s="4"/>
       <c r="B1084" s="5"/>
       <c r="C1084" s="4"/>
@@ -23161,7 +23161,7 @@
       <c r="R1084" s="4"/>
       <c r="S1084" s="4"/>
     </row>
-    <row r="1085" spans="1:19">
+    <row r="1085" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1085" s="4"/>
       <c r="B1085" s="5"/>
       <c r="C1085" s="4"/>
@@ -23182,7 +23182,7 @@
       <c r="R1085" s="4"/>
       <c r="S1085" s="4"/>
     </row>
-    <row r="1086" spans="1:19">
+    <row r="1086" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1086" s="4"/>
       <c r="B1086" s="5"/>
       <c r="C1086" s="4"/>
@@ -23203,7 +23203,7 @@
       <c r="R1086" s="4"/>
       <c r="S1086" s="4"/>
     </row>
-    <row r="1087" spans="1:19">
+    <row r="1087" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1087" s="4"/>
       <c r="B1087" s="5"/>
       <c r="C1087" s="4"/>
@@ -23224,7 +23224,7 @@
       <c r="R1087" s="4"/>
       <c r="S1087" s="4"/>
     </row>
-    <row r="1088" spans="1:19">
+    <row r="1088" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1088" s="4"/>
       <c r="B1088" s="5"/>
       <c r="C1088" s="4"/>
@@ -23245,7 +23245,7 @@
       <c r="R1088" s="4"/>
       <c r="S1088" s="4"/>
     </row>
-    <row r="1089" spans="1:19">
+    <row r="1089" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1089" s="4"/>
       <c r="B1089" s="5"/>
       <c r="C1089" s="4"/>
@@ -23266,7 +23266,7 @@
       <c r="R1089" s="4"/>
       <c r="S1089" s="4"/>
     </row>
-    <row r="1090" spans="1:19">
+    <row r="1090" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1090" s="4"/>
       <c r="B1090" s="5"/>
       <c r="C1090" s="4"/>
@@ -23287,7 +23287,7 @@
       <c r="R1090" s="4"/>
       <c r="S1090" s="4"/>
     </row>
-    <row r="1091" spans="1:19">
+    <row r="1091" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1091" s="4"/>
       <c r="B1091" s="5"/>
       <c r="C1091" s="4"/>
@@ -23308,7 +23308,7 @@
       <c r="R1091" s="4"/>
       <c r="S1091" s="4"/>
     </row>
-    <row r="1092" spans="1:19">
+    <row r="1092" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1092" s="4"/>
       <c r="B1092" s="5"/>
       <c r="C1092" s="4"/>
@@ -23329,7 +23329,7 @@
       <c r="R1092" s="4"/>
       <c r="S1092" s="4"/>
     </row>
-    <row r="1093" spans="1:19">
+    <row r="1093" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1093" s="4"/>
       <c r="B1093" s="5"/>
       <c r="C1093" s="4"/>
@@ -23350,7 +23350,7 @@
       <c r="R1093" s="4"/>
       <c r="S1093" s="4"/>
     </row>
-    <row r="1094" spans="1:19">
+    <row r="1094" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1094" s="4"/>
       <c r="B1094" s="5"/>
       <c r="C1094" s="4"/>
@@ -23371,7 +23371,7 @@
       <c r="R1094" s="4"/>
       <c r="S1094" s="4"/>
     </row>
-    <row r="1095" spans="1:19">
+    <row r="1095" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1095" s="4"/>
       <c r="B1095" s="5"/>
       <c r="C1095" s="4"/>
@@ -23392,7 +23392,7 @@
       <c r="R1095" s="4"/>
       <c r="S1095" s="4"/>
     </row>
-    <row r="1096" spans="1:19">
+    <row r="1096" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1096" s="4"/>
       <c r="B1096" s="5"/>
       <c r="C1096" s="4"/>
@@ -23413,7 +23413,7 @@
       <c r="R1096" s="4"/>
       <c r="S1096" s="4"/>
     </row>
-    <row r="1097" spans="1:19">
+    <row r="1097" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1097" s="4"/>
       <c r="B1097" s="5"/>
       <c r="C1097" s="4"/>
@@ -23434,7 +23434,7 @@
       <c r="R1097" s="4"/>
       <c r="S1097" s="4"/>
     </row>
-    <row r="1098" spans="1:19">
+    <row r="1098" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1098" s="4"/>
       <c r="B1098" s="5"/>
       <c r="C1098" s="4"/>
@@ -23455,7 +23455,7 @@
       <c r="R1098" s="4"/>
       <c r="S1098" s="4"/>
     </row>
-    <row r="1099" spans="1:19">
+    <row r="1099" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1099" s="4"/>
       <c r="B1099" s="5"/>
       <c r="C1099" s="4"/>
@@ -23476,7 +23476,7 @@
       <c r="R1099" s="4"/>
       <c r="S1099" s="4"/>
     </row>
-    <row r="1100" spans="1:19">
+    <row r="1100" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1100" s="4"/>
       <c r="B1100" s="5"/>
       <c r="C1100" s="4"/>
@@ -23497,7 +23497,7 @@
       <c r="R1100" s="4"/>
       <c r="S1100" s="4"/>
     </row>
-    <row r="1101" spans="1:19">
+    <row r="1101" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1101" s="4"/>
       <c r="B1101" s="5"/>
       <c r="C1101" s="4"/>
@@ -23518,7 +23518,7 @@
       <c r="R1101" s="4"/>
       <c r="S1101" s="4"/>
     </row>
-    <row r="1102" spans="1:19">
+    <row r="1102" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1102" s="4"/>
       <c r="B1102" s="5"/>
       <c r="C1102" s="4"/>
